--- a/audit_risk_register.xlsx
+++ b/audit_risk_register.xlsx
@@ -690,7 +690,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>审计风险评估热力图谱 · 使用说明</t>
+          <t>审计风险评估热力图谱 v1.2 · 使用说明</t>
         </is>
       </c>
     </row>

--- a/audit_risk_register.xlsx
+++ b/audit_risk_register.xlsx
@@ -22,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -132,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +192,9 @@
     <xf numFmtId="9" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -216,6 +221,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2440,7 +2446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z203"/>
+  <dimension ref="A1:AB203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2469,6 +2475,8 @@
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="40" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="12" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2620,6 +2628,18 @@
           <t>打分依据</t>
         </is>
       </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>优先级排序键
+(辅助)</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>选定期间排序键
+(辅助)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
@@ -2721,6 +2741,14 @@
           <t>2025 年内审抽查发现 3 笔超标准报销；预算系统 2025Q4 上线刚性拦截</t>
         </is>
       </c>
+      <c r="AA4" s="25">
+        <f>IF($A4="","",IF(T4="","",T4+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="25">
+        <f>IF($A4="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F4='汇总与优先级'!$B$2),$AA4,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
@@ -2822,6 +2850,14 @@
           <t>2025 年内审抽查发现 3 笔超标准报销；预算系统 2025Q4 上线刚性拦截</t>
         </is>
       </c>
+      <c r="AA5" s="25">
+        <f>IF($A5="","",IF(T5="","",T5+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="25">
+        <f>IF($A5="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F5='汇总与优先级'!$B$2),$AA5,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
@@ -2923,6 +2959,14 @@
           <t>上年度审计调整收入截止事项 2 项，涉及金额 120 万元</t>
         </is>
       </c>
+      <c r="AA6" s="25">
+        <f>IF($A6="","",IF(T6="","",T6+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB6" s="25">
+        <f>IF($A6="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F6='汇总与优先级'!$B$2),$AA6,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -3024,6 +3068,14 @@
           <t>上年度审计调整收入截止事项 2 项，涉及金额 120 万元</t>
         </is>
       </c>
+      <c r="AA7" s="25">
+        <f>IF($A7="","",IF(T7="","",T7+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="25">
+        <f>IF($A7="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F7='汇总与优先级'!$B$2),$AA7,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
@@ -3125,6 +3177,14 @@
           <t>资金制度修订后未再发现越权支付；网银复核日志抽查正常</t>
         </is>
       </c>
+      <c r="AA8" s="25">
+        <f>IF($A8="","",IF(T8="","",T8+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="25">
+        <f>IF($A8="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F8='汇总与优先级'!$B$2),$AA8,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -3226,6 +3286,14 @@
           <t>资金制度修订后未再发现越权支付；网银复核日志抽查正常</t>
         </is>
       </c>
+      <c r="AA9" s="25">
+        <f>IF($A9="","",IF(T9="","",T9+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="25">
+        <f>IF($A9="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F9='汇总与优先级'!$B$2),$AA9,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
@@ -3327,6 +3395,14 @@
           <t>近两年招标投诉 2 起；关联供应商筛查发现 1 家未申报关联关系</t>
         </is>
       </c>
+      <c r="AA10" s="25">
+        <f>IF($A10="","",IF(T10="","",T10+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="25">
+        <f>IF($A10="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F10='汇总与优先级'!$B$2),$AA10,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -3428,6 +3504,14 @@
           <t>近两年招标投诉 2 起；关联供应商筛查发现 1 家未申报关联关系</t>
         </is>
       </c>
+      <c r="AA11" s="25">
+        <f>IF($A11="","",IF(T11="","",T11+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="25">
+        <f>IF($A11="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F11='汇总与优先级'!$B$2),$AA11,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
@@ -3529,6 +3613,14 @@
           <t>法律纠纷台账 2 起未决诉讼均涉合同条款缺陷</t>
         </is>
       </c>
+      <c r="AA12" s="25">
+        <f>IF($A12="","",IF(T12="","",T12+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="25">
+        <f>IF($A12="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F12='汇总与优先级'!$B$2),$AA12,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
@@ -3630,6 +3722,14 @@
           <t>法律纠纷台账 2 起未决诉讼均涉合同条款缺陷</t>
         </is>
       </c>
+      <c r="AA13" s="25">
+        <f>IF($A13="","",IF(T13="","",T13+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="25">
+        <f>IF($A13="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F13='汇总与优先级'!$B$2),$AA13,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
@@ -3734,6 +3834,14 @@
           <t>仓库验收单抽查 20% 缺少影像附件</t>
         </is>
       </c>
+      <c r="AA14" s="25">
+        <f>IF($A14="","",IF(T14="","",T14+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="25">
+        <f>IF($A14="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F14='汇总与优先级'!$B$2),$AA14,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -3838,6 +3946,14 @@
           <t>仓库验收单抽查 20% 缺少影像附件</t>
         </is>
       </c>
+      <c r="AA15" s="25">
+        <f>IF($A15="","",IF(T15="","",T15+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB15" s="25">
+        <f>IF($A15="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F15='汇总与优先级'!$B$2),$AA15,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
@@ -3942,6 +4058,14 @@
           <t>在建项目概算执行率 108%，设计变更签证 47 项</t>
         </is>
       </c>
+      <c r="AA16" s="25">
+        <f>IF($A16="","",IF(T16="","",T16+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB16" s="25">
+        <f>IF($A16="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F16='汇总与优先级'!$B$2),$AA16,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -4046,6 +4170,14 @@
           <t>在建项目概算执行率 108%，设计变更签证 47 项</t>
         </is>
       </c>
+      <c r="AA17" s="25">
+        <f>IF($A17="","",IF(T17="","",T17+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB17" s="25">
+        <f>IF($A17="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F17='汇总与优先级'!$B$2),$AA17,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
@@ -4150,6 +4282,14 @@
           <t>本年度安监通报 1 起未遂事故；特种作业持证率 100%</t>
         </is>
       </c>
+      <c r="AA18" s="25">
+        <f>IF($A18="","",IF(T18="","",T18+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB18" s="25">
+        <f>IF($A18="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F18='汇总与优先级'!$B$2),$AA18,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
@@ -4254,6 +4394,14 @@
           <t>本年度安监通报 1 起未遂事故；特种作业持证率 100%</t>
         </is>
       </c>
+      <c r="AA19" s="25">
+        <f>IF($A19="","",IF(T19="","",T19+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB19" s="25">
+        <f>IF($A19="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F19='汇总与优先级'!$B$2),$AA19,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
@@ -4355,6 +4503,14 @@
           <t>两个竣工项目结算超期 6 个月以上，暂估挂账 860 万元</t>
         </is>
       </c>
+      <c r="AA20" s="25">
+        <f>IF($A20="","",IF(T20="","",T20+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB20" s="25">
+        <f>IF($A20="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F20='汇总与优先级'!$B$2),$AA20,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
@@ -4456,6 +4612,14 @@
           <t>两个竣工项目结算超期 6 个月以上，暂估挂账 860 万元</t>
         </is>
       </c>
+      <c r="AA21" s="25">
+        <f>IF($A21="","",IF(T21="","",T21+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB21" s="25">
+        <f>IF($A21="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F21='汇总与优先级'!$B$2),$AA21,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
@@ -4557,6 +4721,14 @@
           <t>权限复核发现 3 个离职未销账号；日志审计已覆盖核心系统</t>
         </is>
       </c>
+      <c r="AA22" s="25">
+        <f>IF($A22="","",IF(T22="","",T22+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB22" s="25">
+        <f>IF($A22="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F22='汇总与优先级'!$B$2),$AA22,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
@@ -4658,6 +4830,14 @@
           <t>权限复核发现 3 个离职未销账号；日志审计已覆盖核心系统</t>
         </is>
       </c>
+      <c r="AA23" s="25">
+        <f>IF($A23="","",IF(T23="","",T23+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB23" s="25">
+        <f>IF($A23="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F23='汇总与优先级'!$B$2),$AA23,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
@@ -4759,6 +4939,14 @@
           <t>灾备演练 RTO 达标；双活改造完成验收</t>
         </is>
       </c>
+      <c r="AA24" s="25">
+        <f>IF($A24="","",IF(T24="","",T24+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB24" s="25">
+        <f>IF($A24="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F24='汇总与优先级'!$B$2),$AA24,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
@@ -4860,6 +5048,14 @@
           <t>灾备演练 RTO 达标；双活改造完成验收</t>
         </is>
       </c>
+      <c r="AA25" s="25">
+        <f>IF($A25="","",IF(T25="","",T25+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB25" s="25">
+        <f>IF($A25="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F25='汇总与优先级'!$B$2),$AA25,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
@@ -4961,6 +5157,14 @@
           <t>行业勒索事件高发；EDR 终端覆盖率因预算削减降至 60%</t>
         </is>
       </c>
+      <c r="AA26" s="25">
+        <f>IF($A26="","",IF(T26="","",T26+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB26" s="25">
+        <f>IF($A26="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F26='汇总与优先级'!$B$2),$AA26,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
@@ -5062,6 +5266,14 @@
           <t>行业勒索事件高发；EDR 终端覆盖率因预算削减降至 60%</t>
         </is>
       </c>
+      <c r="AA27" s="25">
+        <f>IF($A27="","",IF(T27="","",T27+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB27" s="25">
+        <f>IF($A27="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F27='汇总与优先级'!$B$2),$AA27,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
@@ -5160,6 +5372,14 @@
           <t>财务、信息骨干离职率同比上升；AB 角覆盖不到位</t>
         </is>
       </c>
+      <c r="AA28" s="25">
+        <f>IF($A28="","",IF(T28="","",T28+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB28" s="25">
+        <f>IF($A28="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F28='汇总与优先级'!$B$2),$AA28,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
@@ -5258,6 +5478,14 @@
           <t>财务、信息骨干离职率同比上升；AB 角覆盖不到位</t>
         </is>
       </c>
+      <c r="AA29" s="25">
+        <f>IF($A29="","",IF(T29="","",T29+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB29" s="25">
+        <f>IF($A29="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F29='汇总与优先级'!$B$2),$AA29,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
@@ -5359,6 +5587,14 @@
           <t>近三年未发现招聘舞弊案例；背景调查执行率 100%</t>
         </is>
       </c>
+      <c r="AA30" s="25">
+        <f>IF($A30="","",IF(T30="","",T30+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB30" s="25">
+        <f>IF($A30="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F30='汇总与优先级'!$B$2),$AA30,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
@@ -5460,6 +5696,14 @@
           <t>近三年未发现招聘舞弊案例；背景调查执行率 100%</t>
         </is>
       </c>
+      <c r="AA31" s="25">
+        <f>IF($A31="","",IF(T31="","",T31+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB31" s="25">
+        <f>IF($A31="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F31='汇总与优先级'!$B$2),$AA31,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
@@ -5564,6 +5808,14 @@
           <t>上期盘点差异率 0.8% 已整改；条码管理覆盖主要仓库</t>
         </is>
       </c>
+      <c r="AA32" s="25">
+        <f>IF($A32="","",IF(T32="","",T32+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB32" s="25">
+        <f>IF($A32="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F32='汇总与优先级'!$B$2),$AA32,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
@@ -5668,6 +5920,14 @@
           <t>上期盘点差异率 0.8% 已整改；条码管理覆盖主要仓库</t>
         </is>
       </c>
+      <c r="AA33" s="25">
+        <f>IF($A33="","",IF(T33="","",T33+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB33" s="25">
+        <f>IF($A33="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F33='汇总与优先级'!$B$2),$AA33,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
@@ -5772,6 +6032,14 @@
           <t>闲置设备原值 1,200 万元；投资后评价制度已发布</t>
         </is>
       </c>
+      <c r="AA34" s="25">
+        <f>IF($A34="","",IF(T34="","",T34+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB34" s="25">
+        <f>IF($A34="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F34='汇总与优先级'!$B$2),$AA34,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
@@ -5876,6 +6144,14 @@
           <t>闲置设备原值 1,200 万元；投资后评价制度已发布</t>
         </is>
       </c>
+      <c r="AA35" s="25">
+        <f>IF($A35="","",IF(T35="","",T35+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB35" s="25">
+        <f>IF($A35="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F35='汇总与优先级'!$B$2),$AA35,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
@@ -5980,6 +6256,14 @@
           <t>上年度两个投资项目未达可研预期收益；董事会决策留痕不全</t>
         </is>
       </c>
+      <c r="AA36" s="25">
+        <f>IF($A36="","",IF(T36="","",T36+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB36" s="25">
+        <f>IF($A36="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F36='汇总与优先级'!$B$2),$AA36,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
@@ -6084,6 +6368,14 @@
           <t>上年度两个投资项目未达可研预期收益；董事会决策留痕不全</t>
         </is>
       </c>
+      <c r="AA37" s="25">
+        <f>IF($A37="","",IF(T37="","",T37+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB37" s="25">
+        <f>IF($A37="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F37='汇总与优先级'!$B$2),$AA37,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
@@ -6185,6 +6477,14 @@
           <t>审计发现 2 项大额事项未见集体决策记录</t>
         </is>
       </c>
+      <c r="AA38" s="25">
+        <f>IF($A38="","",IF(T38="","",T38+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB38" s="25">
+        <f>IF($A38="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F38='汇总与优先级'!$B$2),$AA38,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
@@ -6286,6 +6586,14 @@
           <t>审计发现 2 项大额事项未见集体决策记录</t>
         </is>
       </c>
+      <c r="AA39" s="25">
+        <f>IF($A39="","",IF(T39="","",T39+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB39" s="25">
+        <f>IF($A39="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F39='汇总与优先级'!$B$2),$AA39,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
@@ -6387,6 +6695,14 @@
           <t>上年度汇算清缴调整事项 5 项；无税务处罚记录</t>
         </is>
       </c>
+      <c r="AA40" s="25">
+        <f>IF($A40="","",IF(T40="","",T40+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB40" s="25">
+        <f>IF($A40="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F40='汇总与优先级'!$B$2),$AA40,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
@@ -6488,6 +6804,14 @@
           <t>上年度汇算清缴调整事项 5 项；无税务处罚记录</t>
         </is>
       </c>
+      <c r="AA41" s="25">
+        <f>IF($A41="","",IF(T41="","",T41+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB41" s="25">
+        <f>IF($A41="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F41='汇总与优先级'!$B$2),$AA41,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
@@ -6592,6 +6916,14 @@
           <t>履约台账覆盖率 70%；2 份合同变更未走审批</t>
         </is>
       </c>
+      <c r="AA42" s="25">
+        <f>IF($A42="","",IF(T42="","",T42+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB42" s="25">
+        <f>IF($A42="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F42='汇总与优先级'!$B$2),$AA42,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
@@ -6696,6 +7028,14 @@
           <t>履约台账覆盖率 70%；2 份合同变更未走审批</t>
         </is>
       </c>
+      <c r="AA43" s="25">
+        <f>IF($A43="","",IF(T43="","",T43+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB43" s="25">
+        <f>IF($A43="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F43='汇总与优先级'!$B$2),$AA43,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
@@ -6800,6 +7140,14 @@
           <t>外包商名录 3 年未更新；发生 1 起外包安全事故</t>
         </is>
       </c>
+      <c r="AA44" s="25">
+        <f>IF($A44="","",IF(T44="","",T44+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB44" s="25">
+        <f>IF($A44="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F44='汇总与优先级'!$B$2),$AA44,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
@@ -6904,6 +7252,14 @@
           <t>外包商名录 3 年未更新；发生 1 起外包安全事故</t>
         </is>
       </c>
+      <c r="AA45" s="25">
+        <f>IF($A45="","",IF(T45="","",T45+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB45" s="25">
+        <f>IF($A45="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F45='汇总与优先级'!$B$2),$AA45,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
@@ -7005,6 +7361,14 @@
           <t>数据监管新规密集出台；行业 App 违规通报案例增多</t>
         </is>
       </c>
+      <c r="AA46" s="25">
+        <f>IF($A46="","",IF(T46="","",T46+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB46" s="25">
+        <f>IF($A46="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F46='汇总与优先级'!$B$2),$AA46,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
@@ -7106,6 +7470,14 @@
           <t>数据监管新规密集出台；行业 App 违规通报案例增多</t>
         </is>
       </c>
+      <c r="AA47" s="25">
+        <f>IF($A47="","",IF(T47="","",T47+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB47" s="25">
+        <f>IF($A47="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F47='汇总与优先级'!$B$2),$AA47,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
@@ -7210,6 +7582,14 @@
           <t>上年度环保在线监测数据 2 次异常；未发生处罚</t>
         </is>
       </c>
+      <c r="AA48" s="25">
+        <f>IF($A48="","",IF(T48="","",T48+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB48" s="25">
+        <f>IF($A48="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F48='汇总与优先级'!$B$2),$AA48,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="22" t="inlineStr">
@@ -7314,6 +7694,14 @@
           <t>上年度环保在线监测数据 2 次异常；未发生处罚</t>
         </is>
       </c>
+      <c r="AA49" s="25">
+        <f>IF($A49="","",IF(T49="","",T49+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB49" s="25">
+        <f>IF($A49="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F49='汇总与优先级'!$B$2),$AA49,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
@@ -7415,6 +7803,14 @@
           <t>账户年检完成率 100%；票据背书抽查发现 1 处瑕疵</t>
         </is>
       </c>
+      <c r="AA50" s="25">
+        <f>IF($A50="","",IF(T50="","",T50+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB50" s="25">
+        <f>IF($A50="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F50='汇总与优先级'!$B$2),$AA50,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
@@ -7515,6 +7911,14 @@
         <is>
           <t>账户年检完成率 100%；票据背书抽查发现 1 处瑕疵</t>
         </is>
+      </c>
+      <c r="AA51" s="25">
+        <f>IF($A51="","",IF(T51="","",T51+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB51" s="25">
+        <f>IF($A51="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F51='汇总与优先级'!$B$2),$AA51,NA()))</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -7558,6 +7962,14 @@
         <f>IF($A52="","",IF(OR(Q52="",Q52=0),"",(Q52-T52)/Q52))</f>
         <v/>
       </c>
+      <c r="AA52" s="25">
+        <f>IF($A52="","",IF(T52="","",T52+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB52" s="25">
+        <f>IF($A52="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F52='汇总与优先级'!$B$2),$AA52,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="P53" s="23">
@@ -7600,6 +8012,14 @@
         <f>IF($A53="","",IF(OR(Q53="",Q53=0),"",(Q53-T53)/Q53))</f>
         <v/>
       </c>
+      <c r="AA53" s="25">
+        <f>IF($A53="","",IF(T53="","",T53+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB53" s="25">
+        <f>IF($A53="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F53='汇总与优先级'!$B$2),$AA53,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="P54" s="23">
@@ -7642,6 +8062,14 @@
         <f>IF($A54="","",IF(OR(Q54="",Q54=0),"",(Q54-T54)/Q54))</f>
         <v/>
       </c>
+      <c r="AA54" s="25">
+        <f>IF($A54="","",IF(T54="","",T54+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB54" s="25">
+        <f>IF($A54="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F54='汇总与优先级'!$B$2),$AA54,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="P55" s="23">
@@ -7684,6 +8112,14 @@
         <f>IF($A55="","",IF(OR(Q55="",Q55=0),"",(Q55-T55)/Q55))</f>
         <v/>
       </c>
+      <c r="AA55" s="25">
+        <f>IF($A55="","",IF(T55="","",T55+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB55" s="25">
+        <f>IF($A55="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F55='汇总与优先级'!$B$2),$AA55,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="P56" s="23">
@@ -7726,6 +8162,14 @@
         <f>IF($A56="","",IF(OR(Q56="",Q56=0),"",(Q56-T56)/Q56))</f>
         <v/>
       </c>
+      <c r="AA56" s="25">
+        <f>IF($A56="","",IF(T56="","",T56+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB56" s="25">
+        <f>IF($A56="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F56='汇总与优先级'!$B$2),$AA56,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="P57" s="23">
@@ -7768,6 +8212,14 @@
         <f>IF($A57="","",IF(OR(Q57="",Q57=0),"",(Q57-T57)/Q57))</f>
         <v/>
       </c>
+      <c r="AA57" s="25">
+        <f>IF($A57="","",IF(T57="","",T57+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB57" s="25">
+        <f>IF($A57="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F57='汇总与优先级'!$B$2),$AA57,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="P58" s="23">
@@ -7810,6 +8262,14 @@
         <f>IF($A58="","",IF(OR(Q58="",Q58=0),"",(Q58-T58)/Q58))</f>
         <v/>
       </c>
+      <c r="AA58" s="25">
+        <f>IF($A58="","",IF(T58="","",T58+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB58" s="25">
+        <f>IF($A58="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F58='汇总与优先级'!$B$2),$AA58,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="P59" s="23">
@@ -7852,6 +8312,14 @@
         <f>IF($A59="","",IF(OR(Q59="",Q59=0),"",(Q59-T59)/Q59))</f>
         <v/>
       </c>
+      <c r="AA59" s="25">
+        <f>IF($A59="","",IF(T59="","",T59+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB59" s="25">
+        <f>IF($A59="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F59='汇总与优先级'!$B$2),$AA59,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="P60" s="23">
@@ -7894,6 +8362,14 @@
         <f>IF($A60="","",IF(OR(Q60="",Q60=0),"",(Q60-T60)/Q60))</f>
         <v/>
       </c>
+      <c r="AA60" s="25">
+        <f>IF($A60="","",IF(T60="","",T60+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB60" s="25">
+        <f>IF($A60="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F60='汇总与优先级'!$B$2),$AA60,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="P61" s="23">
@@ -7936,6 +8412,14 @@
         <f>IF($A61="","",IF(OR(Q61="",Q61=0),"",(Q61-T61)/Q61))</f>
         <v/>
       </c>
+      <c r="AA61" s="25">
+        <f>IF($A61="","",IF(T61="","",T61+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB61" s="25">
+        <f>IF($A61="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F61='汇总与优先级'!$B$2),$AA61,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="P62" s="23">
@@ -7978,6 +8462,14 @@
         <f>IF($A62="","",IF(OR(Q62="",Q62=0),"",(Q62-T62)/Q62))</f>
         <v/>
       </c>
+      <c r="AA62" s="25">
+        <f>IF($A62="","",IF(T62="","",T62+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB62" s="25">
+        <f>IF($A62="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F62='汇总与优先级'!$B$2),$AA62,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="P63" s="23">
@@ -8020,6 +8512,14 @@
         <f>IF($A63="","",IF(OR(Q63="",Q63=0),"",(Q63-T63)/Q63))</f>
         <v/>
       </c>
+      <c r="AA63" s="25">
+        <f>IF($A63="","",IF(T63="","",T63+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB63" s="25">
+        <f>IF($A63="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F63='汇总与优先级'!$B$2),$AA63,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="P64" s="23">
@@ -8062,6 +8562,14 @@
         <f>IF($A64="","",IF(OR(Q64="",Q64=0),"",(Q64-T64)/Q64))</f>
         <v/>
       </c>
+      <c r="AA64" s="25">
+        <f>IF($A64="","",IF(T64="","",T64+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB64" s="25">
+        <f>IF($A64="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F64='汇总与优先级'!$B$2),$AA64,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="P65" s="23">
@@ -8104,6 +8612,14 @@
         <f>IF($A65="","",IF(OR(Q65="",Q65=0),"",(Q65-T65)/Q65))</f>
         <v/>
       </c>
+      <c r="AA65" s="25">
+        <f>IF($A65="","",IF(T65="","",T65+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB65" s="25">
+        <f>IF($A65="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F65='汇总与优先级'!$B$2),$AA65,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="P66" s="23">
@@ -8146,6 +8662,14 @@
         <f>IF($A66="","",IF(OR(Q66="",Q66=0),"",(Q66-T66)/Q66))</f>
         <v/>
       </c>
+      <c r="AA66" s="25">
+        <f>IF($A66="","",IF(T66="","",T66+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB66" s="25">
+        <f>IF($A66="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F66='汇总与优先级'!$B$2),$AA66,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="P67" s="23">
@@ -8188,6 +8712,14 @@
         <f>IF($A67="","",IF(OR(Q67="",Q67=0),"",(Q67-T67)/Q67))</f>
         <v/>
       </c>
+      <c r="AA67" s="25">
+        <f>IF($A67="","",IF(T67="","",T67+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB67" s="25">
+        <f>IF($A67="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F67='汇总与优先级'!$B$2),$AA67,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="P68" s="23">
@@ -8230,6 +8762,14 @@
         <f>IF($A68="","",IF(OR(Q68="",Q68=0),"",(Q68-T68)/Q68))</f>
         <v/>
       </c>
+      <c r="AA68" s="25">
+        <f>IF($A68="","",IF(T68="","",T68+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB68" s="25">
+        <f>IF($A68="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F68='汇总与优先级'!$B$2),$AA68,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="P69" s="23">
@@ -8272,6 +8812,14 @@
         <f>IF($A69="","",IF(OR(Q69="",Q69=0),"",(Q69-T69)/Q69))</f>
         <v/>
       </c>
+      <c r="AA69" s="25">
+        <f>IF($A69="","",IF(T69="","",T69+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB69" s="25">
+        <f>IF($A69="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F69='汇总与优先级'!$B$2),$AA69,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="P70" s="23">
@@ -8314,6 +8862,14 @@
         <f>IF($A70="","",IF(OR(Q70="",Q70=0),"",(Q70-T70)/Q70))</f>
         <v/>
       </c>
+      <c r="AA70" s="25">
+        <f>IF($A70="","",IF(T70="","",T70+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB70" s="25">
+        <f>IF($A70="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F70='汇总与优先级'!$B$2),$AA70,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="P71" s="23">
@@ -8356,6 +8912,14 @@
         <f>IF($A71="","",IF(OR(Q71="",Q71=0),"",(Q71-T71)/Q71))</f>
         <v/>
       </c>
+      <c r="AA71" s="25">
+        <f>IF($A71="","",IF(T71="","",T71+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB71" s="25">
+        <f>IF($A71="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F71='汇总与优先级'!$B$2),$AA71,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="P72" s="23">
@@ -8398,6 +8962,14 @@
         <f>IF($A72="","",IF(OR(Q72="",Q72=0),"",(Q72-T72)/Q72))</f>
         <v/>
       </c>
+      <c r="AA72" s="25">
+        <f>IF($A72="","",IF(T72="","",T72+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB72" s="25">
+        <f>IF($A72="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F72='汇总与优先级'!$B$2),$AA72,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="P73" s="23">
@@ -8440,6 +9012,14 @@
         <f>IF($A73="","",IF(OR(Q73="",Q73=0),"",(Q73-T73)/Q73))</f>
         <v/>
       </c>
+      <c r="AA73" s="25">
+        <f>IF($A73="","",IF(T73="","",T73+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB73" s="25">
+        <f>IF($A73="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F73='汇总与优先级'!$B$2),$AA73,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="P74" s="23">
@@ -8482,6 +9062,14 @@
         <f>IF($A74="","",IF(OR(Q74="",Q74=0),"",(Q74-T74)/Q74))</f>
         <v/>
       </c>
+      <c r="AA74" s="25">
+        <f>IF($A74="","",IF(T74="","",T74+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB74" s="25">
+        <f>IF($A74="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F74='汇总与优先级'!$B$2),$AA74,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="P75" s="23">
@@ -8524,6 +9112,14 @@
         <f>IF($A75="","",IF(OR(Q75="",Q75=0),"",(Q75-T75)/Q75))</f>
         <v/>
       </c>
+      <c r="AA75" s="25">
+        <f>IF($A75="","",IF(T75="","",T75+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB75" s="25">
+        <f>IF($A75="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F75='汇总与优先级'!$B$2),$AA75,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="P76" s="23">
@@ -8566,6 +9162,14 @@
         <f>IF($A76="","",IF(OR(Q76="",Q76=0),"",(Q76-T76)/Q76))</f>
         <v/>
       </c>
+      <c r="AA76" s="25">
+        <f>IF($A76="","",IF(T76="","",T76+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB76" s="25">
+        <f>IF($A76="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F76='汇总与优先级'!$B$2),$AA76,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="P77" s="23">
@@ -8608,6 +9212,14 @@
         <f>IF($A77="","",IF(OR(Q77="",Q77=0),"",(Q77-T77)/Q77))</f>
         <v/>
       </c>
+      <c r="AA77" s="25">
+        <f>IF($A77="","",IF(T77="","",T77+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB77" s="25">
+        <f>IF($A77="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F77='汇总与优先级'!$B$2),$AA77,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="P78" s="23">
@@ -8650,6 +9262,14 @@
         <f>IF($A78="","",IF(OR(Q78="",Q78=0),"",(Q78-T78)/Q78))</f>
         <v/>
       </c>
+      <c r="AA78" s="25">
+        <f>IF($A78="","",IF(T78="","",T78+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB78" s="25">
+        <f>IF($A78="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F78='汇总与优先级'!$B$2),$AA78,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="P79" s="23">
@@ -8692,6 +9312,14 @@
         <f>IF($A79="","",IF(OR(Q79="",Q79=0),"",(Q79-T79)/Q79))</f>
         <v/>
       </c>
+      <c r="AA79" s="25">
+        <f>IF($A79="","",IF(T79="","",T79+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB79" s="25">
+        <f>IF($A79="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F79='汇总与优先级'!$B$2),$AA79,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="P80" s="23">
@@ -8734,6 +9362,14 @@
         <f>IF($A80="","",IF(OR(Q80="",Q80=0),"",(Q80-T80)/Q80))</f>
         <v/>
       </c>
+      <c r="AA80" s="25">
+        <f>IF($A80="","",IF(T80="","",T80+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB80" s="25">
+        <f>IF($A80="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F80='汇总与优先级'!$B$2),$AA80,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="P81" s="23">
@@ -8776,6 +9412,14 @@
         <f>IF($A81="","",IF(OR(Q81="",Q81=0),"",(Q81-T81)/Q81))</f>
         <v/>
       </c>
+      <c r="AA81" s="25">
+        <f>IF($A81="","",IF(T81="","",T81+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB81" s="25">
+        <f>IF($A81="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F81='汇总与优先级'!$B$2),$AA81,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="P82" s="23">
@@ -8818,6 +9462,14 @@
         <f>IF($A82="","",IF(OR(Q82="",Q82=0),"",(Q82-T82)/Q82))</f>
         <v/>
       </c>
+      <c r="AA82" s="25">
+        <f>IF($A82="","",IF(T82="","",T82+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB82" s="25">
+        <f>IF($A82="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F82='汇总与优先级'!$B$2),$AA82,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="P83" s="23">
@@ -8860,6 +9512,14 @@
         <f>IF($A83="","",IF(OR(Q83="",Q83=0),"",(Q83-T83)/Q83))</f>
         <v/>
       </c>
+      <c r="AA83" s="25">
+        <f>IF($A83="","",IF(T83="","",T83+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB83" s="25">
+        <f>IF($A83="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F83='汇总与优先级'!$B$2),$AA83,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="P84" s="23">
@@ -8902,6 +9562,14 @@
         <f>IF($A84="","",IF(OR(Q84="",Q84=0),"",(Q84-T84)/Q84))</f>
         <v/>
       </c>
+      <c r="AA84" s="25">
+        <f>IF($A84="","",IF(T84="","",T84+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB84" s="25">
+        <f>IF($A84="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F84='汇总与优先级'!$B$2),$AA84,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="P85" s="23">
@@ -8944,6 +9612,14 @@
         <f>IF($A85="","",IF(OR(Q85="",Q85=0),"",(Q85-T85)/Q85))</f>
         <v/>
       </c>
+      <c r="AA85" s="25">
+        <f>IF($A85="","",IF(T85="","",T85+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB85" s="25">
+        <f>IF($A85="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F85='汇总与优先级'!$B$2),$AA85,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="P86" s="23">
@@ -8986,6 +9662,14 @@
         <f>IF($A86="","",IF(OR(Q86="",Q86=0),"",(Q86-T86)/Q86))</f>
         <v/>
       </c>
+      <c r="AA86" s="25">
+        <f>IF($A86="","",IF(T86="","",T86+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB86" s="25">
+        <f>IF($A86="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F86='汇总与优先级'!$B$2),$AA86,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="P87" s="23">
@@ -9028,6 +9712,14 @@
         <f>IF($A87="","",IF(OR(Q87="",Q87=0),"",(Q87-T87)/Q87))</f>
         <v/>
       </c>
+      <c r="AA87" s="25">
+        <f>IF($A87="","",IF(T87="","",T87+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB87" s="25">
+        <f>IF($A87="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F87='汇总与优先级'!$B$2),$AA87,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="P88" s="23">
@@ -9070,6 +9762,14 @@
         <f>IF($A88="","",IF(OR(Q88="",Q88=0),"",(Q88-T88)/Q88))</f>
         <v/>
       </c>
+      <c r="AA88" s="25">
+        <f>IF($A88="","",IF(T88="","",T88+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB88" s="25">
+        <f>IF($A88="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F88='汇总与优先级'!$B$2),$AA88,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="P89" s="23">
@@ -9112,6 +9812,14 @@
         <f>IF($A89="","",IF(OR(Q89="",Q89=0),"",(Q89-T89)/Q89))</f>
         <v/>
       </c>
+      <c r="AA89" s="25">
+        <f>IF($A89="","",IF(T89="","",T89+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB89" s="25">
+        <f>IF($A89="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F89='汇总与优先级'!$B$2),$AA89,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="P90" s="23">
@@ -9154,6 +9862,14 @@
         <f>IF($A90="","",IF(OR(Q90="",Q90=0),"",(Q90-T90)/Q90))</f>
         <v/>
       </c>
+      <c r="AA90" s="25">
+        <f>IF($A90="","",IF(T90="","",T90+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB90" s="25">
+        <f>IF($A90="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F90='汇总与优先级'!$B$2),$AA90,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="P91" s="23">
@@ -9196,6 +9912,14 @@
         <f>IF($A91="","",IF(OR(Q91="",Q91=0),"",(Q91-T91)/Q91))</f>
         <v/>
       </c>
+      <c r="AA91" s="25">
+        <f>IF($A91="","",IF(T91="","",T91+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB91" s="25">
+        <f>IF($A91="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F91='汇总与优先级'!$B$2),$AA91,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="P92" s="23">
@@ -9238,6 +9962,14 @@
         <f>IF($A92="","",IF(OR(Q92="",Q92=0),"",(Q92-T92)/Q92))</f>
         <v/>
       </c>
+      <c r="AA92" s="25">
+        <f>IF($A92="","",IF(T92="","",T92+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB92" s="25">
+        <f>IF($A92="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F92='汇总与优先级'!$B$2),$AA92,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="P93" s="23">
@@ -9280,6 +10012,14 @@
         <f>IF($A93="","",IF(OR(Q93="",Q93=0),"",(Q93-T93)/Q93))</f>
         <v/>
       </c>
+      <c r="AA93" s="25">
+        <f>IF($A93="","",IF(T93="","",T93+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB93" s="25">
+        <f>IF($A93="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F93='汇总与优先级'!$B$2),$AA93,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="P94" s="23">
@@ -9322,6 +10062,14 @@
         <f>IF($A94="","",IF(OR(Q94="",Q94=0),"",(Q94-T94)/Q94))</f>
         <v/>
       </c>
+      <c r="AA94" s="25">
+        <f>IF($A94="","",IF(T94="","",T94+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB94" s="25">
+        <f>IF($A94="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F94='汇总与优先级'!$B$2),$AA94,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="P95" s="23">
@@ -9364,6 +10112,14 @@
         <f>IF($A95="","",IF(OR(Q95="",Q95=0),"",(Q95-T95)/Q95))</f>
         <v/>
       </c>
+      <c r="AA95" s="25">
+        <f>IF($A95="","",IF(T95="","",T95+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB95" s="25">
+        <f>IF($A95="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F95='汇总与优先级'!$B$2),$AA95,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="P96" s="23">
@@ -9406,6 +10162,14 @@
         <f>IF($A96="","",IF(OR(Q96="",Q96=0),"",(Q96-T96)/Q96))</f>
         <v/>
       </c>
+      <c r="AA96" s="25">
+        <f>IF($A96="","",IF(T96="","",T96+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB96" s="25">
+        <f>IF($A96="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F96='汇总与优先级'!$B$2),$AA96,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="P97" s="23">
@@ -9448,6 +10212,14 @@
         <f>IF($A97="","",IF(OR(Q97="",Q97=0),"",(Q97-T97)/Q97))</f>
         <v/>
       </c>
+      <c r="AA97" s="25">
+        <f>IF($A97="","",IF(T97="","",T97+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB97" s="25">
+        <f>IF($A97="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F97='汇总与优先级'!$B$2),$AA97,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="P98" s="23">
@@ -9490,6 +10262,14 @@
         <f>IF($A98="","",IF(OR(Q98="",Q98=0),"",(Q98-T98)/Q98))</f>
         <v/>
       </c>
+      <c r="AA98" s="25">
+        <f>IF($A98="","",IF(T98="","",T98+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB98" s="25">
+        <f>IF($A98="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F98='汇总与优先级'!$B$2),$AA98,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="P99" s="23">
@@ -9532,6 +10312,14 @@
         <f>IF($A99="","",IF(OR(Q99="",Q99=0),"",(Q99-T99)/Q99))</f>
         <v/>
       </c>
+      <c r="AA99" s="25">
+        <f>IF($A99="","",IF(T99="","",T99+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB99" s="25">
+        <f>IF($A99="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F99='汇总与优先级'!$B$2),$AA99,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="P100" s="23">
@@ -9574,6 +10362,14 @@
         <f>IF($A100="","",IF(OR(Q100="",Q100=0),"",(Q100-T100)/Q100))</f>
         <v/>
       </c>
+      <c r="AA100" s="25">
+        <f>IF($A100="","",IF(T100="","",T100+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB100" s="25">
+        <f>IF($A100="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F100='汇总与优先级'!$B$2),$AA100,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="P101" s="23">
@@ -9616,6 +10412,14 @@
         <f>IF($A101="","",IF(OR(Q101="",Q101=0),"",(Q101-T101)/Q101))</f>
         <v/>
       </c>
+      <c r="AA101" s="25">
+        <f>IF($A101="","",IF(T101="","",T101+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB101" s="25">
+        <f>IF($A101="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F101='汇总与优先级'!$B$2),$AA101,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="P102" s="23">
@@ -9658,6 +10462,14 @@
         <f>IF($A102="","",IF(OR(Q102="",Q102=0),"",(Q102-T102)/Q102))</f>
         <v/>
       </c>
+      <c r="AA102" s="25">
+        <f>IF($A102="","",IF(T102="","",T102+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB102" s="25">
+        <f>IF($A102="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F102='汇总与优先级'!$B$2),$AA102,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="P103" s="23">
@@ -9700,6 +10512,14 @@
         <f>IF($A103="","",IF(OR(Q103="",Q103=0),"",(Q103-T103)/Q103))</f>
         <v/>
       </c>
+      <c r="AA103" s="25">
+        <f>IF($A103="","",IF(T103="","",T103+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB103" s="25">
+        <f>IF($A103="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F103='汇总与优先级'!$B$2),$AA103,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="P104" s="23">
@@ -9742,6 +10562,14 @@
         <f>IF($A104="","",IF(OR(Q104="",Q104=0),"",(Q104-T104)/Q104))</f>
         <v/>
       </c>
+      <c r="AA104" s="25">
+        <f>IF($A104="","",IF(T104="","",T104+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB104" s="25">
+        <f>IF($A104="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F104='汇总与优先级'!$B$2),$AA104,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="P105" s="23">
@@ -9784,6 +10612,14 @@
         <f>IF($A105="","",IF(OR(Q105="",Q105=0),"",(Q105-T105)/Q105))</f>
         <v/>
       </c>
+      <c r="AA105" s="25">
+        <f>IF($A105="","",IF(T105="","",T105+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB105" s="25">
+        <f>IF($A105="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F105='汇总与优先级'!$B$2),$AA105,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="P106" s="23">
@@ -9826,6 +10662,14 @@
         <f>IF($A106="","",IF(OR(Q106="",Q106=0),"",(Q106-T106)/Q106))</f>
         <v/>
       </c>
+      <c r="AA106" s="25">
+        <f>IF($A106="","",IF(T106="","",T106+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB106" s="25">
+        <f>IF($A106="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F106='汇总与优先级'!$B$2),$AA106,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="P107" s="23">
@@ -9868,6 +10712,14 @@
         <f>IF($A107="","",IF(OR(Q107="",Q107=0),"",(Q107-T107)/Q107))</f>
         <v/>
       </c>
+      <c r="AA107" s="25">
+        <f>IF($A107="","",IF(T107="","",T107+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB107" s="25">
+        <f>IF($A107="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F107='汇总与优先级'!$B$2),$AA107,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="P108" s="23">
@@ -9910,6 +10762,14 @@
         <f>IF($A108="","",IF(OR(Q108="",Q108=0),"",(Q108-T108)/Q108))</f>
         <v/>
       </c>
+      <c r="AA108" s="25">
+        <f>IF($A108="","",IF(T108="","",T108+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB108" s="25">
+        <f>IF($A108="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F108='汇总与优先级'!$B$2),$AA108,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="P109" s="23">
@@ -9952,6 +10812,14 @@
         <f>IF($A109="","",IF(OR(Q109="",Q109=0),"",(Q109-T109)/Q109))</f>
         <v/>
       </c>
+      <c r="AA109" s="25">
+        <f>IF($A109="","",IF(T109="","",T109+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB109" s="25">
+        <f>IF($A109="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F109='汇总与优先级'!$B$2),$AA109,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="P110" s="23">
@@ -9994,6 +10862,14 @@
         <f>IF($A110="","",IF(OR(Q110="",Q110=0),"",(Q110-T110)/Q110))</f>
         <v/>
       </c>
+      <c r="AA110" s="25">
+        <f>IF($A110="","",IF(T110="","",T110+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB110" s="25">
+        <f>IF($A110="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F110='汇总与优先级'!$B$2),$AA110,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="P111" s="23">
@@ -10036,6 +10912,14 @@
         <f>IF($A111="","",IF(OR(Q111="",Q111=0),"",(Q111-T111)/Q111))</f>
         <v/>
       </c>
+      <c r="AA111" s="25">
+        <f>IF($A111="","",IF(T111="","",T111+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB111" s="25">
+        <f>IF($A111="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F111='汇总与优先级'!$B$2),$AA111,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="P112" s="23">
@@ -10078,6 +10962,14 @@
         <f>IF($A112="","",IF(OR(Q112="",Q112=0),"",(Q112-T112)/Q112))</f>
         <v/>
       </c>
+      <c r="AA112" s="25">
+        <f>IF($A112="","",IF(T112="","",T112+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB112" s="25">
+        <f>IF($A112="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F112='汇总与优先级'!$B$2),$AA112,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="P113" s="23">
@@ -10120,6 +11012,14 @@
         <f>IF($A113="","",IF(OR(Q113="",Q113=0),"",(Q113-T113)/Q113))</f>
         <v/>
       </c>
+      <c r="AA113" s="25">
+        <f>IF($A113="","",IF(T113="","",T113+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB113" s="25">
+        <f>IF($A113="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F113='汇总与优先级'!$B$2),$AA113,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="P114" s="23">
@@ -10162,6 +11062,14 @@
         <f>IF($A114="","",IF(OR(Q114="",Q114=0),"",(Q114-T114)/Q114))</f>
         <v/>
       </c>
+      <c r="AA114" s="25">
+        <f>IF($A114="","",IF(T114="","",T114+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB114" s="25">
+        <f>IF($A114="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F114='汇总与优先级'!$B$2),$AA114,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="P115" s="23">
@@ -10204,6 +11112,14 @@
         <f>IF($A115="","",IF(OR(Q115="",Q115=0),"",(Q115-T115)/Q115))</f>
         <v/>
       </c>
+      <c r="AA115" s="25">
+        <f>IF($A115="","",IF(T115="","",T115+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB115" s="25">
+        <f>IF($A115="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F115='汇总与优先级'!$B$2),$AA115,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="P116" s="23">
@@ -10246,6 +11162,14 @@
         <f>IF($A116="","",IF(OR(Q116="",Q116=0),"",(Q116-T116)/Q116))</f>
         <v/>
       </c>
+      <c r="AA116" s="25">
+        <f>IF($A116="","",IF(T116="","",T116+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB116" s="25">
+        <f>IF($A116="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F116='汇总与优先级'!$B$2),$AA116,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="P117" s="23">
@@ -10288,6 +11212,14 @@
         <f>IF($A117="","",IF(OR(Q117="",Q117=0),"",(Q117-T117)/Q117))</f>
         <v/>
       </c>
+      <c r="AA117" s="25">
+        <f>IF($A117="","",IF(T117="","",T117+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB117" s="25">
+        <f>IF($A117="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F117='汇总与优先级'!$B$2),$AA117,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="P118" s="23">
@@ -10330,6 +11262,14 @@
         <f>IF($A118="","",IF(OR(Q118="",Q118=0),"",(Q118-T118)/Q118))</f>
         <v/>
       </c>
+      <c r="AA118" s="25">
+        <f>IF($A118="","",IF(T118="","",T118+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB118" s="25">
+        <f>IF($A118="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F118='汇总与优先级'!$B$2),$AA118,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="P119" s="23">
@@ -10372,6 +11312,14 @@
         <f>IF($A119="","",IF(OR(Q119="",Q119=0),"",(Q119-T119)/Q119))</f>
         <v/>
       </c>
+      <c r="AA119" s="25">
+        <f>IF($A119="","",IF(T119="","",T119+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB119" s="25">
+        <f>IF($A119="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F119='汇总与优先级'!$B$2),$AA119,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="P120" s="23">
@@ -10414,6 +11362,14 @@
         <f>IF($A120="","",IF(OR(Q120="",Q120=0),"",(Q120-T120)/Q120))</f>
         <v/>
       </c>
+      <c r="AA120" s="25">
+        <f>IF($A120="","",IF(T120="","",T120+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB120" s="25">
+        <f>IF($A120="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F120='汇总与优先级'!$B$2),$AA120,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="P121" s="23">
@@ -10456,6 +11412,14 @@
         <f>IF($A121="","",IF(OR(Q121="",Q121=0),"",(Q121-T121)/Q121))</f>
         <v/>
       </c>
+      <c r="AA121" s="25">
+        <f>IF($A121="","",IF(T121="","",T121+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB121" s="25">
+        <f>IF($A121="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F121='汇总与优先级'!$B$2),$AA121,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="P122" s="23">
@@ -10498,6 +11462,14 @@
         <f>IF($A122="","",IF(OR(Q122="",Q122=0),"",(Q122-T122)/Q122))</f>
         <v/>
       </c>
+      <c r="AA122" s="25">
+        <f>IF($A122="","",IF(T122="","",T122+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB122" s="25">
+        <f>IF($A122="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F122='汇总与优先级'!$B$2),$AA122,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="P123" s="23">
@@ -10540,6 +11512,14 @@
         <f>IF($A123="","",IF(OR(Q123="",Q123=0),"",(Q123-T123)/Q123))</f>
         <v/>
       </c>
+      <c r="AA123" s="25">
+        <f>IF($A123="","",IF(T123="","",T123+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB123" s="25">
+        <f>IF($A123="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F123='汇总与优先级'!$B$2),$AA123,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="P124" s="23">
@@ -10582,6 +11562,14 @@
         <f>IF($A124="","",IF(OR(Q124="",Q124=0),"",(Q124-T124)/Q124))</f>
         <v/>
       </c>
+      <c r="AA124" s="25">
+        <f>IF($A124="","",IF(T124="","",T124+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB124" s="25">
+        <f>IF($A124="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F124='汇总与优先级'!$B$2),$AA124,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="P125" s="23">
@@ -10624,6 +11612,14 @@
         <f>IF($A125="","",IF(OR(Q125="",Q125=0),"",(Q125-T125)/Q125))</f>
         <v/>
       </c>
+      <c r="AA125" s="25">
+        <f>IF($A125="","",IF(T125="","",T125+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB125" s="25">
+        <f>IF($A125="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F125='汇总与优先级'!$B$2),$AA125,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="P126" s="23">
@@ -10666,6 +11662,14 @@
         <f>IF($A126="","",IF(OR(Q126="",Q126=0),"",(Q126-T126)/Q126))</f>
         <v/>
       </c>
+      <c r="AA126" s="25">
+        <f>IF($A126="","",IF(T126="","",T126+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB126" s="25">
+        <f>IF($A126="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F126='汇总与优先级'!$B$2),$AA126,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="P127" s="23">
@@ -10708,6 +11712,14 @@
         <f>IF($A127="","",IF(OR(Q127="",Q127=0),"",(Q127-T127)/Q127))</f>
         <v/>
       </c>
+      <c r="AA127" s="25">
+        <f>IF($A127="","",IF(T127="","",T127+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB127" s="25">
+        <f>IF($A127="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F127='汇总与优先级'!$B$2),$AA127,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="P128" s="23">
@@ -10750,6 +11762,14 @@
         <f>IF($A128="","",IF(OR(Q128="",Q128=0),"",(Q128-T128)/Q128))</f>
         <v/>
       </c>
+      <c r="AA128" s="25">
+        <f>IF($A128="","",IF(T128="","",T128+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB128" s="25">
+        <f>IF($A128="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F128='汇总与优先级'!$B$2),$AA128,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="P129" s="23">
@@ -10792,6 +11812,14 @@
         <f>IF($A129="","",IF(OR(Q129="",Q129=0),"",(Q129-T129)/Q129))</f>
         <v/>
       </c>
+      <c r="AA129" s="25">
+        <f>IF($A129="","",IF(T129="","",T129+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB129" s="25">
+        <f>IF($A129="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F129='汇总与优先级'!$B$2),$AA129,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="P130" s="23">
@@ -10834,6 +11862,14 @@
         <f>IF($A130="","",IF(OR(Q130="",Q130=0),"",(Q130-T130)/Q130))</f>
         <v/>
       </c>
+      <c r="AA130" s="25">
+        <f>IF($A130="","",IF(T130="","",T130+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB130" s="25">
+        <f>IF($A130="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F130='汇总与优先级'!$B$2),$AA130,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="P131" s="23">
@@ -10876,6 +11912,14 @@
         <f>IF($A131="","",IF(OR(Q131="",Q131=0),"",(Q131-T131)/Q131))</f>
         <v/>
       </c>
+      <c r="AA131" s="25">
+        <f>IF($A131="","",IF(T131="","",T131+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB131" s="25">
+        <f>IF($A131="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F131='汇总与优先级'!$B$2),$AA131,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="P132" s="23">
@@ -10918,6 +11962,14 @@
         <f>IF($A132="","",IF(OR(Q132="",Q132=0),"",(Q132-T132)/Q132))</f>
         <v/>
       </c>
+      <c r="AA132" s="25">
+        <f>IF($A132="","",IF(T132="","",T132+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB132" s="25">
+        <f>IF($A132="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F132='汇总与优先级'!$B$2),$AA132,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="P133" s="23">
@@ -10960,6 +12012,14 @@
         <f>IF($A133="","",IF(OR(Q133="",Q133=0),"",(Q133-T133)/Q133))</f>
         <v/>
       </c>
+      <c r="AA133" s="25">
+        <f>IF($A133="","",IF(T133="","",T133+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB133" s="25">
+        <f>IF($A133="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F133='汇总与优先级'!$B$2),$AA133,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="P134" s="23">
@@ -11002,6 +12062,14 @@
         <f>IF($A134="","",IF(OR(Q134="",Q134=0),"",(Q134-T134)/Q134))</f>
         <v/>
       </c>
+      <c r="AA134" s="25">
+        <f>IF($A134="","",IF(T134="","",T134+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB134" s="25">
+        <f>IF($A134="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F134='汇总与优先级'!$B$2),$AA134,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="P135" s="23">
@@ -11044,6 +12112,14 @@
         <f>IF($A135="","",IF(OR(Q135="",Q135=0),"",(Q135-T135)/Q135))</f>
         <v/>
       </c>
+      <c r="AA135" s="25">
+        <f>IF($A135="","",IF(T135="","",T135+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB135" s="25">
+        <f>IF($A135="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F135='汇总与优先级'!$B$2),$AA135,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="P136" s="23">
@@ -11086,6 +12162,14 @@
         <f>IF($A136="","",IF(OR(Q136="",Q136=0),"",(Q136-T136)/Q136))</f>
         <v/>
       </c>
+      <c r="AA136" s="25">
+        <f>IF($A136="","",IF(T136="","",T136+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB136" s="25">
+        <f>IF($A136="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F136='汇总与优先级'!$B$2),$AA136,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="P137" s="23">
@@ -11128,6 +12212,14 @@
         <f>IF($A137="","",IF(OR(Q137="",Q137=0),"",(Q137-T137)/Q137))</f>
         <v/>
       </c>
+      <c r="AA137" s="25">
+        <f>IF($A137="","",IF(T137="","",T137+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB137" s="25">
+        <f>IF($A137="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F137='汇总与优先级'!$B$2),$AA137,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="P138" s="23">
@@ -11170,6 +12262,14 @@
         <f>IF($A138="","",IF(OR(Q138="",Q138=0),"",(Q138-T138)/Q138))</f>
         <v/>
       </c>
+      <c r="AA138" s="25">
+        <f>IF($A138="","",IF(T138="","",T138+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB138" s="25">
+        <f>IF($A138="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F138='汇总与优先级'!$B$2),$AA138,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="P139" s="23">
@@ -11212,6 +12312,14 @@
         <f>IF($A139="","",IF(OR(Q139="",Q139=0),"",(Q139-T139)/Q139))</f>
         <v/>
       </c>
+      <c r="AA139" s="25">
+        <f>IF($A139="","",IF(T139="","",T139+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB139" s="25">
+        <f>IF($A139="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F139='汇总与优先级'!$B$2),$AA139,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="P140" s="23">
@@ -11254,6 +12362,14 @@
         <f>IF($A140="","",IF(OR(Q140="",Q140=0),"",(Q140-T140)/Q140))</f>
         <v/>
       </c>
+      <c r="AA140" s="25">
+        <f>IF($A140="","",IF(T140="","",T140+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB140" s="25">
+        <f>IF($A140="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F140='汇总与优先级'!$B$2),$AA140,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="P141" s="23">
@@ -11296,6 +12412,14 @@
         <f>IF($A141="","",IF(OR(Q141="",Q141=0),"",(Q141-T141)/Q141))</f>
         <v/>
       </c>
+      <c r="AA141" s="25">
+        <f>IF($A141="","",IF(T141="","",T141+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB141" s="25">
+        <f>IF($A141="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F141='汇总与优先级'!$B$2),$AA141,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="P142" s="23">
@@ -11338,6 +12462,14 @@
         <f>IF($A142="","",IF(OR(Q142="",Q142=0),"",(Q142-T142)/Q142))</f>
         <v/>
       </c>
+      <c r="AA142" s="25">
+        <f>IF($A142="","",IF(T142="","",T142+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB142" s="25">
+        <f>IF($A142="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F142='汇总与优先级'!$B$2),$AA142,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="P143" s="23">
@@ -11380,6 +12512,14 @@
         <f>IF($A143="","",IF(OR(Q143="",Q143=0),"",(Q143-T143)/Q143))</f>
         <v/>
       </c>
+      <c r="AA143" s="25">
+        <f>IF($A143="","",IF(T143="","",T143+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB143" s="25">
+        <f>IF($A143="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F143='汇总与优先级'!$B$2),$AA143,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="P144" s="23">
@@ -11422,6 +12562,14 @@
         <f>IF($A144="","",IF(OR(Q144="",Q144=0),"",(Q144-T144)/Q144))</f>
         <v/>
       </c>
+      <c r="AA144" s="25">
+        <f>IF($A144="","",IF(T144="","",T144+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB144" s="25">
+        <f>IF($A144="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F144='汇总与优先级'!$B$2),$AA144,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="P145" s="23">
@@ -11464,6 +12612,14 @@
         <f>IF($A145="","",IF(OR(Q145="",Q145=0),"",(Q145-T145)/Q145))</f>
         <v/>
       </c>
+      <c r="AA145" s="25">
+        <f>IF($A145="","",IF(T145="","",T145+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB145" s="25">
+        <f>IF($A145="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F145='汇总与优先级'!$B$2),$AA145,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="P146" s="23">
@@ -11506,6 +12662,14 @@
         <f>IF($A146="","",IF(OR(Q146="",Q146=0),"",(Q146-T146)/Q146))</f>
         <v/>
       </c>
+      <c r="AA146" s="25">
+        <f>IF($A146="","",IF(T146="","",T146+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB146" s="25">
+        <f>IF($A146="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F146='汇总与优先级'!$B$2),$AA146,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="P147" s="23">
@@ -11548,6 +12712,14 @@
         <f>IF($A147="","",IF(OR(Q147="",Q147=0),"",(Q147-T147)/Q147))</f>
         <v/>
       </c>
+      <c r="AA147" s="25">
+        <f>IF($A147="","",IF(T147="","",T147+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB147" s="25">
+        <f>IF($A147="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F147='汇总与优先级'!$B$2),$AA147,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="P148" s="23">
@@ -11590,6 +12762,14 @@
         <f>IF($A148="","",IF(OR(Q148="",Q148=0),"",(Q148-T148)/Q148))</f>
         <v/>
       </c>
+      <c r="AA148" s="25">
+        <f>IF($A148="","",IF(T148="","",T148+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB148" s="25">
+        <f>IF($A148="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F148='汇总与优先级'!$B$2),$AA148,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="P149" s="23">
@@ -11632,6 +12812,14 @@
         <f>IF($A149="","",IF(OR(Q149="",Q149=0),"",(Q149-T149)/Q149))</f>
         <v/>
       </c>
+      <c r="AA149" s="25">
+        <f>IF($A149="","",IF(T149="","",T149+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB149" s="25">
+        <f>IF($A149="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F149='汇总与优先级'!$B$2),$AA149,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="P150" s="23">
@@ -11674,6 +12862,14 @@
         <f>IF($A150="","",IF(OR(Q150="",Q150=0),"",(Q150-T150)/Q150))</f>
         <v/>
       </c>
+      <c r="AA150" s="25">
+        <f>IF($A150="","",IF(T150="","",T150+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB150" s="25">
+        <f>IF($A150="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F150='汇总与优先级'!$B$2),$AA150,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="P151" s="23">
@@ -11716,6 +12912,14 @@
         <f>IF($A151="","",IF(OR(Q151="",Q151=0),"",(Q151-T151)/Q151))</f>
         <v/>
       </c>
+      <c r="AA151" s="25">
+        <f>IF($A151="","",IF(T151="","",T151+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB151" s="25">
+        <f>IF($A151="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F151='汇总与优先级'!$B$2),$AA151,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="P152" s="23">
@@ -11758,6 +12962,14 @@
         <f>IF($A152="","",IF(OR(Q152="",Q152=0),"",(Q152-T152)/Q152))</f>
         <v/>
       </c>
+      <c r="AA152" s="25">
+        <f>IF($A152="","",IF(T152="","",T152+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB152" s="25">
+        <f>IF($A152="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F152='汇总与优先级'!$B$2),$AA152,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="P153" s="23">
@@ -11800,6 +13012,14 @@
         <f>IF($A153="","",IF(OR(Q153="",Q153=0),"",(Q153-T153)/Q153))</f>
         <v/>
       </c>
+      <c r="AA153" s="25">
+        <f>IF($A153="","",IF(T153="","",T153+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB153" s="25">
+        <f>IF($A153="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F153='汇总与优先级'!$B$2),$AA153,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="P154" s="23">
@@ -11842,6 +13062,14 @@
         <f>IF($A154="","",IF(OR(Q154="",Q154=0),"",(Q154-T154)/Q154))</f>
         <v/>
       </c>
+      <c r="AA154" s="25">
+        <f>IF($A154="","",IF(T154="","",T154+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB154" s="25">
+        <f>IF($A154="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F154='汇总与优先级'!$B$2),$AA154,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="P155" s="23">
@@ -11884,6 +13112,14 @@
         <f>IF($A155="","",IF(OR(Q155="",Q155=0),"",(Q155-T155)/Q155))</f>
         <v/>
       </c>
+      <c r="AA155" s="25">
+        <f>IF($A155="","",IF(T155="","",T155+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB155" s="25">
+        <f>IF($A155="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F155='汇总与优先级'!$B$2),$AA155,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="P156" s="23">
@@ -11926,6 +13162,14 @@
         <f>IF($A156="","",IF(OR(Q156="",Q156=0),"",(Q156-T156)/Q156))</f>
         <v/>
       </c>
+      <c r="AA156" s="25">
+        <f>IF($A156="","",IF(T156="","",T156+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB156" s="25">
+        <f>IF($A156="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F156='汇总与优先级'!$B$2),$AA156,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="P157" s="23">
@@ -11968,6 +13212,14 @@
         <f>IF($A157="","",IF(OR(Q157="",Q157=0),"",(Q157-T157)/Q157))</f>
         <v/>
       </c>
+      <c r="AA157" s="25">
+        <f>IF($A157="","",IF(T157="","",T157+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB157" s="25">
+        <f>IF($A157="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F157='汇总与优先级'!$B$2),$AA157,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="P158" s="23">
@@ -12010,6 +13262,14 @@
         <f>IF($A158="","",IF(OR(Q158="",Q158=0),"",(Q158-T158)/Q158))</f>
         <v/>
       </c>
+      <c r="AA158" s="25">
+        <f>IF($A158="","",IF(T158="","",T158+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB158" s="25">
+        <f>IF($A158="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F158='汇总与优先级'!$B$2),$AA158,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="P159" s="23">
@@ -12052,6 +13312,14 @@
         <f>IF($A159="","",IF(OR(Q159="",Q159=0),"",(Q159-T159)/Q159))</f>
         <v/>
       </c>
+      <c r="AA159" s="25">
+        <f>IF($A159="","",IF(T159="","",T159+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB159" s="25">
+        <f>IF($A159="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F159='汇总与优先级'!$B$2),$AA159,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="P160" s="23">
@@ -12094,6 +13362,14 @@
         <f>IF($A160="","",IF(OR(Q160="",Q160=0),"",(Q160-T160)/Q160))</f>
         <v/>
       </c>
+      <c r="AA160" s="25">
+        <f>IF($A160="","",IF(T160="","",T160+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB160" s="25">
+        <f>IF($A160="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F160='汇总与优先级'!$B$2),$AA160,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="P161" s="23">
@@ -12136,6 +13412,14 @@
         <f>IF($A161="","",IF(OR(Q161="",Q161=0),"",(Q161-T161)/Q161))</f>
         <v/>
       </c>
+      <c r="AA161" s="25">
+        <f>IF($A161="","",IF(T161="","",T161+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB161" s="25">
+        <f>IF($A161="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F161='汇总与优先级'!$B$2),$AA161,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="P162" s="23">
@@ -12178,6 +13462,14 @@
         <f>IF($A162="","",IF(OR(Q162="",Q162=0),"",(Q162-T162)/Q162))</f>
         <v/>
       </c>
+      <c r="AA162" s="25">
+        <f>IF($A162="","",IF(T162="","",T162+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB162" s="25">
+        <f>IF($A162="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F162='汇总与优先级'!$B$2),$AA162,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="P163" s="23">
@@ -12220,6 +13512,14 @@
         <f>IF($A163="","",IF(OR(Q163="",Q163=0),"",(Q163-T163)/Q163))</f>
         <v/>
       </c>
+      <c r="AA163" s="25">
+        <f>IF($A163="","",IF(T163="","",T163+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB163" s="25">
+        <f>IF($A163="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F163='汇总与优先级'!$B$2),$AA163,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="P164" s="23">
@@ -12262,6 +13562,14 @@
         <f>IF($A164="","",IF(OR(Q164="",Q164=0),"",(Q164-T164)/Q164))</f>
         <v/>
       </c>
+      <c r="AA164" s="25">
+        <f>IF($A164="","",IF(T164="","",T164+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB164" s="25">
+        <f>IF($A164="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F164='汇总与优先级'!$B$2),$AA164,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="P165" s="23">
@@ -12304,6 +13612,14 @@
         <f>IF($A165="","",IF(OR(Q165="",Q165=0),"",(Q165-T165)/Q165))</f>
         <v/>
       </c>
+      <c r="AA165" s="25">
+        <f>IF($A165="","",IF(T165="","",T165+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB165" s="25">
+        <f>IF($A165="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F165='汇总与优先级'!$B$2),$AA165,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="P166" s="23">
@@ -12346,6 +13662,14 @@
         <f>IF($A166="","",IF(OR(Q166="",Q166=0),"",(Q166-T166)/Q166))</f>
         <v/>
       </c>
+      <c r="AA166" s="25">
+        <f>IF($A166="","",IF(T166="","",T166+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB166" s="25">
+        <f>IF($A166="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F166='汇总与优先级'!$B$2),$AA166,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="P167" s="23">
@@ -12388,6 +13712,14 @@
         <f>IF($A167="","",IF(OR(Q167="",Q167=0),"",(Q167-T167)/Q167))</f>
         <v/>
       </c>
+      <c r="AA167" s="25">
+        <f>IF($A167="","",IF(T167="","",T167+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB167" s="25">
+        <f>IF($A167="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F167='汇总与优先级'!$B$2),$AA167,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="P168" s="23">
@@ -12430,6 +13762,14 @@
         <f>IF($A168="","",IF(OR(Q168="",Q168=0),"",(Q168-T168)/Q168))</f>
         <v/>
       </c>
+      <c r="AA168" s="25">
+        <f>IF($A168="","",IF(T168="","",T168+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB168" s="25">
+        <f>IF($A168="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F168='汇总与优先级'!$B$2),$AA168,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="P169" s="23">
@@ -12472,6 +13812,14 @@
         <f>IF($A169="","",IF(OR(Q169="",Q169=0),"",(Q169-T169)/Q169))</f>
         <v/>
       </c>
+      <c r="AA169" s="25">
+        <f>IF($A169="","",IF(T169="","",T169+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB169" s="25">
+        <f>IF($A169="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F169='汇总与优先级'!$B$2),$AA169,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="P170" s="23">
@@ -12514,6 +13862,14 @@
         <f>IF($A170="","",IF(OR(Q170="",Q170=0),"",(Q170-T170)/Q170))</f>
         <v/>
       </c>
+      <c r="AA170" s="25">
+        <f>IF($A170="","",IF(T170="","",T170+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB170" s="25">
+        <f>IF($A170="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F170='汇总与优先级'!$B$2),$AA170,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="P171" s="23">
@@ -12556,6 +13912,14 @@
         <f>IF($A171="","",IF(OR(Q171="",Q171=0),"",(Q171-T171)/Q171))</f>
         <v/>
       </c>
+      <c r="AA171" s="25">
+        <f>IF($A171="","",IF(T171="","",T171+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB171" s="25">
+        <f>IF($A171="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F171='汇总与优先级'!$B$2),$AA171,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="P172" s="23">
@@ -12598,6 +13962,14 @@
         <f>IF($A172="","",IF(OR(Q172="",Q172=0),"",(Q172-T172)/Q172))</f>
         <v/>
       </c>
+      <c r="AA172" s="25">
+        <f>IF($A172="","",IF(T172="","",T172+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB172" s="25">
+        <f>IF($A172="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F172='汇总与优先级'!$B$2),$AA172,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="P173" s="23">
@@ -12640,6 +14012,14 @@
         <f>IF($A173="","",IF(OR(Q173="",Q173=0),"",(Q173-T173)/Q173))</f>
         <v/>
       </c>
+      <c r="AA173" s="25">
+        <f>IF($A173="","",IF(T173="","",T173+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB173" s="25">
+        <f>IF($A173="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F173='汇总与优先级'!$B$2),$AA173,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="P174" s="23">
@@ -12682,6 +14062,14 @@
         <f>IF($A174="","",IF(OR(Q174="",Q174=0),"",(Q174-T174)/Q174))</f>
         <v/>
       </c>
+      <c r="AA174" s="25">
+        <f>IF($A174="","",IF(T174="","",T174+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB174" s="25">
+        <f>IF($A174="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F174='汇总与优先级'!$B$2),$AA174,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="P175" s="23">
@@ -12724,6 +14112,14 @@
         <f>IF($A175="","",IF(OR(Q175="",Q175=0),"",(Q175-T175)/Q175))</f>
         <v/>
       </c>
+      <c r="AA175" s="25">
+        <f>IF($A175="","",IF(T175="","",T175+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB175" s="25">
+        <f>IF($A175="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F175='汇总与优先级'!$B$2),$AA175,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="P176" s="23">
@@ -12766,6 +14162,14 @@
         <f>IF($A176="","",IF(OR(Q176="",Q176=0),"",(Q176-T176)/Q176))</f>
         <v/>
       </c>
+      <c r="AA176" s="25">
+        <f>IF($A176="","",IF(T176="","",T176+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB176" s="25">
+        <f>IF($A176="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F176='汇总与优先级'!$B$2),$AA176,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="P177" s="23">
@@ -12808,6 +14212,14 @@
         <f>IF($A177="","",IF(OR(Q177="",Q177=0),"",(Q177-T177)/Q177))</f>
         <v/>
       </c>
+      <c r="AA177" s="25">
+        <f>IF($A177="","",IF(T177="","",T177+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB177" s="25">
+        <f>IF($A177="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F177='汇总与优先级'!$B$2),$AA177,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="P178" s="23">
@@ -12850,6 +14262,14 @@
         <f>IF($A178="","",IF(OR(Q178="",Q178=0),"",(Q178-T178)/Q178))</f>
         <v/>
       </c>
+      <c r="AA178" s="25">
+        <f>IF($A178="","",IF(T178="","",T178+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB178" s="25">
+        <f>IF($A178="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F178='汇总与优先级'!$B$2),$AA178,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="P179" s="23">
@@ -12892,6 +14312,14 @@
         <f>IF($A179="","",IF(OR(Q179="",Q179=0),"",(Q179-T179)/Q179))</f>
         <v/>
       </c>
+      <c r="AA179" s="25">
+        <f>IF($A179="","",IF(T179="","",T179+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB179" s="25">
+        <f>IF($A179="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F179='汇总与优先级'!$B$2),$AA179,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="P180" s="23">
@@ -12934,6 +14362,14 @@
         <f>IF($A180="","",IF(OR(Q180="",Q180=0),"",(Q180-T180)/Q180))</f>
         <v/>
       </c>
+      <c r="AA180" s="25">
+        <f>IF($A180="","",IF(T180="","",T180+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB180" s="25">
+        <f>IF($A180="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F180='汇总与优先级'!$B$2),$AA180,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="P181" s="23">
@@ -12976,6 +14412,14 @@
         <f>IF($A181="","",IF(OR(Q181="",Q181=0),"",(Q181-T181)/Q181))</f>
         <v/>
       </c>
+      <c r="AA181" s="25">
+        <f>IF($A181="","",IF(T181="","",T181+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB181" s="25">
+        <f>IF($A181="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F181='汇总与优先级'!$B$2),$AA181,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="P182" s="23">
@@ -13018,6 +14462,14 @@
         <f>IF($A182="","",IF(OR(Q182="",Q182=0),"",(Q182-T182)/Q182))</f>
         <v/>
       </c>
+      <c r="AA182" s="25">
+        <f>IF($A182="","",IF(T182="","",T182+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB182" s="25">
+        <f>IF($A182="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F182='汇总与优先级'!$B$2),$AA182,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="P183" s="23">
@@ -13060,6 +14512,14 @@
         <f>IF($A183="","",IF(OR(Q183="",Q183=0),"",(Q183-T183)/Q183))</f>
         <v/>
       </c>
+      <c r="AA183" s="25">
+        <f>IF($A183="","",IF(T183="","",T183+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB183" s="25">
+        <f>IF($A183="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F183='汇总与优先级'!$B$2),$AA183,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="P184" s="23">
@@ -13102,6 +14562,14 @@
         <f>IF($A184="","",IF(OR(Q184="",Q184=0),"",(Q184-T184)/Q184))</f>
         <v/>
       </c>
+      <c r="AA184" s="25">
+        <f>IF($A184="","",IF(T184="","",T184+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB184" s="25">
+        <f>IF($A184="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F184='汇总与优先级'!$B$2),$AA184,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="P185" s="23">
@@ -13144,6 +14612,14 @@
         <f>IF($A185="","",IF(OR(Q185="",Q185=0),"",(Q185-T185)/Q185))</f>
         <v/>
       </c>
+      <c r="AA185" s="25">
+        <f>IF($A185="","",IF(T185="","",T185+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB185" s="25">
+        <f>IF($A185="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F185='汇总与优先级'!$B$2),$AA185,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="P186" s="23">
@@ -13186,6 +14662,14 @@
         <f>IF($A186="","",IF(OR(Q186="",Q186=0),"",(Q186-T186)/Q186))</f>
         <v/>
       </c>
+      <c r="AA186" s="25">
+        <f>IF($A186="","",IF(T186="","",T186+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB186" s="25">
+        <f>IF($A186="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F186='汇总与优先级'!$B$2),$AA186,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="P187" s="23">
@@ -13228,6 +14712,14 @@
         <f>IF($A187="","",IF(OR(Q187="",Q187=0),"",(Q187-T187)/Q187))</f>
         <v/>
       </c>
+      <c r="AA187" s="25">
+        <f>IF($A187="","",IF(T187="","",T187+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB187" s="25">
+        <f>IF($A187="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F187='汇总与优先级'!$B$2),$AA187,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="P188" s="23">
@@ -13270,6 +14762,14 @@
         <f>IF($A188="","",IF(OR(Q188="",Q188=0),"",(Q188-T188)/Q188))</f>
         <v/>
       </c>
+      <c r="AA188" s="25">
+        <f>IF($A188="","",IF(T188="","",T188+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB188" s="25">
+        <f>IF($A188="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F188='汇总与优先级'!$B$2),$AA188,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="P189" s="23">
@@ -13312,6 +14812,14 @@
         <f>IF($A189="","",IF(OR(Q189="",Q189=0),"",(Q189-T189)/Q189))</f>
         <v/>
       </c>
+      <c r="AA189" s="25">
+        <f>IF($A189="","",IF(T189="","",T189+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB189" s="25">
+        <f>IF($A189="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F189='汇总与优先级'!$B$2),$AA189,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="P190" s="23">
@@ -13354,6 +14862,14 @@
         <f>IF($A190="","",IF(OR(Q190="",Q190=0),"",(Q190-T190)/Q190))</f>
         <v/>
       </c>
+      <c r="AA190" s="25">
+        <f>IF($A190="","",IF(T190="","",T190+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB190" s="25">
+        <f>IF($A190="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F190='汇总与优先级'!$B$2),$AA190,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="P191" s="23">
@@ -13396,6 +14912,14 @@
         <f>IF($A191="","",IF(OR(Q191="",Q191=0),"",(Q191-T191)/Q191))</f>
         <v/>
       </c>
+      <c r="AA191" s="25">
+        <f>IF($A191="","",IF(T191="","",T191+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB191" s="25">
+        <f>IF($A191="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F191='汇总与优先级'!$B$2),$AA191,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="P192" s="23">
@@ -13438,6 +14962,14 @@
         <f>IF($A192="","",IF(OR(Q192="",Q192=0),"",(Q192-T192)/Q192))</f>
         <v/>
       </c>
+      <c r="AA192" s="25">
+        <f>IF($A192="","",IF(T192="","",T192+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB192" s="25">
+        <f>IF($A192="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F192='汇总与优先级'!$B$2),$AA192,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="P193" s="23">
@@ -13480,6 +15012,14 @@
         <f>IF($A193="","",IF(OR(Q193="",Q193=0),"",(Q193-T193)/Q193))</f>
         <v/>
       </c>
+      <c r="AA193" s="25">
+        <f>IF($A193="","",IF(T193="","",T193+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB193" s="25">
+        <f>IF($A193="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F193='汇总与优先级'!$B$2),$AA193,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="P194" s="23">
@@ -13522,6 +15062,14 @@
         <f>IF($A194="","",IF(OR(Q194="",Q194=0),"",(Q194-T194)/Q194))</f>
         <v/>
       </c>
+      <c r="AA194" s="25">
+        <f>IF($A194="","",IF(T194="","",T194+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB194" s="25">
+        <f>IF($A194="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F194='汇总与优先级'!$B$2),$AA194,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="P195" s="23">
@@ -13564,6 +15112,14 @@
         <f>IF($A195="","",IF(OR(Q195="",Q195=0),"",(Q195-T195)/Q195))</f>
         <v/>
       </c>
+      <c r="AA195" s="25">
+        <f>IF($A195="","",IF(T195="","",T195+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB195" s="25">
+        <f>IF($A195="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F195='汇总与优先级'!$B$2),$AA195,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="P196" s="23">
@@ -13606,6 +15162,14 @@
         <f>IF($A196="","",IF(OR(Q196="",Q196=0),"",(Q196-T196)/Q196))</f>
         <v/>
       </c>
+      <c r="AA196" s="25">
+        <f>IF($A196="","",IF(T196="","",T196+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB196" s="25">
+        <f>IF($A196="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F196='汇总与优先级'!$B$2),$AA196,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="P197" s="23">
@@ -13648,6 +15212,14 @@
         <f>IF($A197="","",IF(OR(Q197="",Q197=0),"",(Q197-T197)/Q197))</f>
         <v/>
       </c>
+      <c r="AA197" s="25">
+        <f>IF($A197="","",IF(T197="","",T197+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB197" s="25">
+        <f>IF($A197="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F197='汇总与优先级'!$B$2),$AA197,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="P198" s="23">
@@ -13690,6 +15262,14 @@
         <f>IF($A198="","",IF(OR(Q198="",Q198=0),"",(Q198-T198)/Q198))</f>
         <v/>
       </c>
+      <c r="AA198" s="25">
+        <f>IF($A198="","",IF(T198="","",T198+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB198" s="25">
+        <f>IF($A198="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F198='汇总与优先级'!$B$2),$AA198,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="P199" s="23">
@@ -13732,6 +15312,14 @@
         <f>IF($A199="","",IF(OR(Q199="",Q199=0),"",(Q199-T199)/Q199))</f>
         <v/>
       </c>
+      <c r="AA199" s="25">
+        <f>IF($A199="","",IF(T199="","",T199+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB199" s="25">
+        <f>IF($A199="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F199='汇总与优先级'!$B$2),$AA199,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="P200" s="23">
@@ -13774,6 +15362,14 @@
         <f>IF($A200="","",IF(OR(Q200="",Q200=0),"",(Q200-T200)/Q200))</f>
         <v/>
       </c>
+      <c r="AA200" s="25">
+        <f>IF($A200="","",IF(T200="","",T200+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB200" s="25">
+        <f>IF($A200="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F200='汇总与优先级'!$B$2),$AA200,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="P201" s="23">
@@ -13816,6 +15412,14 @@
         <f>IF($A201="","",IF(OR(Q201="",Q201=0),"",(Q201-T201)/Q201))</f>
         <v/>
       </c>
+      <c r="AA201" s="25">
+        <f>IF($A201="","",IF(T201="","",T201+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB201" s="25">
+        <f>IF($A201="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F201='汇总与优先级'!$B$2),$AA201,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="P202" s="23">
@@ -13858,6 +15462,14 @@
         <f>IF($A202="","",IF(OR(Q202="",Q202=0),"",(Q202-T202)/Q202))</f>
         <v/>
       </c>
+      <c r="AA202" s="25">
+        <f>IF($A202="","",IF(T202="","",T202+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB202" s="25">
+        <f>IF($A202="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F202='汇总与优先级'!$B$2),$AA202,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="P203" s="23">
@@ -13898,6 +15510,14 @@
       </c>
       <c r="Y203" s="24">
         <f>IF($A203="","",IF(OR(Q203="",Q203=0),"",(Q203-T203)/Q203))</f>
+        <v/>
+      </c>
+      <c r="AA203" s="25">
+        <f>IF($A203="","",IF(T203="","",T203+(204-ROW())/1000000))</f>
+        <v/>
+      </c>
+      <c r="AB203" s="25">
+        <f>IF($A203="",NA(),IF(OR('汇总与优先级'!$B$2="全部",$F203='汇总与优先级'!$B$2),$AA203,NA()))</f>
         <v/>
       </c>
     </row>
@@ -15942,7 +17562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>风险热力图（可能性 × 综合影响）</t>
+          <t>风险热力图（可能性 × 综合影响档）</t>
         </is>
       </c>
     </row>
@@ -15952,7 +17572,7 @@
           <t>评估期间筛选：</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>2026H1</t>
         </is>
@@ -15966,9 +17586,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>可能性＼影响</t>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>可能性＼影响档</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -15988,126 +17608,126 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B7,风险登记册!$V$4:$V$203,C$6)</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B7,风险登记册!$V$4:$V$203,D$6)</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B7,风险登记册!$V$4:$V$203,E$6)</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B7,风险登记册!$V$4:$V$203,F$6)</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B7,风险登记册!$V$4:$V$203,G$6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B8,风险登记册!$V$4:$V$203,C$6)</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B8,风险登记册!$V$4:$V$203,D$6)</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B8,风险登记册!$V$4:$V$203,E$6)</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B8,风险登记册!$V$4:$V$203,F$6)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B8,风险登记册!$V$4:$V$203,G$6)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B9,风险登记册!$V$4:$V$203,C$6)</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B9,风险登记册!$V$4:$V$203,D$6)</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B9,风险登记册!$V$4:$V$203,E$6)</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B9,风险登记册!$V$4:$V$203,F$6)</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B9,风险登记册!$V$4:$V$203,G$6)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B10,风险登记册!$V$4:$V$203,C$6)</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B10,风险登记册!$V$4:$V$203,D$6)</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B10,风险登记册!$V$4:$V$203,E$6)</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B10,风险登记册!$V$4:$V$203,F$6)</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B10,风险登记册!$V$4:$V$203,G$6)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B11,风险登记册!$V$4:$V$203,C$6)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B11,风险登记册!$V$4:$V$203,D$6)</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B11,风险登记册!$V$4:$V$203,E$6)</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B11,风险登记册!$V$4:$V$203,F$6)</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="29">
         <f>COUNTIFS(风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B11,风险登记册!$V$4:$V$203,G$6)</f>
         <v/>
       </c>
@@ -16120,9 +17740,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>可能性＼影响</t>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>可能性＼影响档</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -16142,126 +17762,126 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B15,风险登记册!$V$4:$V$203,C$14),"")</f>
         <v/>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B15,风险登记册!$V$4:$V$203,D$14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B15,风险登记册!$V$4:$V$203,E$14),"")</f>
         <v/>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B15,风险登记册!$V$4:$V$203,F$14),"")</f>
         <v/>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B15,风险登记册!$V$4:$V$203,G$14),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B16,风险登记册!$V$4:$V$203,C$14),"")</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B16,风险登记册!$V$4:$V$203,D$14),"")</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B16,风险登记册!$V$4:$V$203,E$14),"")</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B16,风险登记册!$V$4:$V$203,F$14),"")</f>
         <v/>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B16,风险登记册!$V$4:$V$203,G$14),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B17,风险登记册!$V$4:$V$203,C$14),"")</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B17,风险登记册!$V$4:$V$203,D$14),"")</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B17,风险登记册!$V$4:$V$203,E$14),"")</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B17,风险登记册!$V$4:$V$203,F$14),"")</f>
         <v/>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B17,风险登记册!$V$4:$V$203,G$14),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B18,风险登记册!$V$4:$V$203,C$14),"")</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B18,风险登记册!$V$4:$V$203,D$14),"")</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B18,风险登记册!$V$4:$V$203,E$14),"")</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B18,风险登记册!$V$4:$V$203,F$14),"")</f>
         <v/>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B18,风险登记册!$V$4:$V$203,G$14),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B19,风险登记册!$V$4:$V$203,C$14),"")</f>
         <v/>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B19,风险登记册!$V$4:$V$203,D$14),"")</f>
         <v/>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B19,风险登记册!$V$4:$V$203,E$14),"")</f>
         <v/>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B19,风险登记册!$V$4:$V$203,F$14),"")</f>
         <v/>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="34">
         <f>IFERROR(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$F$4:$F$203,IF($C$3="全部","&lt;&gt;",$C$3),风险登记册!$G$4:$G$203,$B19,风险登记册!$V$4:$V$203,G$14),"")</f>
         <v/>
       </c>
@@ -16305,7 +17925,7 @@
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>说明：固有矩阵定位＝(发生可能性, 综合影响取整)；剩余矩阵同一坐标展示控制后的平均剩余分。逐条风险的精确剩余分见「汇总与优先级」页。</t>
+          <t>说明：固有矩阵定位＝(发生可能性, 综合影响档)；影响档由精确综合影响四舍五入得到。剩余矩阵同一坐标展示控制后的平均剩余分。逐条风险的精确剩余分见「汇总与优先级」页。</t>
         </is>
       </c>
     </row>
@@ -16343,7 +17963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -16357,6 +17977,7 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16372,7 +17993,7 @@
           <t>评估期间（联动热力图页）：</t>
         </is>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="35">
         <f>热力图!$C$3</f>
         <v/>
       </c>
@@ -16431,7 +18052,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A6,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A6,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16462,7 +18083,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A7,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A7,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16493,7 +18114,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A8,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A8,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16524,7 +18145,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A9,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A9,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16555,7 +18176,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A10,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A10,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16586,7 +18207,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A11,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A11,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16617,7 +18238,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A12,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A12,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16648,7 +18269,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A13,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A13,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16679,7 +18300,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A14,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A14,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16710,7 +18331,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A15,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A15,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16741,7 +18362,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A16,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A16,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16772,7 +18393,7 @@
         <f>COUNTIFS(风险登记册!$C$4:$C$203,$A17,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2))</f>
         <v/>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="34">
         <f>IFERROR(ROUND(AVERAGEIFS(风险登记册!$T$4:$T$203,风险登记册!$C$4:$C$203,$A17,风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2)),2),"—")</f>
         <v/>
       </c>
@@ -16856,3684 +18477,4010 @@
           <t>建议频次</t>
         </is>
       </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>选源排序键
+(辅助)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5">
-        <f>IF($B21="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I21)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I21,风险登记册!$A$4:$A$203,"&lt;"&amp;$B21)+1)</f>
+        <f>IF($L21="","",ROWS($A$21:A21))</f>
         <v/>
       </c>
       <c r="B21" s="5">
-        <f>IF($B21="","",风险登记册!A4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF($B21="","",风险登记册!B4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF($B21="","",风险登记册!C4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IF($B21="","",风险登记册!E4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>IF($B21="","",风险登记册!G4)</f>
-        <v/>
-      </c>
-      <c r="G21" s="33">
-        <f>IF($B21="","",风险登记册!Q4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF($L21="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H21" s="5">
-        <f>IF($B21="","",风险登记册!R4)</f>
-        <v/>
-      </c>
-      <c r="I21" s="33">
-        <f>IF($B21="","",风险登记册!T4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="34">
+        <f>IF($L21="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J21" s="5">
-        <f>IF($B21="","",风险登记册!U4)</f>
+        <f>IF($L21="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L21,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IF($B21="","",IF($J21="极高","每年必审",IF($J21="高","每年审计",IF($J21="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L21="","",IF($J21="极高","每年必审",IF($J21="高","每年审计",IF($J21="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L21" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L21)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5">
-        <f>IF($B22="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I22)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I22,风险登记册!$A$4:$A$203,"&lt;"&amp;$B22)+1)</f>
+        <f>IF($L22="","",ROWS($A$21:A22))</f>
         <v/>
       </c>
       <c r="B22" s="5">
-        <f>IF($B22="","",风险登记册!A5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF($B22="","",风险登记册!B5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF($B22="","",风险登记册!C5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IF($B22="","",风险登记册!E5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>IF($B22="","",风险登记册!G5)</f>
-        <v/>
-      </c>
-      <c r="G22" s="33">
-        <f>IF($B22="","",风险登记册!Q5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF($L22="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H22" s="5">
-        <f>IF($B22="","",风险登记册!R5)</f>
-        <v/>
-      </c>
-      <c r="I22" s="33">
-        <f>IF($B22="","",风险登记册!T5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="34">
+        <f>IF($L22="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J22" s="5">
-        <f>IF($B22="","",风险登记册!U5)</f>
+        <f>IF($L22="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L22,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IF($B22="","",IF($J22="极高","每年必审",IF($J22="高","每年审计",IF($J22="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L22="","",IF($J22="极高","每年必审",IF($J22="高","每年审计",IF($J22="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L22" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L22)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5">
-        <f>IF($B23="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I23)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I23,风险登记册!$A$4:$A$203,"&lt;"&amp;$B23)+1)</f>
+        <f>IF($L23="","",ROWS($A$21:A23))</f>
         <v/>
       </c>
       <c r="B23" s="5">
-        <f>IF($B23="","",风险登记册!A6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF($B23="","",风险登记册!B6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF($B23="","",风险登记册!C6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IF($B23="","",风险登记册!E6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>IF($B23="","",风险登记册!G6)</f>
-        <v/>
-      </c>
-      <c r="G23" s="33">
-        <f>IF($B23="","",风险登记册!Q6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF($L23="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H23" s="5">
-        <f>IF($B23="","",风险登记册!R6)</f>
-        <v/>
-      </c>
-      <c r="I23" s="33">
-        <f>IF($B23="","",风险登记册!T6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="34">
+        <f>IF($L23="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J23" s="5">
-        <f>IF($B23="","",风险登记册!U6)</f>
+        <f>IF($L23="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L23,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IF($B23="","",IF($J23="极高","每年必审",IF($J23="高","每年审计",IF($J23="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L23="","",IF($J23="极高","每年必审",IF($J23="高","每年审计",IF($J23="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L23" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L23)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5">
-        <f>IF($B24="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I24)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I24,风险登记册!$A$4:$A$203,"&lt;"&amp;$B24)+1)</f>
+        <f>IF($L24="","",ROWS($A$21:A24))</f>
         <v/>
       </c>
       <c r="B24" s="5">
-        <f>IF($B24="","",风险登记册!A7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF($B24="","",风险登记册!B7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF($B24="","",风险登记册!C7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IF($B24="","",风险登记册!E7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>IF($B24="","",风险登记册!G7)</f>
-        <v/>
-      </c>
-      <c r="G24" s="33">
-        <f>IF($B24="","",风险登记册!Q7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF($L24="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H24" s="5">
-        <f>IF($B24="","",风险登记册!R7)</f>
-        <v/>
-      </c>
-      <c r="I24" s="33">
-        <f>IF($B24="","",风险登记册!T7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="34">
+        <f>IF($L24="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J24" s="5">
-        <f>IF($B24="","",风险登记册!U7)</f>
+        <f>IF($L24="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L24,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IF($B24="","",IF($J24="极高","每年必审",IF($J24="高","每年审计",IF($J24="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L24="","",IF($J24="极高","每年必审",IF($J24="高","每年审计",IF($J24="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L24" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L24)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5">
-        <f>IF($B25="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I25)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I25,风险登记册!$A$4:$A$203,"&lt;"&amp;$B25)+1)</f>
+        <f>IF($L25="","",ROWS($A$21:A25))</f>
         <v/>
       </c>
       <c r="B25" s="5">
-        <f>IF($B25="","",风险登记册!A8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF($B25="","",风险登记册!B8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF($B25="","",风险登记册!C8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IF($B25="","",风险登记册!E8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>IF($B25="","",风险登记册!G8)</f>
-        <v/>
-      </c>
-      <c r="G25" s="33">
-        <f>IF($B25="","",风险登记册!Q8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF($L25="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H25" s="5">
-        <f>IF($B25="","",风险登记册!R8)</f>
-        <v/>
-      </c>
-      <c r="I25" s="33">
-        <f>IF($B25="","",风险登记册!T8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="34">
+        <f>IF($L25="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J25" s="5">
-        <f>IF($B25="","",风险登记册!U8)</f>
+        <f>IF($L25="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L25,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IF($B25="","",IF($J25="极高","每年必审",IF($J25="高","每年审计",IF($J25="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L25="","",IF($J25="极高","每年必审",IF($J25="高","每年审计",IF($J25="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L25" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L25)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5">
-        <f>IF($B26="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I26)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I26,风险登记册!$A$4:$A$203,"&lt;"&amp;$B26)+1)</f>
+        <f>IF($L26="","",ROWS($A$21:A26))</f>
         <v/>
       </c>
       <c r="B26" s="5">
-        <f>IF($B26="","",风险登记册!A9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF($B26="","",风险登记册!B9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF($B26="","",风险登记册!C9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IF($B26="","",风险登记册!E9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>IF($B26="","",风险登记册!G9)</f>
-        <v/>
-      </c>
-      <c r="G26" s="33">
-        <f>IF($B26="","",风险登记册!Q9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF($L26="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H26" s="5">
-        <f>IF($B26="","",风险登记册!R9)</f>
-        <v/>
-      </c>
-      <c r="I26" s="33">
-        <f>IF($B26="","",风险登记册!T9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="34">
+        <f>IF($L26="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J26" s="5">
-        <f>IF($B26="","",风险登记册!U9)</f>
+        <f>IF($L26="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L26,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IF($B26="","",IF($J26="极高","每年必审",IF($J26="高","每年审计",IF($J26="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L26="","",IF($J26="极高","每年必审",IF($J26="高","每年审计",IF($J26="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L26" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L26)),"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5">
-        <f>IF($B27="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I27)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I27,风险登记册!$A$4:$A$203,"&lt;"&amp;$B27)+1)</f>
+        <f>IF($L27="","",ROWS($A$21:A27))</f>
         <v/>
       </c>
       <c r="B27" s="5">
-        <f>IF($B27="","",风险登记册!A10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF($B27="","",风险登记册!B10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF($B27="","",风险登记册!C10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IF($B27="","",风险登记册!E10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>IF($B27="","",风险登记册!G10)</f>
-        <v/>
-      </c>
-      <c r="G27" s="33">
-        <f>IF($B27="","",风险登记册!Q10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF($L27="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H27" s="5">
-        <f>IF($B27="","",风险登记册!R10)</f>
-        <v/>
-      </c>
-      <c r="I27" s="33">
-        <f>IF($B27="","",风险登记册!T10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="34">
+        <f>IF($L27="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J27" s="5">
-        <f>IF($B27="","",风险登记册!U10)</f>
+        <f>IF($L27="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L27,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IF($B27="","",IF($J27="极高","每年必审",IF($J27="高","每年审计",IF($J27="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L27="","",IF($J27="极高","每年必审",IF($J27="高","每年审计",IF($J27="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L27" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L27)),"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5">
-        <f>IF($B28="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I28)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I28,风险登记册!$A$4:$A$203,"&lt;"&amp;$B28)+1)</f>
+        <f>IF($L28="","",ROWS($A$21:A28))</f>
         <v/>
       </c>
       <c r="B28" s="5">
-        <f>IF($B28="","",风险登记册!A11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF($B28="","",风险登记册!B11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF($B28="","",风险登记册!C11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IF($B28="","",风险登记册!E11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>IF($B28="","",风险登记册!G11)</f>
-        <v/>
-      </c>
-      <c r="G28" s="33">
-        <f>IF($B28="","",风险登记册!Q11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF($L28="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H28" s="5">
-        <f>IF($B28="","",风险登记册!R11)</f>
-        <v/>
-      </c>
-      <c r="I28" s="33">
-        <f>IF($B28="","",风险登记册!T11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="34">
+        <f>IF($L28="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J28" s="5">
-        <f>IF($B28="","",风险登记册!U11)</f>
+        <f>IF($L28="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L28,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IF($B28="","",IF($J28="极高","每年必审",IF($J28="高","每年审计",IF($J28="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L28="","",IF($J28="极高","每年必审",IF($J28="高","每年审计",IF($J28="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L28" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L28)),"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5">
-        <f>IF($B29="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I29)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I29,风险登记册!$A$4:$A$203,"&lt;"&amp;$B29)+1)</f>
+        <f>IF($L29="","",ROWS($A$21:A29))</f>
         <v/>
       </c>
       <c r="B29" s="5">
-        <f>IF($B29="","",风险登记册!A12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF($B29="","",风险登记册!B12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF($B29="","",风险登记册!C12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IF($B29="","",风险登记册!E12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>IF($B29="","",风险登记册!G12)</f>
-        <v/>
-      </c>
-      <c r="G29" s="33">
-        <f>IF($B29="","",风险登记册!Q12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF($L29="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H29" s="5">
-        <f>IF($B29="","",风险登记册!R12)</f>
-        <v/>
-      </c>
-      <c r="I29" s="33">
-        <f>IF($B29="","",风险登记册!T12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="34">
+        <f>IF($L29="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J29" s="5">
-        <f>IF($B29="","",风险登记册!U12)</f>
+        <f>IF($L29="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L29,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IF($B29="","",IF($J29="极高","每年必审",IF($J29="高","每年审计",IF($J29="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L29="","",IF($J29="极高","每年必审",IF($J29="高","每年审计",IF($J29="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L29" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L29)),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5">
-        <f>IF($B30="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I30)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I30,风险登记册!$A$4:$A$203,"&lt;"&amp;$B30)+1)</f>
+        <f>IF($L30="","",ROWS($A$21:A30))</f>
         <v/>
       </c>
       <c r="B30" s="5">
-        <f>IF($B30="","",风险登记册!A13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF($B30="","",风险登记册!B13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF($B30="","",风险登记册!C13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IF($B30="","",风险登记册!E13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>IF($B30="","",风险登记册!G13)</f>
-        <v/>
-      </c>
-      <c r="G30" s="33">
-        <f>IF($B30="","",风险登记册!Q13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF($L30="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H30" s="5">
-        <f>IF($B30="","",风险登记册!R13)</f>
-        <v/>
-      </c>
-      <c r="I30" s="33">
-        <f>IF($B30="","",风险登记册!T13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I30" s="34">
+        <f>IF($L30="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J30" s="5">
-        <f>IF($B30="","",风险登记册!U13)</f>
+        <f>IF($L30="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L30,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IF($B30="","",IF($J30="极高","每年必审",IF($J30="高","每年审计",IF($J30="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L30="","",IF($J30="极高","每年必审",IF($J30="高","每年审计",IF($J30="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L30" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L30)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5">
-        <f>IF($B31="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I31)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I31,风险登记册!$A$4:$A$203,"&lt;"&amp;$B31)+1)</f>
+        <f>IF($L31="","",ROWS($A$21:A31))</f>
         <v/>
       </c>
       <c r="B31" s="5">
-        <f>IF($B31="","",风险登记册!A14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF($B31="","",风险登记册!B14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF($B31="","",风险登记册!C14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IF($B31="","",风险登记册!E14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>IF($B31="","",风险登记册!G14)</f>
-        <v/>
-      </c>
-      <c r="G31" s="33">
-        <f>IF($B31="","",风险登记册!Q14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G31" s="34">
+        <f>IF($L31="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H31" s="5">
-        <f>IF($B31="","",风险登记册!R14)</f>
-        <v/>
-      </c>
-      <c r="I31" s="33">
-        <f>IF($B31="","",风险登记册!T14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I31" s="34">
+        <f>IF($L31="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J31" s="5">
-        <f>IF($B31="","",风险登记册!U14)</f>
+        <f>IF($L31="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L31,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IF($B31="","",IF($J31="极高","每年必审",IF($J31="高","每年审计",IF($J31="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L31="","",IF($J31="极高","每年必审",IF($J31="高","每年审计",IF($J31="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L31" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L31)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5">
-        <f>IF($B32="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I32)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I32,风险登记册!$A$4:$A$203,"&lt;"&amp;$B32)+1)</f>
+        <f>IF($L32="","",ROWS($A$21:A32))</f>
         <v/>
       </c>
       <c r="B32" s="5">
-        <f>IF($B32="","",风险登记册!A15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF($B32="","",风险登记册!B15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF($B32="","",风险登记册!C15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IF($B32="","",风险登记册!E15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>IF($B32="","",风险登记册!G15)</f>
-        <v/>
-      </c>
-      <c r="G32" s="33">
-        <f>IF($B32="","",风险登记册!Q15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G32" s="34">
+        <f>IF($L32="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H32" s="5">
-        <f>IF($B32="","",风险登记册!R15)</f>
-        <v/>
-      </c>
-      <c r="I32" s="33">
-        <f>IF($B32="","",风险登记册!T15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I32" s="34">
+        <f>IF($L32="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J32" s="5">
-        <f>IF($B32="","",风险登记册!U15)</f>
+        <f>IF($L32="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L32,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IF($B32="","",IF($J32="极高","每年必审",IF($J32="高","每年审计",IF($J32="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L32="","",IF($J32="极高","每年必审",IF($J32="高","每年审计",IF($J32="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L32" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L32)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5">
-        <f>IF($B33="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I33)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I33,风险登记册!$A$4:$A$203,"&lt;"&amp;$B33)+1)</f>
+        <f>IF($L33="","",ROWS($A$21:A33))</f>
         <v/>
       </c>
       <c r="B33" s="5">
-        <f>IF($B33="","",风险登记册!A16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF($B33="","",风险登记册!B16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF($B33="","",风险登记册!C16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IF($B33="","",风险登记册!E16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>IF($B33="","",风险登记册!G16)</f>
-        <v/>
-      </c>
-      <c r="G33" s="33">
-        <f>IF($B33="","",风险登记册!Q16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G33" s="34">
+        <f>IF($L33="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H33" s="5">
-        <f>IF($B33="","",风险登记册!R16)</f>
-        <v/>
-      </c>
-      <c r="I33" s="33">
-        <f>IF($B33="","",风险登记册!T16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I33" s="34">
+        <f>IF($L33="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J33" s="5">
-        <f>IF($B33="","",风险登记册!U16)</f>
+        <f>IF($L33="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L33,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IF($B33="","",IF($J33="极高","每年必审",IF($J33="高","每年审计",IF($J33="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L33="","",IF($J33="极高","每年必审",IF($J33="高","每年审计",IF($J33="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L33" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L33)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5">
-        <f>IF($B34="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I34)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I34,风险登记册!$A$4:$A$203,"&lt;"&amp;$B34)+1)</f>
+        <f>IF($L34="","",ROWS($A$21:A34))</f>
         <v/>
       </c>
       <c r="B34" s="5">
-        <f>IF($B34="","",风险登记册!A17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF($B34="","",风险登记册!B17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF($B34="","",风险登记册!C17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IF($B34="","",风险登记册!E17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>IF($B34="","",风险登记册!G17)</f>
-        <v/>
-      </c>
-      <c r="G34" s="33">
-        <f>IF($B34="","",风险登记册!Q17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G34" s="34">
+        <f>IF($L34="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H34" s="5">
-        <f>IF($B34="","",风险登记册!R17)</f>
-        <v/>
-      </c>
-      <c r="I34" s="33">
-        <f>IF($B34="","",风险登记册!T17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I34" s="34">
+        <f>IF($L34="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J34" s="5">
-        <f>IF($B34="","",风险登记册!U17)</f>
+        <f>IF($L34="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L34,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IF($B34="","",IF($J34="极高","每年必审",IF($J34="高","每年审计",IF($J34="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L34="","",IF($J34="极高","每年必审",IF($J34="高","每年审计",IF($J34="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L34" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L34)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5">
-        <f>IF($B35="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I35)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I35,风险登记册!$A$4:$A$203,"&lt;"&amp;$B35)+1)</f>
+        <f>IF($L35="","",ROWS($A$21:A35))</f>
         <v/>
       </c>
       <c r="B35" s="5">
-        <f>IF($B35="","",风险登记册!A18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF($B35="","",风险登记册!B18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF($B35="","",风险登记册!C18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IF($B35="","",风险登记册!E18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F35" s="5">
-        <f>IF($B35="","",风险登记册!G18)</f>
-        <v/>
-      </c>
-      <c r="G35" s="33">
-        <f>IF($B35="","",风险登记册!Q18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G35" s="34">
+        <f>IF($L35="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H35" s="5">
-        <f>IF($B35="","",风险登记册!R18)</f>
-        <v/>
-      </c>
-      <c r="I35" s="33">
-        <f>IF($B35="","",风险登记册!T18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I35" s="34">
+        <f>IF($L35="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J35" s="5">
-        <f>IF($B35="","",风险登记册!U18)</f>
+        <f>IF($L35="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L35,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K35" s="5">
-        <f>IF($B35="","",IF($J35="极高","每年必审",IF($J35="高","每年审计",IF($J35="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L35="","",IF($J35="极高","每年必审",IF($J35="高","每年审计",IF($J35="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L35" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L35)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5">
-        <f>IF($B36="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I36)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I36,风险登记册!$A$4:$A$203,"&lt;"&amp;$B36)+1)</f>
+        <f>IF($L36="","",ROWS($A$21:A36))</f>
         <v/>
       </c>
       <c r="B36" s="5">
-        <f>IF($B36="","",风险登记册!A19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF($B36="","",风险登记册!B19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF($B36="","",风险登记册!C19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IF($B36="","",风险登记册!E19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F36" s="5">
-        <f>IF($B36="","",风险登记册!G19)</f>
-        <v/>
-      </c>
-      <c r="G36" s="33">
-        <f>IF($B36="","",风险登记册!Q19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G36" s="34">
+        <f>IF($L36="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H36" s="5">
-        <f>IF($B36="","",风险登记册!R19)</f>
-        <v/>
-      </c>
-      <c r="I36" s="33">
-        <f>IF($B36="","",风险登记册!T19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I36" s="34">
+        <f>IF($L36="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J36" s="5">
-        <f>IF($B36="","",风险登记册!U19)</f>
+        <f>IF($L36="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L36,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K36" s="5">
-        <f>IF($B36="","",IF($J36="极高","每年必审",IF($J36="高","每年审计",IF($J36="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L36="","",IF($J36="极高","每年必审",IF($J36="高","每年审计",IF($J36="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L36" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L36)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5">
-        <f>IF($B37="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I37)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I37,风险登记册!$A$4:$A$203,"&lt;"&amp;$B37)+1)</f>
+        <f>IF($L37="","",ROWS($A$21:A37))</f>
         <v/>
       </c>
       <c r="B37" s="5">
-        <f>IF($B37="","",风险登记册!A20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF($B37="","",风险登记册!B20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF($B37="","",风险登记册!C20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IF($B37="","",风险登记册!E20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F37" s="5">
-        <f>IF($B37="","",风险登记册!G20)</f>
-        <v/>
-      </c>
-      <c r="G37" s="33">
-        <f>IF($B37="","",风险登记册!Q20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G37" s="34">
+        <f>IF($L37="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H37" s="5">
-        <f>IF($B37="","",风险登记册!R20)</f>
-        <v/>
-      </c>
-      <c r="I37" s="33">
-        <f>IF($B37="","",风险登记册!T20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I37" s="34">
+        <f>IF($L37="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J37" s="5">
-        <f>IF($B37="","",风险登记册!U20)</f>
+        <f>IF($L37="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L37,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K37" s="5">
-        <f>IF($B37="","",IF($J37="极高","每年必审",IF($J37="高","每年审计",IF($J37="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L37="","",IF($J37="极高","每年必审",IF($J37="高","每年审计",IF($J37="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L37" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L37)),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5">
-        <f>IF($B38="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I38)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I38,风险登记册!$A$4:$A$203,"&lt;"&amp;$B38)+1)</f>
+        <f>IF($L38="","",ROWS($A$21:A38))</f>
         <v/>
       </c>
       <c r="B38" s="5">
-        <f>IF($B38="","",风险登记册!A21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF($B38="","",风险登记册!B21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF($B38="","",风险登记册!C21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IF($B38="","",风险登记册!E21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F38" s="5">
-        <f>IF($B38="","",风险登记册!G21)</f>
-        <v/>
-      </c>
-      <c r="G38" s="33">
-        <f>IF($B38="","",风险登记册!Q21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G38" s="34">
+        <f>IF($L38="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H38" s="5">
-        <f>IF($B38="","",风险登记册!R21)</f>
-        <v/>
-      </c>
-      <c r="I38" s="33">
-        <f>IF($B38="","",风险登记册!T21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I38" s="34">
+        <f>IF($L38="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J38" s="5">
-        <f>IF($B38="","",风险登记册!U21)</f>
+        <f>IF($L38="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L38,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K38" s="5">
-        <f>IF($B38="","",IF($J38="极高","每年必审",IF($J38="高","每年审计",IF($J38="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L38="","",IF($J38="极高","每年必审",IF($J38="高","每年审计",IF($J38="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L38" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L38)),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5">
-        <f>IF($B39="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I39)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I39,风险登记册!$A$4:$A$203,"&lt;"&amp;$B39)+1)</f>
+        <f>IF($L39="","",ROWS($A$21:A39))</f>
         <v/>
       </c>
       <c r="B39" s="5">
-        <f>IF($B39="","",风险登记册!A22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF($B39="","",风险登记册!B22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF($B39="","",风险登记册!C22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IF($B39="","",风险登记册!E22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F39" s="5">
-        <f>IF($B39="","",风险登记册!G22)</f>
-        <v/>
-      </c>
-      <c r="G39" s="33">
-        <f>IF($B39="","",风险登记册!Q22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G39" s="34">
+        <f>IF($L39="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H39" s="5">
-        <f>IF($B39="","",风险登记册!R22)</f>
-        <v/>
-      </c>
-      <c r="I39" s="33">
-        <f>IF($B39="","",风险登记册!T22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I39" s="34">
+        <f>IF($L39="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J39" s="5">
-        <f>IF($B39="","",风险登记册!U22)</f>
+        <f>IF($L39="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L39,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>IF($B39="","",IF($J39="极高","每年必审",IF($J39="高","每年审计",IF($J39="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L39="","",IF($J39="极高","每年必审",IF($J39="高","每年审计",IF($J39="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L39" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L39)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5">
-        <f>IF($B40="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I40)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I40,风险登记册!$A$4:$A$203,"&lt;"&amp;$B40)+1)</f>
+        <f>IF($L40="","",ROWS($A$21:A40))</f>
         <v/>
       </c>
       <c r="B40" s="5">
-        <f>IF($B40="","",风险登记册!A23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IF($B40="","",风险登记册!B23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D40" s="6">
-        <f>IF($B40="","",风险登记册!C23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E40" s="6">
-        <f>IF($B40="","",风险登记册!E23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>IF($B40="","",风险登记册!G23)</f>
-        <v/>
-      </c>
-      <c r="G40" s="33">
-        <f>IF($B40="","",风险登记册!Q23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G40" s="34">
+        <f>IF($L40="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H40" s="5">
-        <f>IF($B40="","",风险登记册!R23)</f>
-        <v/>
-      </c>
-      <c r="I40" s="33">
-        <f>IF($B40="","",风险登记册!T23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I40" s="34">
+        <f>IF($L40="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J40" s="5">
-        <f>IF($B40="","",风险登记册!U23)</f>
+        <f>IF($L40="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L40,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IF($B40="","",IF($J40="极高","每年必审",IF($J40="高","每年审计",IF($J40="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L40="","",IF($J40="极高","每年必审",IF($J40="高","每年审计",IF($J40="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L40" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L40)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5">
-        <f>IF($B41="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I41)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I41,风险登记册!$A$4:$A$203,"&lt;"&amp;$B41)+1)</f>
+        <f>IF($L41="","",ROWS($A$21:A41))</f>
         <v/>
       </c>
       <c r="B41" s="5">
-        <f>IF($B41="","",风险登记册!A24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C41" s="6">
-        <f>IF($B41="","",风险登记册!B24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D41" s="6">
-        <f>IF($B41="","",风险登记册!C24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E41" s="6">
-        <f>IF($B41="","",风险登记册!E24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F41" s="5">
-        <f>IF($B41="","",风险登记册!G24)</f>
-        <v/>
-      </c>
-      <c r="G41" s="33">
-        <f>IF($B41="","",风险登记册!Q24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G41" s="34">
+        <f>IF($L41="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H41" s="5">
-        <f>IF($B41="","",风险登记册!R24)</f>
-        <v/>
-      </c>
-      <c r="I41" s="33">
-        <f>IF($B41="","",风险登记册!T24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I41" s="34">
+        <f>IF($L41="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J41" s="5">
-        <f>IF($B41="","",风险登记册!U24)</f>
+        <f>IF($L41="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L41,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>IF($B41="","",IF($J41="极高","每年必审",IF($J41="高","每年审计",IF($J41="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L41="","",IF($J41="极高","每年必审",IF($J41="高","每年审计",IF($J41="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L41" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L41)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5">
-        <f>IF($B42="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I42)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I42,风险登记册!$A$4:$A$203,"&lt;"&amp;$B42)+1)</f>
+        <f>IF($L42="","",ROWS($A$21:A42))</f>
         <v/>
       </c>
       <c r="B42" s="5">
-        <f>IF($B42="","",风险登记册!A25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C42" s="6">
-        <f>IF($B42="","",风险登记册!B25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D42" s="6">
-        <f>IF($B42="","",风险登记册!C25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E42" s="6">
-        <f>IF($B42="","",风险登记册!E25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F42" s="5">
-        <f>IF($B42="","",风险登记册!G25)</f>
-        <v/>
-      </c>
-      <c r="G42" s="33">
-        <f>IF($B42="","",风险登记册!Q25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G42" s="34">
+        <f>IF($L42="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H42" s="5">
-        <f>IF($B42="","",风险登记册!R25)</f>
-        <v/>
-      </c>
-      <c r="I42" s="33">
-        <f>IF($B42="","",风险登记册!T25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I42" s="34">
+        <f>IF($L42="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J42" s="5">
-        <f>IF($B42="","",风险登记册!U25)</f>
+        <f>IF($L42="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L42,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K42" s="5">
-        <f>IF($B42="","",IF($J42="极高","每年必审",IF($J42="高","每年审计",IF($J42="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L42="","",IF($J42="极高","每年必审",IF($J42="高","每年审计",IF($J42="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L42" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L42)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5">
-        <f>IF($B43="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I43)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I43,风险登记册!$A$4:$A$203,"&lt;"&amp;$B43)+1)</f>
+        <f>IF($L43="","",ROWS($A$21:A43))</f>
         <v/>
       </c>
       <c r="B43" s="5">
-        <f>IF($B43="","",风险登记册!A26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C43" s="6">
-        <f>IF($B43="","",风险登记册!B26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D43" s="6">
-        <f>IF($B43="","",风险登记册!C26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E43" s="6">
-        <f>IF($B43="","",风险登记册!E26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F43" s="5">
-        <f>IF($B43="","",风险登记册!G26)</f>
-        <v/>
-      </c>
-      <c r="G43" s="33">
-        <f>IF($B43="","",风险登记册!Q26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G43" s="34">
+        <f>IF($L43="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H43" s="5">
-        <f>IF($B43="","",风险登记册!R26)</f>
-        <v/>
-      </c>
-      <c r="I43" s="33">
-        <f>IF($B43="","",风险登记册!T26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I43" s="34">
+        <f>IF($L43="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J43" s="5">
-        <f>IF($B43="","",风险登记册!U26)</f>
+        <f>IF($L43="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L43,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K43" s="5">
-        <f>IF($B43="","",IF($J43="极高","每年必审",IF($J43="高","每年审计",IF($J43="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L43="","",IF($J43="极高","每年必审",IF($J43="高","每年审计",IF($J43="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L43" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L43)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5">
-        <f>IF($B44="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I44)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I44,风险登记册!$A$4:$A$203,"&lt;"&amp;$B44)+1)</f>
+        <f>IF($L44="","",ROWS($A$21:A44))</f>
         <v/>
       </c>
       <c r="B44" s="5">
-        <f>IF($B44="","",风险登记册!A27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C44" s="6">
-        <f>IF($B44="","",风险登记册!B27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D44" s="6">
-        <f>IF($B44="","",风险登记册!C27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E44" s="6">
-        <f>IF($B44="","",风险登记册!E27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F44" s="5">
-        <f>IF($B44="","",风险登记册!G27)</f>
-        <v/>
-      </c>
-      <c r="G44" s="33">
-        <f>IF($B44="","",风险登记册!Q27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G44" s="34">
+        <f>IF($L44="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H44" s="5">
-        <f>IF($B44="","",风险登记册!R27)</f>
-        <v/>
-      </c>
-      <c r="I44" s="33">
-        <f>IF($B44="","",风险登记册!T27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I44" s="34">
+        <f>IF($L44="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J44" s="5">
-        <f>IF($B44="","",风险登记册!U27)</f>
+        <f>IF($L44="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L44,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K44" s="5">
-        <f>IF($B44="","",IF($J44="极高","每年必审",IF($J44="高","每年审计",IF($J44="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L44="","",IF($J44="极高","每年必审",IF($J44="高","每年审计",IF($J44="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L44" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L44)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5">
-        <f>IF($B45="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I45)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I45,风险登记册!$A$4:$A$203,"&lt;"&amp;$B45)+1)</f>
+        <f>IF($L45="","",ROWS($A$21:A45))</f>
         <v/>
       </c>
       <c r="B45" s="5">
-        <f>IF($B45="","",风险登记册!A28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C45" s="6">
-        <f>IF($B45="","",风险登记册!B28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D45" s="6">
-        <f>IF($B45="","",风险登记册!C28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E45" s="6">
-        <f>IF($B45="","",风险登记册!E28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F45" s="5">
-        <f>IF($B45="","",风险登记册!G28)</f>
-        <v/>
-      </c>
-      <c r="G45" s="33">
-        <f>IF($B45="","",风险登记册!Q28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G45" s="34">
+        <f>IF($L45="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H45" s="5">
-        <f>IF($B45="","",风险登记册!R28)</f>
-        <v/>
-      </c>
-      <c r="I45" s="33">
-        <f>IF($B45="","",风险登记册!T28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I45" s="34">
+        <f>IF($L45="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J45" s="5">
-        <f>IF($B45="","",风险登记册!U28)</f>
+        <f>IF($L45="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L45,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K45" s="5">
-        <f>IF($B45="","",IF($J45="极高","每年必审",IF($J45="高","每年审计",IF($J45="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L45="","",IF($J45="极高","每年必审",IF($J45="高","每年审计",IF($J45="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L45" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L45)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5">
-        <f>IF($B46="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I46)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I46,风险登记册!$A$4:$A$203,"&lt;"&amp;$B46)+1)</f>
+        <f>IF($L46="","",ROWS($A$21:A46))</f>
         <v/>
       </c>
       <c r="B46" s="5">
-        <f>IF($B46="","",风险登记册!A29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C46" s="6">
-        <f>IF($B46="","",风险登记册!B29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D46" s="6">
-        <f>IF($B46="","",风险登记册!C29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E46" s="6">
-        <f>IF($B46="","",风险登记册!E29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F46" s="5">
-        <f>IF($B46="","",风险登记册!G29)</f>
-        <v/>
-      </c>
-      <c r="G46" s="33">
-        <f>IF($B46="","",风险登记册!Q29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G46" s="34">
+        <f>IF($L46="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H46" s="5">
-        <f>IF($B46="","",风险登记册!R29)</f>
-        <v/>
-      </c>
-      <c r="I46" s="33">
-        <f>IF($B46="","",风险登记册!T29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I46" s="34">
+        <f>IF($L46="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J46" s="5">
-        <f>IF($B46="","",风险登记册!U29)</f>
+        <f>IF($L46="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L46,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K46" s="5">
-        <f>IF($B46="","",IF($J46="极高","每年必审",IF($J46="高","每年审计",IF($J46="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L46="","",IF($J46="极高","每年必审",IF($J46="高","每年审计",IF($J46="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L46" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L46)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5">
-        <f>IF($B47="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I47)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I47,风险登记册!$A$4:$A$203,"&lt;"&amp;$B47)+1)</f>
+        <f>IF($L47="","",ROWS($A$21:A47))</f>
         <v/>
       </c>
       <c r="B47" s="5">
-        <f>IF($B47="","",风险登记册!A30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C47" s="6">
-        <f>IF($B47="","",风险登记册!B30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D47" s="6">
-        <f>IF($B47="","",风险登记册!C30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E47" s="6">
-        <f>IF($B47="","",风险登记册!E30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F47" s="5">
-        <f>IF($B47="","",风险登记册!G30)</f>
-        <v/>
-      </c>
-      <c r="G47" s="33">
-        <f>IF($B47="","",风险登记册!Q30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G47" s="34">
+        <f>IF($L47="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H47" s="5">
-        <f>IF($B47="","",风险登记册!R30)</f>
-        <v/>
-      </c>
-      <c r="I47" s="33">
-        <f>IF($B47="","",风险登记册!T30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I47" s="34">
+        <f>IF($L47="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J47" s="5">
-        <f>IF($B47="","",风险登记册!U30)</f>
+        <f>IF($L47="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L47,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K47" s="5">
-        <f>IF($B47="","",IF($J47="极高","每年必审",IF($J47="高","每年审计",IF($J47="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L47="","",IF($J47="极高","每年必审",IF($J47="高","每年审计",IF($J47="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L47" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L47)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5">
-        <f>IF($B48="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I48)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I48,风险登记册!$A$4:$A$203,"&lt;"&amp;$B48)+1)</f>
+        <f>IF($L48="","",ROWS($A$21:A48))</f>
         <v/>
       </c>
       <c r="B48" s="5">
-        <f>IF($B48="","",风险登记册!A31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C48" s="6">
-        <f>IF($B48="","",风险登记册!B31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D48" s="6">
-        <f>IF($B48="","",风险登记册!C31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E48" s="6">
-        <f>IF($B48="","",风险登记册!E31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F48" s="5">
-        <f>IF($B48="","",风险登记册!G31)</f>
-        <v/>
-      </c>
-      <c r="G48" s="33">
-        <f>IF($B48="","",风险登记册!Q31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G48" s="34">
+        <f>IF($L48="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H48" s="5">
-        <f>IF($B48="","",风险登记册!R31)</f>
-        <v/>
-      </c>
-      <c r="I48" s="33">
-        <f>IF($B48="","",风险登记册!T31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I48" s="34">
+        <f>IF($L48="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J48" s="5">
-        <f>IF($B48="","",风险登记册!U31)</f>
+        <f>IF($L48="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L48,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K48" s="5">
-        <f>IF($B48="","",IF($J48="极高","每年必审",IF($J48="高","每年审计",IF($J48="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L48="","",IF($J48="极高","每年必审",IF($J48="高","每年审计",IF($J48="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L48" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L48)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5">
-        <f>IF($B49="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I49)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I49,风险登记册!$A$4:$A$203,"&lt;"&amp;$B49)+1)</f>
+        <f>IF($L49="","",ROWS($A$21:A49))</f>
         <v/>
       </c>
       <c r="B49" s="5">
-        <f>IF($B49="","",风险登记册!A32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C49" s="6">
-        <f>IF($B49="","",风险登记册!B32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D49" s="6">
-        <f>IF($B49="","",风险登记册!C32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E49" s="6">
-        <f>IF($B49="","",风险登记册!E32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F49" s="5">
-        <f>IF($B49="","",风险登记册!G32)</f>
-        <v/>
-      </c>
-      <c r="G49" s="33">
-        <f>IF($B49="","",风险登记册!Q32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G49" s="34">
+        <f>IF($L49="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H49" s="5">
-        <f>IF($B49="","",风险登记册!R32)</f>
-        <v/>
-      </c>
-      <c r="I49" s="33">
-        <f>IF($B49="","",风险登记册!T32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I49" s="34">
+        <f>IF($L49="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J49" s="5">
-        <f>IF($B49="","",风险登记册!U32)</f>
+        <f>IF($L49="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L49,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K49" s="5">
-        <f>IF($B49="","",IF($J49="极高","每年必审",IF($J49="高","每年审计",IF($J49="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L49="","",IF($J49="极高","每年必审",IF($J49="高","每年审计",IF($J49="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L49" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L49)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5">
-        <f>IF($B50="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I50)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I50,风险登记册!$A$4:$A$203,"&lt;"&amp;$B50)+1)</f>
+        <f>IF($L50="","",ROWS($A$21:A50))</f>
         <v/>
       </c>
       <c r="B50" s="5">
-        <f>IF($B50="","",风险登记册!A33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C50" s="6">
-        <f>IF($B50="","",风险登记册!B33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D50" s="6">
-        <f>IF($B50="","",风险登记册!C33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E50" s="6">
-        <f>IF($B50="","",风险登记册!E33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F50" s="5">
-        <f>IF($B50="","",风险登记册!G33)</f>
-        <v/>
-      </c>
-      <c r="G50" s="33">
-        <f>IF($B50="","",风险登记册!Q33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G50" s="34">
+        <f>IF($L50="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H50" s="5">
-        <f>IF($B50="","",风险登记册!R33)</f>
-        <v/>
-      </c>
-      <c r="I50" s="33">
-        <f>IF($B50="","",风险登记册!T33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I50" s="34">
+        <f>IF($L50="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J50" s="5">
-        <f>IF($B50="","",风险登记册!U33)</f>
+        <f>IF($L50="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L50,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K50" s="5">
-        <f>IF($B50="","",IF($J50="极高","每年必审",IF($J50="高","每年审计",IF($J50="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L50="","",IF($J50="极高","每年必审",IF($J50="高","每年审计",IF($J50="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L50" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L50)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5">
-        <f>IF($B51="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I51)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I51,风险登记册!$A$4:$A$203,"&lt;"&amp;$B51)+1)</f>
+        <f>IF($L51="","",ROWS($A$21:A51))</f>
         <v/>
       </c>
       <c r="B51" s="5">
-        <f>IF($B51="","",风险登记册!A34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C51" s="6">
-        <f>IF($B51="","",风险登记册!B34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D51" s="6">
-        <f>IF($B51="","",风险登记册!C34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E51" s="6">
-        <f>IF($B51="","",风险登记册!E34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F51" s="5">
-        <f>IF($B51="","",风险登记册!G34)</f>
-        <v/>
-      </c>
-      <c r="G51" s="33">
-        <f>IF($B51="","",风险登记册!Q34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G51" s="34">
+        <f>IF($L51="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H51" s="5">
-        <f>IF($B51="","",风险登记册!R34)</f>
-        <v/>
-      </c>
-      <c r="I51" s="33">
-        <f>IF($B51="","",风险登记册!T34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I51" s="34">
+        <f>IF($L51="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J51" s="5">
-        <f>IF($B51="","",风险登记册!U34)</f>
+        <f>IF($L51="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L51,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K51" s="5">
-        <f>IF($B51="","",IF($J51="极高","每年必审",IF($J51="高","每年审计",IF($J51="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L51="","",IF($J51="极高","每年必审",IF($J51="高","每年审计",IF($J51="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L51" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L51)),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5">
-        <f>IF($B52="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I52)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I52,风险登记册!$A$4:$A$203,"&lt;"&amp;$B52)+1)</f>
+        <f>IF($L52="","",ROWS($A$21:A52))</f>
         <v/>
       </c>
       <c r="B52" s="5">
-        <f>IF($B52="","",风险登记册!A35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C52" s="6">
-        <f>IF($B52="","",风险登记册!B35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D52" s="6">
-        <f>IF($B52="","",风险登记册!C35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E52" s="6">
-        <f>IF($B52="","",风险登记册!E35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F52" s="5">
-        <f>IF($B52="","",风险登记册!G35)</f>
-        <v/>
-      </c>
-      <c r="G52" s="33">
-        <f>IF($B52="","",风险登记册!Q35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G52" s="34">
+        <f>IF($L52="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H52" s="5">
-        <f>IF($B52="","",风险登记册!R35)</f>
-        <v/>
-      </c>
-      <c r="I52" s="33">
-        <f>IF($B52="","",风险登记册!T35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I52" s="34">
+        <f>IF($L52="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J52" s="5">
-        <f>IF($B52="","",风险登记册!U35)</f>
+        <f>IF($L52="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L52,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K52" s="5">
-        <f>IF($B52="","",IF($J52="极高","每年必审",IF($J52="高","每年审计",IF($J52="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L52="","",IF($J52="极高","每年必审",IF($J52="高","每年审计",IF($J52="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L52" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L52)),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5">
-        <f>IF($B53="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I53)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I53,风险登记册!$A$4:$A$203,"&lt;"&amp;$B53)+1)</f>
+        <f>IF($L53="","",ROWS($A$21:A53))</f>
         <v/>
       </c>
       <c r="B53" s="5">
-        <f>IF($B53="","",风险登记册!A36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C53" s="6">
-        <f>IF($B53="","",风险登记册!B36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D53" s="6">
-        <f>IF($B53="","",风险登记册!C36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E53" s="6">
-        <f>IF($B53="","",风险登记册!E36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F53" s="5">
-        <f>IF($B53="","",风险登记册!G36)</f>
-        <v/>
-      </c>
-      <c r="G53" s="33">
-        <f>IF($B53="","",风险登记册!Q36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G53" s="34">
+        <f>IF($L53="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H53" s="5">
-        <f>IF($B53="","",风险登记册!R36)</f>
-        <v/>
-      </c>
-      <c r="I53" s="33">
-        <f>IF($B53="","",风险登记册!T36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I53" s="34">
+        <f>IF($L53="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J53" s="5">
-        <f>IF($B53="","",风险登记册!U36)</f>
+        <f>IF($L53="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L53,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K53" s="5">
-        <f>IF($B53="","",IF($J53="极高","每年必审",IF($J53="高","每年审计",IF($J53="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L53="","",IF($J53="极高","每年必审",IF($J53="高","每年审计",IF($J53="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L53" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L53)),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5">
-        <f>IF($B54="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I54)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I54,风险登记册!$A$4:$A$203,"&lt;"&amp;$B54)+1)</f>
+        <f>IF($L54="","",ROWS($A$21:A54))</f>
         <v/>
       </c>
       <c r="B54" s="5">
-        <f>IF($B54="","",风险登记册!A37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C54" s="6">
-        <f>IF($B54="","",风险登记册!B37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D54" s="6">
-        <f>IF($B54="","",风险登记册!C37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E54" s="6">
-        <f>IF($B54="","",风险登记册!E37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F54" s="5">
-        <f>IF($B54="","",风险登记册!G37)</f>
-        <v/>
-      </c>
-      <c r="G54" s="33">
-        <f>IF($B54="","",风险登记册!Q37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G54" s="34">
+        <f>IF($L54="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H54" s="5">
-        <f>IF($B54="","",风险登记册!R37)</f>
-        <v/>
-      </c>
-      <c r="I54" s="33">
-        <f>IF($B54="","",风险登记册!T37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I54" s="34">
+        <f>IF($L54="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J54" s="5">
-        <f>IF($B54="","",风险登记册!U37)</f>
+        <f>IF($L54="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L54,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K54" s="5">
-        <f>IF($B54="","",IF($J54="极高","每年必审",IF($J54="高","每年审计",IF($J54="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L54="","",IF($J54="极高","每年必审",IF($J54="高","每年审计",IF($J54="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L54" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L54)),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5">
-        <f>IF($B55="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I55)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I55,风险登记册!$A$4:$A$203,"&lt;"&amp;$B55)+1)</f>
+        <f>IF($L55="","",ROWS($A$21:A55))</f>
         <v/>
       </c>
       <c r="B55" s="5">
-        <f>IF($B55="","",风险登记册!A38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C55" s="6">
-        <f>IF($B55="","",风险登记册!B38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D55" s="6">
-        <f>IF($B55="","",风险登记册!C38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E55" s="6">
-        <f>IF($B55="","",风险登记册!E38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F55" s="5">
-        <f>IF($B55="","",风险登记册!G38)</f>
-        <v/>
-      </c>
-      <c r="G55" s="33">
-        <f>IF($B55="","",风险登记册!Q38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G55" s="34">
+        <f>IF($L55="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H55" s="5">
-        <f>IF($B55="","",风险登记册!R38)</f>
-        <v/>
-      </c>
-      <c r="I55" s="33">
-        <f>IF($B55="","",风险登记册!T38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I55" s="34">
+        <f>IF($L55="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J55" s="5">
-        <f>IF($B55="","",风险登记册!U38)</f>
+        <f>IF($L55="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L55,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K55" s="5">
-        <f>IF($B55="","",IF($J55="极高","每年必审",IF($J55="高","每年审计",IF($J55="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L55="","",IF($J55="极高","每年必审",IF($J55="高","每年审计",IF($J55="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L55" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L55)),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5">
-        <f>IF($B56="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I56)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I56,风险登记册!$A$4:$A$203,"&lt;"&amp;$B56)+1)</f>
+        <f>IF($L56="","",ROWS($A$21:A56))</f>
         <v/>
       </c>
       <c r="B56" s="5">
-        <f>IF($B56="","",风险登记册!A39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C56" s="6">
-        <f>IF($B56="","",风险登记册!B39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D56" s="6">
-        <f>IF($B56="","",风险登记册!C39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E56" s="6">
-        <f>IF($B56="","",风险登记册!E39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F56" s="5">
-        <f>IF($B56="","",风险登记册!G39)</f>
-        <v/>
-      </c>
-      <c r="G56" s="33">
-        <f>IF($B56="","",风险登记册!Q39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G56" s="34">
+        <f>IF($L56="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H56" s="5">
-        <f>IF($B56="","",风险登记册!R39)</f>
-        <v/>
-      </c>
-      <c r="I56" s="33">
-        <f>IF($B56="","",风险登记册!T39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I56" s="34">
+        <f>IF($L56="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J56" s="5">
-        <f>IF($B56="","",风险登记册!U39)</f>
+        <f>IF($L56="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L56,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K56" s="5">
-        <f>IF($B56="","",IF($J56="极高","每年必审",IF($J56="高","每年审计",IF($J56="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L56="","",IF($J56="极高","每年必审",IF($J56="高","每年审计",IF($J56="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L56" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L56)),"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5">
-        <f>IF($B57="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I57)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I57,风险登记册!$A$4:$A$203,"&lt;"&amp;$B57)+1)</f>
+        <f>IF($L57="","",ROWS($A$21:A57))</f>
         <v/>
       </c>
       <c r="B57" s="5">
-        <f>IF($B57="","",风险登记册!A40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C57" s="6">
-        <f>IF($B57="","",风险登记册!B40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D57" s="6">
-        <f>IF($B57="","",风险登记册!C40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E57" s="6">
-        <f>IF($B57="","",风险登记册!E40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F57" s="5">
-        <f>IF($B57="","",风险登记册!G40)</f>
-        <v/>
-      </c>
-      <c r="G57" s="33">
-        <f>IF($B57="","",风险登记册!Q40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G57" s="34">
+        <f>IF($L57="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H57" s="5">
-        <f>IF($B57="","",风险登记册!R40)</f>
-        <v/>
-      </c>
-      <c r="I57" s="33">
-        <f>IF($B57="","",风险登记册!T40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I57" s="34">
+        <f>IF($L57="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J57" s="5">
-        <f>IF($B57="","",风险登记册!U40)</f>
+        <f>IF($L57="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L57,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K57" s="5">
-        <f>IF($B57="","",IF($J57="极高","每年必审",IF($J57="高","每年审计",IF($J57="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L57="","",IF($J57="极高","每年必审",IF($J57="高","每年审计",IF($J57="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L57" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L57)),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5">
-        <f>IF($B58="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I58)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I58,风险登记册!$A$4:$A$203,"&lt;"&amp;$B58)+1)</f>
+        <f>IF($L58="","",ROWS($A$21:A58))</f>
         <v/>
       </c>
       <c r="B58" s="5">
-        <f>IF($B58="","",风险登记册!A41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C58" s="6">
-        <f>IF($B58="","",风险登记册!B41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D58" s="6">
-        <f>IF($B58="","",风险登记册!C41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E58" s="6">
-        <f>IF($B58="","",风险登记册!E41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F58" s="5">
-        <f>IF($B58="","",风险登记册!G41)</f>
-        <v/>
-      </c>
-      <c r="G58" s="33">
-        <f>IF($B58="","",风险登记册!Q41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G58" s="34">
+        <f>IF($L58="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H58" s="5">
-        <f>IF($B58="","",风险登记册!R41)</f>
-        <v/>
-      </c>
-      <c r="I58" s="33">
-        <f>IF($B58="","",风险登记册!T41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I58" s="34">
+        <f>IF($L58="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J58" s="5">
-        <f>IF($B58="","",风险登记册!U41)</f>
+        <f>IF($L58="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L58,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K58" s="5">
-        <f>IF($B58="","",IF($J58="极高","每年必审",IF($J58="高","每年审计",IF($J58="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L58="","",IF($J58="极高","每年必审",IF($J58="高","每年审计",IF($J58="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L58" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L58)),"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5">
-        <f>IF($B59="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I59)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I59,风险登记册!$A$4:$A$203,"&lt;"&amp;$B59)+1)</f>
+        <f>IF($L59="","",ROWS($A$21:A59))</f>
         <v/>
       </c>
       <c r="B59" s="5">
-        <f>IF($B59="","",风险登记册!A42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C59" s="6">
-        <f>IF($B59="","",风险登记册!B42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D59" s="6">
-        <f>IF($B59="","",风险登记册!C42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E59" s="6">
-        <f>IF($B59="","",风险登记册!E42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F59" s="5">
-        <f>IF($B59="","",风险登记册!G42)</f>
-        <v/>
-      </c>
-      <c r="G59" s="33">
-        <f>IF($B59="","",风险登记册!Q42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G59" s="34">
+        <f>IF($L59="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H59" s="5">
-        <f>IF($B59="","",风险登记册!R42)</f>
-        <v/>
-      </c>
-      <c r="I59" s="33">
-        <f>IF($B59="","",风险登记册!T42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I59" s="34">
+        <f>IF($L59="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J59" s="5">
-        <f>IF($B59="","",风险登记册!U42)</f>
+        <f>IF($L59="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L59,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K59" s="5">
-        <f>IF($B59="","",IF($J59="极高","每年必审",IF($J59="高","每年审计",IF($J59="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L59="","",IF($J59="极高","每年必审",IF($J59="高","每年审计",IF($J59="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L59" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L59)),"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5">
-        <f>IF($B60="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I60)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I60,风险登记册!$A$4:$A$203,"&lt;"&amp;$B60)+1)</f>
+        <f>IF($L60="","",ROWS($A$21:A60))</f>
         <v/>
       </c>
       <c r="B60" s="5">
-        <f>IF($B60="","",风险登记册!A43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C60" s="6">
-        <f>IF($B60="","",风险登记册!B43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D60" s="6">
-        <f>IF($B60="","",风险登记册!C43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E60" s="6">
-        <f>IF($B60="","",风险登记册!E43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F60" s="5">
-        <f>IF($B60="","",风险登记册!G43)</f>
-        <v/>
-      </c>
-      <c r="G60" s="33">
-        <f>IF($B60="","",风险登记册!Q43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G60" s="34">
+        <f>IF($L60="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H60" s="5">
-        <f>IF($B60="","",风险登记册!R43)</f>
-        <v/>
-      </c>
-      <c r="I60" s="33">
-        <f>IF($B60="","",风险登记册!T43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I60" s="34">
+        <f>IF($L60="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J60" s="5">
-        <f>IF($B60="","",风险登记册!U43)</f>
+        <f>IF($L60="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L60,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K60" s="5">
-        <f>IF($B60="","",IF($J60="极高","每年必审",IF($J60="高","每年审计",IF($J60="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L60="","",IF($J60="极高","每年必审",IF($J60="高","每年审计",IF($J60="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L60" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L60)),"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5">
-        <f>IF($B61="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I61)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I61,风险登记册!$A$4:$A$203,"&lt;"&amp;$B61)+1)</f>
+        <f>IF($L61="","",ROWS($A$21:A61))</f>
         <v/>
       </c>
       <c r="B61" s="5">
-        <f>IF($B61="","",风险登记册!A44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C61" s="6">
-        <f>IF($B61="","",风险登记册!B44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D61" s="6">
-        <f>IF($B61="","",风险登记册!C44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E61" s="6">
-        <f>IF($B61="","",风险登记册!E44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F61" s="5">
-        <f>IF($B61="","",风险登记册!G44)</f>
-        <v/>
-      </c>
-      <c r="G61" s="33">
-        <f>IF($B61="","",风险登记册!Q44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G61" s="34">
+        <f>IF($L61="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H61" s="5">
-        <f>IF($B61="","",风险登记册!R44)</f>
-        <v/>
-      </c>
-      <c r="I61" s="33">
-        <f>IF($B61="","",风险登记册!T44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I61" s="34">
+        <f>IF($L61="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J61" s="5">
-        <f>IF($B61="","",风险登记册!U44)</f>
+        <f>IF($L61="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L61,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K61" s="5">
-        <f>IF($B61="","",IF($J61="极高","每年必审",IF($J61="高","每年审计",IF($J61="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L61="","",IF($J61="极高","每年必审",IF($J61="高","每年审计",IF($J61="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L61" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L61)),"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5">
-        <f>IF($B62="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I62)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I62,风险登记册!$A$4:$A$203,"&lt;"&amp;$B62)+1)</f>
+        <f>IF($L62="","",ROWS($A$21:A62))</f>
         <v/>
       </c>
       <c r="B62" s="5">
-        <f>IF($B62="","",风险登记册!A45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C62" s="6">
-        <f>IF($B62="","",风险登记册!B45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D62" s="6">
-        <f>IF($B62="","",风险登记册!C45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E62" s="6">
-        <f>IF($B62="","",风险登记册!E45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F62" s="5">
-        <f>IF($B62="","",风险登记册!G45)</f>
-        <v/>
-      </c>
-      <c r="G62" s="33">
-        <f>IF($B62="","",风险登记册!Q45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G62" s="34">
+        <f>IF($L62="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H62" s="5">
-        <f>IF($B62="","",风险登记册!R45)</f>
-        <v/>
-      </c>
-      <c r="I62" s="33">
-        <f>IF($B62="","",风险登记册!T45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I62" s="34">
+        <f>IF($L62="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J62" s="5">
-        <f>IF($B62="","",风险登记册!U45)</f>
+        <f>IF($L62="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L62,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K62" s="5">
-        <f>IF($B62="","",IF($J62="极高","每年必审",IF($J62="高","每年审计",IF($J62="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L62="","",IF($J62="极高","每年必审",IF($J62="高","每年审计",IF($J62="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L62" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L62)),"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5">
-        <f>IF($B63="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I63)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I63,风险登记册!$A$4:$A$203,"&lt;"&amp;$B63)+1)</f>
+        <f>IF($L63="","",ROWS($A$21:A63))</f>
         <v/>
       </c>
       <c r="B63" s="5">
-        <f>IF($B63="","",风险登记册!A46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C63" s="6">
-        <f>IF($B63="","",风险登记册!B46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D63" s="6">
-        <f>IF($B63="","",风险登记册!C46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E63" s="6">
-        <f>IF($B63="","",风险登记册!E46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F63" s="5">
-        <f>IF($B63="","",风险登记册!G46)</f>
-        <v/>
-      </c>
-      <c r="G63" s="33">
-        <f>IF($B63="","",风险登记册!Q46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G63" s="34">
+        <f>IF($L63="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H63" s="5">
-        <f>IF($B63="","",风险登记册!R46)</f>
-        <v/>
-      </c>
-      <c r="I63" s="33">
-        <f>IF($B63="","",风险登记册!T46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I63" s="34">
+        <f>IF($L63="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J63" s="5">
-        <f>IF($B63="","",风险登记册!U46)</f>
+        <f>IF($L63="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L63,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K63" s="5">
-        <f>IF($B63="","",IF($J63="极高","每年必审",IF($J63="高","每年审计",IF($J63="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L63="","",IF($J63="极高","每年必审",IF($J63="高","每年审计",IF($J63="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L63" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L63)),"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5">
-        <f>IF($B64="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I64)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I64,风险登记册!$A$4:$A$203,"&lt;"&amp;$B64)+1)</f>
+        <f>IF($L64="","",ROWS($A$21:A64))</f>
         <v/>
       </c>
       <c r="B64" s="5">
-        <f>IF($B64="","",风险登记册!A47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C64" s="6">
-        <f>IF($B64="","",风险登记册!B47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D64" s="6">
-        <f>IF($B64="","",风险登记册!C47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E64" s="6">
-        <f>IF($B64="","",风险登记册!E47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F64" s="5">
-        <f>IF($B64="","",风险登记册!G47)</f>
-        <v/>
-      </c>
-      <c r="G64" s="33">
-        <f>IF($B64="","",风险登记册!Q47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G64" s="34">
+        <f>IF($L64="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H64" s="5">
-        <f>IF($B64="","",风险登记册!R47)</f>
-        <v/>
-      </c>
-      <c r="I64" s="33">
-        <f>IF($B64="","",风险登记册!T47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I64" s="34">
+        <f>IF($L64="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J64" s="5">
-        <f>IF($B64="","",风险登记册!U47)</f>
+        <f>IF($L64="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L64,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K64" s="5">
-        <f>IF($B64="","",IF($J64="极高","每年必审",IF($J64="高","每年审计",IF($J64="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L64="","",IF($J64="极高","每年必审",IF($J64="高","每年审计",IF($J64="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L64" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L64)),"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5">
-        <f>IF($B65="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I65)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I65,风险登记册!$A$4:$A$203,"&lt;"&amp;$B65)+1)</f>
+        <f>IF($L65="","",ROWS($A$21:A65))</f>
         <v/>
       </c>
       <c r="B65" s="5">
-        <f>IF($B65="","",风险登记册!A48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C65" s="6">
-        <f>IF($B65="","",风险登记册!B48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D65" s="6">
-        <f>IF($B65="","",风险登记册!C48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E65" s="6">
-        <f>IF($B65="","",风险登记册!E48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F65" s="5">
-        <f>IF($B65="","",风险登记册!G48)</f>
-        <v/>
-      </c>
-      <c r="G65" s="33">
-        <f>IF($B65="","",风险登记册!Q48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G65" s="34">
+        <f>IF($L65="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H65" s="5">
-        <f>IF($B65="","",风险登记册!R48)</f>
-        <v/>
-      </c>
-      <c r="I65" s="33">
-        <f>IF($B65="","",风险登记册!T48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I65" s="34">
+        <f>IF($L65="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J65" s="5">
-        <f>IF($B65="","",风险登记册!U48)</f>
+        <f>IF($L65="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L65,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K65" s="5">
-        <f>IF($B65="","",IF($J65="极高","每年必审",IF($J65="高","每年审计",IF($J65="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L65="","",IF($J65="极高","每年必审",IF($J65="高","每年审计",IF($J65="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L65" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L65)),"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5">
-        <f>IF($B66="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I66)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I66,风险登记册!$A$4:$A$203,"&lt;"&amp;$B66)+1)</f>
+        <f>IF($L66="","",ROWS($A$21:A66))</f>
         <v/>
       </c>
       <c r="B66" s="5">
-        <f>IF($B66="","",风险登记册!A49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C66" s="6">
-        <f>IF($B66="","",风险登记册!B49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D66" s="6">
-        <f>IF($B66="","",风险登记册!C49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E66" s="6">
-        <f>IF($B66="","",风险登记册!E49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F66" s="5">
-        <f>IF($B66="","",风险登记册!G49)</f>
-        <v/>
-      </c>
-      <c r="G66" s="33">
-        <f>IF($B66="","",风险登记册!Q49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G66" s="34">
+        <f>IF($L66="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H66" s="5">
-        <f>IF($B66="","",风险登记册!R49)</f>
-        <v/>
-      </c>
-      <c r="I66" s="33">
-        <f>IF($B66="","",风险登记册!T49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I66" s="34">
+        <f>IF($L66="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J66" s="5">
-        <f>IF($B66="","",风险登记册!U49)</f>
+        <f>IF($L66="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L66,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K66" s="5">
-        <f>IF($B66="","",IF($J66="极高","每年必审",IF($J66="高","每年审计",IF($J66="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L66="","",IF($J66="极高","每年必审",IF($J66="高","每年审计",IF($J66="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L66" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L66)),"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5">
-        <f>IF($B67="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I67)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I67,风险登记册!$A$4:$A$203,"&lt;"&amp;$B67)+1)</f>
+        <f>IF($L67="","",ROWS($A$21:A67))</f>
         <v/>
       </c>
       <c r="B67" s="5">
-        <f>IF($B67="","",风险登记册!A50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C67" s="6">
-        <f>IF($B67="","",风险登记册!B50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D67" s="6">
-        <f>IF($B67="","",风险登记册!C50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E67" s="6">
-        <f>IF($B67="","",风险登记册!E50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F67" s="5">
-        <f>IF($B67="","",风险登记册!G50)</f>
-        <v/>
-      </c>
-      <c r="G67" s="33">
-        <f>IF($B67="","",风险登记册!Q50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G67" s="34">
+        <f>IF($L67="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H67" s="5">
-        <f>IF($B67="","",风险登记册!R50)</f>
-        <v/>
-      </c>
-      <c r="I67" s="33">
-        <f>IF($B67="","",风险登记册!T50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I67" s="34">
+        <f>IF($L67="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J67" s="5">
-        <f>IF($B67="","",风险登记册!U50)</f>
+        <f>IF($L67="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L67,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K67" s="5">
-        <f>IF($B67="","",IF($J67="极高","每年必审",IF($J67="高","每年审计",IF($J67="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L67="","",IF($J67="极高","每年必审",IF($J67="高","每年审计",IF($J67="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L67" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L67)),"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5">
-        <f>IF($B68="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I68)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I68,风险登记册!$A$4:$A$203,"&lt;"&amp;$B68)+1)</f>
+        <f>IF($L68="","",ROWS($A$21:A68))</f>
         <v/>
       </c>
       <c r="B68" s="5">
-        <f>IF($B68="","",风险登记册!A51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C68" s="6">
-        <f>IF($B68="","",风险登记册!B51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D68" s="6">
-        <f>IF($B68="","",风险登记册!C51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E68" s="6">
-        <f>IF($B68="","",风险登记册!E51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F68" s="5">
-        <f>IF($B68="","",风险登记册!G51)</f>
-        <v/>
-      </c>
-      <c r="G68" s="33">
-        <f>IF($B68="","",风险登记册!Q51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G68" s="34">
+        <f>IF($L68="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H68" s="5">
-        <f>IF($B68="","",风险登记册!R51)</f>
-        <v/>
-      </c>
-      <c r="I68" s="33">
-        <f>IF($B68="","",风险登记册!T51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I68" s="34">
+        <f>IF($L68="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J68" s="5">
-        <f>IF($B68="","",风险登记册!U51)</f>
+        <f>IF($L68="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L68,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K68" s="5">
-        <f>IF($B68="","",IF($J68="极高","每年必审",IF($J68="高","每年审计",IF($J68="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L68="","",IF($J68="极高","每年必审",IF($J68="高","每年审计",IF($J68="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L68" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L68)),"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5">
-        <f>IF($B69="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I69)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I69,风险登记册!$A$4:$A$203,"&lt;"&amp;$B69)+1)</f>
+        <f>IF($L69="","",ROWS($A$21:A69))</f>
         <v/>
       </c>
       <c r="B69" s="5">
-        <f>IF($B69="","",风险登记册!A52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C69" s="6">
-        <f>IF($B69="","",风险登记册!B52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D69" s="6">
-        <f>IF($B69="","",风险登记册!C52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E69" s="6">
-        <f>IF($B69="","",风险登记册!E52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F69" s="5">
-        <f>IF($B69="","",风险登记册!G52)</f>
-        <v/>
-      </c>
-      <c r="G69" s="33">
-        <f>IF($B69="","",风险登记册!Q52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G69" s="34">
+        <f>IF($L69="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H69" s="5">
-        <f>IF($B69="","",风险登记册!R52)</f>
-        <v/>
-      </c>
-      <c r="I69" s="33">
-        <f>IF($B69="","",风险登记册!T52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I69" s="34">
+        <f>IF($L69="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J69" s="5">
-        <f>IF($B69="","",风险登记册!U52)</f>
+        <f>IF($L69="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L69,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K69" s="5">
-        <f>IF($B69="","",IF($J69="极高","每年必审",IF($J69="高","每年审计",IF($J69="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L69="","",IF($J69="极高","每年必审",IF($J69="高","每年审计",IF($J69="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L69" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L69)),"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5">
-        <f>IF($B70="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I70)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I70,风险登记册!$A$4:$A$203,"&lt;"&amp;$B70)+1)</f>
+        <f>IF($L70="","",ROWS($A$21:A70))</f>
         <v/>
       </c>
       <c r="B70" s="5">
-        <f>IF($B70="","",风险登记册!A53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C70" s="6">
-        <f>IF($B70="","",风险登记册!B53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D70" s="6">
-        <f>IF($B70="","",风险登记册!C53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E70" s="6">
-        <f>IF($B70="","",风险登记册!E53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F70" s="5">
-        <f>IF($B70="","",风险登记册!G53)</f>
-        <v/>
-      </c>
-      <c r="G70" s="33">
-        <f>IF($B70="","",风险登记册!Q53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G70" s="34">
+        <f>IF($L70="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H70" s="5">
-        <f>IF($B70="","",风险登记册!R53)</f>
-        <v/>
-      </c>
-      <c r="I70" s="33">
-        <f>IF($B70="","",风险登记册!T53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I70" s="34">
+        <f>IF($L70="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J70" s="5">
-        <f>IF($B70="","",风险登记册!U53)</f>
+        <f>IF($L70="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L70,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K70" s="5">
-        <f>IF($B70="","",IF($J70="极高","每年必审",IF($J70="高","每年审计",IF($J70="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L70="","",IF($J70="极高","每年必审",IF($J70="高","每年审计",IF($J70="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L70" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L70)),"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5">
-        <f>IF($B71="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I71)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I71,风险登记册!$A$4:$A$203,"&lt;"&amp;$B71)+1)</f>
+        <f>IF($L71="","",ROWS($A$21:A71))</f>
         <v/>
       </c>
       <c r="B71" s="5">
-        <f>IF($B71="","",风险登记册!A54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C71" s="6">
-        <f>IF($B71="","",风险登记册!B54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D71" s="6">
-        <f>IF($B71="","",风险登记册!C54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E71" s="6">
-        <f>IF($B71="","",风险登记册!E54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F71" s="5">
-        <f>IF($B71="","",风险登记册!G54)</f>
-        <v/>
-      </c>
-      <c r="G71" s="33">
-        <f>IF($B71="","",风险登记册!Q54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G71" s="34">
+        <f>IF($L71="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H71" s="5">
-        <f>IF($B71="","",风险登记册!R54)</f>
-        <v/>
-      </c>
-      <c r="I71" s="33">
-        <f>IF($B71="","",风险登记册!T54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I71" s="34">
+        <f>IF($L71="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J71" s="5">
-        <f>IF($B71="","",风险登记册!U54)</f>
+        <f>IF($L71="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L71,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K71" s="5">
-        <f>IF($B71="","",IF($J71="极高","每年必审",IF($J71="高","每年审计",IF($J71="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L71="","",IF($J71="极高","每年必审",IF($J71="高","每年审计",IF($J71="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L71" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L71)),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5">
-        <f>IF($B72="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I72)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I72,风险登记册!$A$4:$A$203,"&lt;"&amp;$B72)+1)</f>
+        <f>IF($L72="","",ROWS($A$21:A72))</f>
         <v/>
       </c>
       <c r="B72" s="5">
-        <f>IF($B72="","",风险登记册!A55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C72" s="6">
-        <f>IF($B72="","",风险登记册!B55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D72" s="6">
-        <f>IF($B72="","",风险登记册!C55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E72" s="6">
-        <f>IF($B72="","",风险登记册!E55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F72" s="5">
-        <f>IF($B72="","",风险登记册!G55)</f>
-        <v/>
-      </c>
-      <c r="G72" s="33">
-        <f>IF($B72="","",风险登记册!Q55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G72" s="34">
+        <f>IF($L72="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H72" s="5">
-        <f>IF($B72="","",风险登记册!R55)</f>
-        <v/>
-      </c>
-      <c r="I72" s="33">
-        <f>IF($B72="","",风险登记册!T55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I72" s="34">
+        <f>IF($L72="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J72" s="5">
-        <f>IF($B72="","",风险登记册!U55)</f>
+        <f>IF($L72="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L72,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K72" s="5">
-        <f>IF($B72="","",IF($J72="极高","每年必审",IF($J72="高","每年审计",IF($J72="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L72="","",IF($J72="极高","每年必审",IF($J72="高","每年审计",IF($J72="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L72" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L72)),"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5">
-        <f>IF($B73="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I73)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I73,风险登记册!$A$4:$A$203,"&lt;"&amp;$B73)+1)</f>
+        <f>IF($L73="","",ROWS($A$21:A73))</f>
         <v/>
       </c>
       <c r="B73" s="5">
-        <f>IF($B73="","",风险登记册!A56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C73" s="6">
-        <f>IF($B73="","",风险登记册!B56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D73" s="6">
-        <f>IF($B73="","",风险登记册!C56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E73" s="6">
-        <f>IF($B73="","",风险登记册!E56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F73" s="5">
-        <f>IF($B73="","",风险登记册!G56)</f>
-        <v/>
-      </c>
-      <c r="G73" s="33">
-        <f>IF($B73="","",风险登记册!Q56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G73" s="34">
+        <f>IF($L73="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H73" s="5">
-        <f>IF($B73="","",风险登记册!R56)</f>
-        <v/>
-      </c>
-      <c r="I73" s="33">
-        <f>IF($B73="","",风险登记册!T56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I73" s="34">
+        <f>IF($L73="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J73" s="5">
-        <f>IF($B73="","",风险登记册!U56)</f>
+        <f>IF($L73="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L73,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K73" s="5">
-        <f>IF($B73="","",IF($J73="极高","每年必审",IF($J73="高","每年审计",IF($J73="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L73="","",IF($J73="极高","每年必审",IF($J73="高","每年审计",IF($J73="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L73" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L73)),"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5">
-        <f>IF($B74="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I74)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I74,风险登记册!$A$4:$A$203,"&lt;"&amp;$B74)+1)</f>
+        <f>IF($L74="","",ROWS($A$21:A74))</f>
         <v/>
       </c>
       <c r="B74" s="5">
-        <f>IF($B74="","",风险登记册!A57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C74" s="6">
-        <f>IF($B74="","",风险登记册!B57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D74" s="6">
-        <f>IF($B74="","",风险登记册!C57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E74" s="6">
-        <f>IF($B74="","",风险登记册!E57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F74" s="5">
-        <f>IF($B74="","",风险登记册!G57)</f>
-        <v/>
-      </c>
-      <c r="G74" s="33">
-        <f>IF($B74="","",风险登记册!Q57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G74" s="34">
+        <f>IF($L74="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H74" s="5">
-        <f>IF($B74="","",风险登记册!R57)</f>
-        <v/>
-      </c>
-      <c r="I74" s="33">
-        <f>IF($B74="","",风险登记册!T57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I74" s="34">
+        <f>IF($L74="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J74" s="5">
-        <f>IF($B74="","",风险登记册!U57)</f>
+        <f>IF($L74="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L74,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K74" s="5">
-        <f>IF($B74="","",IF($J74="极高","每年必审",IF($J74="高","每年审计",IF($J74="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L74="","",IF($J74="极高","每年必审",IF($J74="高","每年审计",IF($J74="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L74" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L74)),"")</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5">
-        <f>IF($B75="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I75)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I75,风险登记册!$A$4:$A$203,"&lt;"&amp;$B75)+1)</f>
+        <f>IF($L75="","",ROWS($A$21:A75))</f>
         <v/>
       </c>
       <c r="B75" s="5">
-        <f>IF($B75="","",风险登记册!A58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C75" s="6">
-        <f>IF($B75="","",风险登记册!B58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D75" s="6">
-        <f>IF($B75="","",风险登记册!C58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E75" s="6">
-        <f>IF($B75="","",风险登记册!E58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F75" s="5">
-        <f>IF($B75="","",风险登记册!G58)</f>
-        <v/>
-      </c>
-      <c r="G75" s="33">
-        <f>IF($B75="","",风险登记册!Q58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G75" s="34">
+        <f>IF($L75="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H75" s="5">
-        <f>IF($B75="","",风险登记册!R58)</f>
-        <v/>
-      </c>
-      <c r="I75" s="33">
-        <f>IF($B75="","",风险登记册!T58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I75" s="34">
+        <f>IF($L75="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J75" s="5">
-        <f>IF($B75="","",风险登记册!U58)</f>
+        <f>IF($L75="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L75,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K75" s="5">
-        <f>IF($B75="","",IF($J75="极高","每年必审",IF($J75="高","每年审计",IF($J75="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L75="","",IF($J75="极高","每年必审",IF($J75="高","每年审计",IF($J75="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L75" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L75)),"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5">
-        <f>IF($B76="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I76)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I76,风险登记册!$A$4:$A$203,"&lt;"&amp;$B76)+1)</f>
+        <f>IF($L76="","",ROWS($A$21:A76))</f>
         <v/>
       </c>
       <c r="B76" s="5">
-        <f>IF($B76="","",风险登记册!A59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C76" s="6">
-        <f>IF($B76="","",风险登记册!B59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D76" s="6">
-        <f>IF($B76="","",风险登记册!C59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E76" s="6">
-        <f>IF($B76="","",风险登记册!E59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F76" s="5">
-        <f>IF($B76="","",风险登记册!G59)</f>
-        <v/>
-      </c>
-      <c r="G76" s="33">
-        <f>IF($B76="","",风险登记册!Q59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G76" s="34">
+        <f>IF($L76="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H76" s="5">
-        <f>IF($B76="","",风险登记册!R59)</f>
-        <v/>
-      </c>
-      <c r="I76" s="33">
-        <f>IF($B76="","",风险登记册!T59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I76" s="34">
+        <f>IF($L76="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J76" s="5">
-        <f>IF($B76="","",风险登记册!U59)</f>
+        <f>IF($L76="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L76,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K76" s="5">
-        <f>IF($B76="","",IF($J76="极高","每年必审",IF($J76="高","每年审计",IF($J76="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L76="","",IF($J76="极高","每年必审",IF($J76="高","每年审计",IF($J76="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L76" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L76)),"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5">
-        <f>IF($B77="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I77)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I77,风险登记册!$A$4:$A$203,"&lt;"&amp;$B77)+1)</f>
+        <f>IF($L77="","",ROWS($A$21:A77))</f>
         <v/>
       </c>
       <c r="B77" s="5">
-        <f>IF($B77="","",风险登记册!A60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C77" s="6">
-        <f>IF($B77="","",风险登记册!B60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D77" s="6">
-        <f>IF($B77="","",风险登记册!C60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E77" s="6">
-        <f>IF($B77="","",风险登记册!E60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F77" s="5">
-        <f>IF($B77="","",风险登记册!G60)</f>
-        <v/>
-      </c>
-      <c r="G77" s="33">
-        <f>IF($B77="","",风险登记册!Q60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G77" s="34">
+        <f>IF($L77="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H77" s="5">
-        <f>IF($B77="","",风险登记册!R60)</f>
-        <v/>
-      </c>
-      <c r="I77" s="33">
-        <f>IF($B77="","",风险登记册!T60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I77" s="34">
+        <f>IF($L77="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J77" s="5">
-        <f>IF($B77="","",风险登记册!U60)</f>
+        <f>IF($L77="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L77,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K77" s="5">
-        <f>IF($B77="","",IF($J77="极高","每年必审",IF($J77="高","每年审计",IF($J77="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L77="","",IF($J77="极高","每年必审",IF($J77="高","每年审计",IF($J77="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L77" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L77)),"")</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5">
-        <f>IF($B78="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I78)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I78,风险登记册!$A$4:$A$203,"&lt;"&amp;$B78)+1)</f>
+        <f>IF($L78="","",ROWS($A$21:A78))</f>
         <v/>
       </c>
       <c r="B78" s="5">
-        <f>IF($B78="","",风险登记册!A61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C78" s="6">
-        <f>IF($B78="","",风险登记册!B61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D78" s="6">
-        <f>IF($B78="","",风险登记册!C61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E78" s="6">
-        <f>IF($B78="","",风险登记册!E61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F78" s="5">
-        <f>IF($B78="","",风险登记册!G61)</f>
-        <v/>
-      </c>
-      <c r="G78" s="33">
-        <f>IF($B78="","",风险登记册!Q61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G78" s="34">
+        <f>IF($L78="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H78" s="5">
-        <f>IF($B78="","",风险登记册!R61)</f>
-        <v/>
-      </c>
-      <c r="I78" s="33">
-        <f>IF($B78="","",风险登记册!T61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I78" s="34">
+        <f>IF($L78="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J78" s="5">
-        <f>IF($B78="","",风险登记册!U61)</f>
+        <f>IF($L78="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L78,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K78" s="5">
-        <f>IF($B78="","",IF($J78="极高","每年必审",IF($J78="高","每年审计",IF($J78="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L78="","",IF($J78="极高","每年必审",IF($J78="高","每年审计",IF($J78="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L78" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L78)),"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5">
-        <f>IF($B79="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I79)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I79,风险登记册!$A$4:$A$203,"&lt;"&amp;$B79)+1)</f>
+        <f>IF($L79="","",ROWS($A$21:A79))</f>
         <v/>
       </c>
       <c r="B79" s="5">
-        <f>IF($B79="","",风险登记册!A62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C79" s="6">
-        <f>IF($B79="","",风险登记册!B62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D79" s="6">
-        <f>IF($B79="","",风险登记册!C62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E79" s="6">
-        <f>IF($B79="","",风险登记册!E62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F79" s="5">
-        <f>IF($B79="","",风险登记册!G62)</f>
-        <v/>
-      </c>
-      <c r="G79" s="33">
-        <f>IF($B79="","",风险登记册!Q62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G79" s="34">
+        <f>IF($L79="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H79" s="5">
-        <f>IF($B79="","",风险登记册!R62)</f>
-        <v/>
-      </c>
-      <c r="I79" s="33">
-        <f>IF($B79="","",风险登记册!T62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I79" s="34">
+        <f>IF($L79="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J79" s="5">
-        <f>IF($B79="","",风险登记册!U62)</f>
+        <f>IF($L79="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L79,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K79" s="5">
-        <f>IF($B79="","",IF($J79="极高","每年必审",IF($J79="高","每年审计",IF($J79="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L79="","",IF($J79="极高","每年必审",IF($J79="高","每年审计",IF($J79="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L79" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L79)),"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5">
-        <f>IF($B80="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I80)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I80,风险登记册!$A$4:$A$203,"&lt;"&amp;$B80)+1)</f>
+        <f>IF($L80="","",ROWS($A$21:A80))</f>
         <v/>
       </c>
       <c r="B80" s="5">
-        <f>IF($B80="","",风险登记册!A63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C80" s="6">
-        <f>IF($B80="","",风险登记册!B63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D80" s="6">
-        <f>IF($B80="","",风险登记册!C63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E80" s="6">
-        <f>IF($B80="","",风险登记册!E63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F80" s="5">
-        <f>IF($B80="","",风险登记册!G63)</f>
-        <v/>
-      </c>
-      <c r="G80" s="33">
-        <f>IF($B80="","",风险登记册!Q63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G80" s="34">
+        <f>IF($L80="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H80" s="5">
-        <f>IF($B80="","",风险登记册!R63)</f>
-        <v/>
-      </c>
-      <c r="I80" s="33">
-        <f>IF($B80="","",风险登记册!T63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I80" s="34">
+        <f>IF($L80="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J80" s="5">
-        <f>IF($B80="","",风险登记册!U63)</f>
+        <f>IF($L80="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L80,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K80" s="5">
-        <f>IF($B80="","",IF($J80="极高","每年必审",IF($J80="高","每年审计",IF($J80="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L80="","",IF($J80="极高","每年必审",IF($J80="高","每年审计",IF($J80="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L80" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L80)),"")</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5">
-        <f>IF($B81="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I81)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I81,风险登记册!$A$4:$A$203,"&lt;"&amp;$B81)+1)</f>
+        <f>IF($L81="","",ROWS($A$21:A81))</f>
         <v/>
       </c>
       <c r="B81" s="5">
-        <f>IF($B81="","",风险登记册!A64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C81" s="6">
-        <f>IF($B81="","",风险登记册!B64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D81" s="6">
-        <f>IF($B81="","",风险登记册!C64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E81" s="6">
-        <f>IF($B81="","",风险登记册!E64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F81" s="5">
-        <f>IF($B81="","",风险登记册!G64)</f>
-        <v/>
-      </c>
-      <c r="G81" s="33">
-        <f>IF($B81="","",风险登记册!Q64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G81" s="34">
+        <f>IF($L81="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H81" s="5">
-        <f>IF($B81="","",风险登记册!R64)</f>
-        <v/>
-      </c>
-      <c r="I81" s="33">
-        <f>IF($B81="","",风险登记册!T64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I81" s="34">
+        <f>IF($L81="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J81" s="5">
-        <f>IF($B81="","",风险登记册!U64)</f>
+        <f>IF($L81="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L81,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K81" s="5">
-        <f>IF($B81="","",IF($J81="极高","每年必审",IF($J81="高","每年审计",IF($J81="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L81="","",IF($J81="极高","每年必审",IF($J81="高","每年审计",IF($J81="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L81" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L81)),"")</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5">
-        <f>IF($B82="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I82)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I82,风险登记册!$A$4:$A$203,"&lt;"&amp;$B82)+1)</f>
+        <f>IF($L82="","",ROWS($A$21:A82))</f>
         <v/>
       </c>
       <c r="B82" s="5">
-        <f>IF($B82="","",风险登记册!A65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C82" s="6">
-        <f>IF($B82="","",风险登记册!B65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D82" s="6">
-        <f>IF($B82="","",风险登记册!C65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E82" s="6">
-        <f>IF($B82="","",风险登记册!E65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F82" s="5">
-        <f>IF($B82="","",风险登记册!G65)</f>
-        <v/>
-      </c>
-      <c r="G82" s="33">
-        <f>IF($B82="","",风险登记册!Q65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G82" s="34">
+        <f>IF($L82="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H82" s="5">
-        <f>IF($B82="","",风险登记册!R65)</f>
-        <v/>
-      </c>
-      <c r="I82" s="33">
-        <f>IF($B82="","",风险登记册!T65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I82" s="34">
+        <f>IF($L82="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J82" s="5">
-        <f>IF($B82="","",风险登记册!U65)</f>
+        <f>IF($L82="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L82,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K82" s="5">
-        <f>IF($B82="","",IF($J82="极高","每年必审",IF($J82="高","每年审计",IF($J82="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L82="","",IF($J82="极高","每年必审",IF($J82="高","每年审计",IF($J82="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L82" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L82)),"")</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5">
-        <f>IF($B83="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I83)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I83,风险登记册!$A$4:$A$203,"&lt;"&amp;$B83)+1)</f>
+        <f>IF($L83="","",ROWS($A$21:A83))</f>
         <v/>
       </c>
       <c r="B83" s="5">
-        <f>IF($B83="","",风险登记册!A66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C83" s="6">
-        <f>IF($B83="","",风险登记册!B66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D83" s="6">
-        <f>IF($B83="","",风险登记册!C66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E83" s="6">
-        <f>IF($B83="","",风险登记册!E66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F83" s="5">
-        <f>IF($B83="","",风险登记册!G66)</f>
-        <v/>
-      </c>
-      <c r="G83" s="33">
-        <f>IF($B83="","",风险登记册!Q66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G83" s="34">
+        <f>IF($L83="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H83" s="5">
-        <f>IF($B83="","",风险登记册!R66)</f>
-        <v/>
-      </c>
-      <c r="I83" s="33">
-        <f>IF($B83="","",风险登记册!T66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I83" s="34">
+        <f>IF($L83="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J83" s="5">
-        <f>IF($B83="","",风险登记册!U66)</f>
+        <f>IF($L83="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L83,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K83" s="5">
-        <f>IF($B83="","",IF($J83="极高","每年必审",IF($J83="高","每年审计",IF($J83="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L83="","",IF($J83="极高","每年必审",IF($J83="高","每年审计",IF($J83="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L83" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5">
-        <f>IF($B84="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I84)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I84,风险登记册!$A$4:$A$203,"&lt;"&amp;$B84)+1)</f>
+        <f>IF($L84="","",ROWS($A$21:A84))</f>
         <v/>
       </c>
       <c r="B84" s="5">
-        <f>IF($B84="","",风险登记册!A67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C84" s="6">
-        <f>IF($B84="","",风险登记册!B67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D84" s="6">
-        <f>IF($B84="","",风险登记册!C67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E84" s="6">
-        <f>IF($B84="","",风险登记册!E67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F84" s="5">
-        <f>IF($B84="","",风险登记册!G67)</f>
-        <v/>
-      </c>
-      <c r="G84" s="33">
-        <f>IF($B84="","",风险登记册!Q67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G84" s="34">
+        <f>IF($L84="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H84" s="5">
-        <f>IF($B84="","",风险登记册!R67)</f>
-        <v/>
-      </c>
-      <c r="I84" s="33">
-        <f>IF($B84="","",风险登记册!T67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I84" s="34">
+        <f>IF($L84="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J84" s="5">
-        <f>IF($B84="","",风险登记册!U67)</f>
+        <f>IF($L84="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L84,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K84" s="5">
-        <f>IF($B84="","",IF($J84="极高","每年必审",IF($J84="高","每年审计",IF($J84="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L84="","",IF($J84="极高","每年必审",IF($J84="高","每年审计",IF($J84="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L84" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L84)),"")</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5">
-        <f>IF($B85="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I85)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I85,风险登记册!$A$4:$A$203,"&lt;"&amp;$B85)+1)</f>
+        <f>IF($L85="","",ROWS($A$21:A85))</f>
         <v/>
       </c>
       <c r="B85" s="5">
-        <f>IF($B85="","",风险登记册!A68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C85" s="6">
-        <f>IF($B85="","",风险登记册!B68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D85" s="6">
-        <f>IF($B85="","",风险登记册!C68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E85" s="6">
-        <f>IF($B85="","",风险登记册!E68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F85" s="5">
-        <f>IF($B85="","",风险登记册!G68)</f>
-        <v/>
-      </c>
-      <c r="G85" s="33">
-        <f>IF($B85="","",风险登记册!Q68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G85" s="34">
+        <f>IF($L85="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H85" s="5">
-        <f>IF($B85="","",风险登记册!R68)</f>
-        <v/>
-      </c>
-      <c r="I85" s="33">
-        <f>IF($B85="","",风险登记册!T68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I85" s="34">
+        <f>IF($L85="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J85" s="5">
-        <f>IF($B85="","",风险登记册!U68)</f>
+        <f>IF($L85="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L85,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K85" s="5">
-        <f>IF($B85="","",IF($J85="极高","每年必审",IF($J85="高","每年审计",IF($J85="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L85="","",IF($J85="极高","每年必审",IF($J85="高","每年审计",IF($J85="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L85" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L85)),"")</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5">
-        <f>IF($B86="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I86)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I86,风险登记册!$A$4:$A$203,"&lt;"&amp;$B86)+1)</f>
+        <f>IF($L86="","",ROWS($A$21:A86))</f>
         <v/>
       </c>
       <c r="B86" s="5">
-        <f>IF($B86="","",风险登记册!A69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C86" s="6">
-        <f>IF($B86="","",风险登记册!B69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D86" s="6">
-        <f>IF($B86="","",风险登记册!C69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E86" s="6">
-        <f>IF($B86="","",风险登记册!E69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F86" s="5">
-        <f>IF($B86="","",风险登记册!G69)</f>
-        <v/>
-      </c>
-      <c r="G86" s="33">
-        <f>IF($B86="","",风险登记册!Q69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G86" s="34">
+        <f>IF($L86="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H86" s="5">
-        <f>IF($B86="","",风险登记册!R69)</f>
-        <v/>
-      </c>
-      <c r="I86" s="33">
-        <f>IF($B86="","",风险登记册!T69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I86" s="34">
+        <f>IF($L86="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J86" s="5">
-        <f>IF($B86="","",风险登记册!U69)</f>
+        <f>IF($L86="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L86,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K86" s="5">
-        <f>IF($B86="","",IF($J86="极高","每年必审",IF($J86="高","每年审计",IF($J86="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L86="","",IF($J86="极高","每年必审",IF($J86="高","每年审计",IF($J86="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L86" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L86)),"")</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5">
-        <f>IF($B87="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I87)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I87,风险登记册!$A$4:$A$203,"&lt;"&amp;$B87)+1)</f>
+        <f>IF($L87="","",ROWS($A$21:A87))</f>
         <v/>
       </c>
       <c r="B87" s="5">
-        <f>IF($B87="","",风险登记册!A70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C87" s="6">
-        <f>IF($B87="","",风险登记册!B70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D87" s="6">
-        <f>IF($B87="","",风险登记册!C70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E87" s="6">
-        <f>IF($B87="","",风险登记册!E70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F87" s="5">
-        <f>IF($B87="","",风险登记册!G70)</f>
-        <v/>
-      </c>
-      <c r="G87" s="33">
-        <f>IF($B87="","",风险登记册!Q70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G87" s="34">
+        <f>IF($L87="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H87" s="5">
-        <f>IF($B87="","",风险登记册!R70)</f>
-        <v/>
-      </c>
-      <c r="I87" s="33">
-        <f>IF($B87="","",风险登记册!T70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I87" s="34">
+        <f>IF($L87="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J87" s="5">
-        <f>IF($B87="","",风险登记册!U70)</f>
+        <f>IF($L87="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L87,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K87" s="5">
-        <f>IF($B87="","",IF($J87="极高","每年必审",IF($J87="高","每年审计",IF($J87="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L87="","",IF($J87="极高","每年必审",IF($J87="高","每年审计",IF($J87="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L87" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L87)),"")</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5">
-        <f>IF($B88="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I88)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I88,风险登记册!$A$4:$A$203,"&lt;"&amp;$B88)+1)</f>
+        <f>IF($L88="","",ROWS($A$21:A88))</f>
         <v/>
       </c>
       <c r="B88" s="5">
-        <f>IF($B88="","",风险登记册!A71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C88" s="6">
-        <f>IF($B88="","",风险登记册!B71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D88" s="6">
-        <f>IF($B88="","",风险登记册!C71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E88" s="6">
-        <f>IF($B88="","",风险登记册!E71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F88" s="5">
-        <f>IF($B88="","",风险登记册!G71)</f>
-        <v/>
-      </c>
-      <c r="G88" s="33">
-        <f>IF($B88="","",风险登记册!Q71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G88" s="34">
+        <f>IF($L88="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H88" s="5">
-        <f>IF($B88="","",风险登记册!R71)</f>
-        <v/>
-      </c>
-      <c r="I88" s="33">
-        <f>IF($B88="","",风险登记册!T71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I88" s="34">
+        <f>IF($L88="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J88" s="5">
-        <f>IF($B88="","",风险登记册!U71)</f>
+        <f>IF($L88="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L88,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K88" s="5">
-        <f>IF($B88="","",IF($J88="极高","每年必审",IF($J88="高","每年审计",IF($J88="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L88="","",IF($J88="极高","每年必审",IF($J88="高","每年审计",IF($J88="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L88" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L88)),"")</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5">
-        <f>IF($B89="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I89)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I89,风险登记册!$A$4:$A$203,"&lt;"&amp;$B89)+1)</f>
+        <f>IF($L89="","",ROWS($A$21:A89))</f>
         <v/>
       </c>
       <c r="B89" s="5">
-        <f>IF($B89="","",风险登记册!A72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C89" s="6">
-        <f>IF($B89="","",风险登记册!B72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D89" s="6">
-        <f>IF($B89="","",风险登记册!C72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E89" s="6">
-        <f>IF($B89="","",风险登记册!E72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F89" s="5">
-        <f>IF($B89="","",风险登记册!G72)</f>
-        <v/>
-      </c>
-      <c r="G89" s="33">
-        <f>IF($B89="","",风险登记册!Q72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G89" s="34">
+        <f>IF($L89="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H89" s="5">
-        <f>IF($B89="","",风险登记册!R72)</f>
-        <v/>
-      </c>
-      <c r="I89" s="33">
-        <f>IF($B89="","",风险登记册!T72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I89" s="34">
+        <f>IF($L89="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J89" s="5">
-        <f>IF($B89="","",风险登记册!U72)</f>
+        <f>IF($L89="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L89,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K89" s="5">
-        <f>IF($B89="","",IF($J89="极高","每年必审",IF($J89="高","每年审计",IF($J89="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L89="","",IF($J89="极高","每年必审",IF($J89="高","每年审计",IF($J89="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L89" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L89)),"")</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5">
-        <f>IF($B90="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I90)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I90,风险登记册!$A$4:$A$203,"&lt;"&amp;$B90)+1)</f>
+        <f>IF($L90="","",ROWS($A$21:A90))</f>
         <v/>
       </c>
       <c r="B90" s="5">
-        <f>IF($B90="","",风险登记册!A73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C90" s="6">
-        <f>IF($B90="","",风险登记册!B73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D90" s="6">
-        <f>IF($B90="","",风险登记册!C73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E90" s="6">
-        <f>IF($B90="","",风险登记册!E73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F90" s="5">
-        <f>IF($B90="","",风险登记册!G73)</f>
-        <v/>
-      </c>
-      <c r="G90" s="33">
-        <f>IF($B90="","",风险登记册!Q73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G90" s="34">
+        <f>IF($L90="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H90" s="5">
-        <f>IF($B90="","",风险登记册!R73)</f>
-        <v/>
-      </c>
-      <c r="I90" s="33">
-        <f>IF($B90="","",风险登记册!T73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I90" s="34">
+        <f>IF($L90="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J90" s="5">
-        <f>IF($B90="","",风险登记册!U73)</f>
+        <f>IF($L90="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L90,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K90" s="5">
-        <f>IF($B90="","",IF($J90="极高","每年必审",IF($J90="高","每年审计",IF($J90="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L90="","",IF($J90="极高","每年必审",IF($J90="高","每年审计",IF($J90="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L90" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L90)),"")</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5">
-        <f>IF($B91="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I91)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I91,风险登记册!$A$4:$A$203,"&lt;"&amp;$B91)+1)</f>
+        <f>IF($L91="","",ROWS($A$21:A91))</f>
         <v/>
       </c>
       <c r="B91" s="5">
-        <f>IF($B91="","",风险登记册!A74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C91" s="6">
-        <f>IF($B91="","",风险登记册!B74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D91" s="6">
-        <f>IF($B91="","",风险登记册!C74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E91" s="6">
-        <f>IF($B91="","",风险登记册!E74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F91" s="5">
-        <f>IF($B91="","",风险登记册!G74)</f>
-        <v/>
-      </c>
-      <c r="G91" s="33">
-        <f>IF($B91="","",风险登记册!Q74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G91" s="34">
+        <f>IF($L91="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H91" s="5">
-        <f>IF($B91="","",风险登记册!R74)</f>
-        <v/>
-      </c>
-      <c r="I91" s="33">
-        <f>IF($B91="","",风险登记册!T74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I91" s="34">
+        <f>IF($L91="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J91" s="5">
-        <f>IF($B91="","",风险登记册!U74)</f>
+        <f>IF($L91="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L91,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K91" s="5">
-        <f>IF($B91="","",IF($J91="极高","每年必审",IF($J91="高","每年审计",IF($J91="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L91="","",IF($J91="极高","每年必审",IF($J91="高","每年审计",IF($J91="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L91" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L91)),"")</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5">
-        <f>IF($B92="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I92)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I92,风险登记册!$A$4:$A$203,"&lt;"&amp;$B92)+1)</f>
+        <f>IF($L92="","",ROWS($A$21:A92))</f>
         <v/>
       </c>
       <c r="B92" s="5">
-        <f>IF($B92="","",风险登记册!A75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C92" s="6">
-        <f>IF($B92="","",风险登记册!B75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D92" s="6">
-        <f>IF($B92="","",风险登记册!C75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E92" s="6">
-        <f>IF($B92="","",风险登记册!E75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F92" s="5">
-        <f>IF($B92="","",风险登记册!G75)</f>
-        <v/>
-      </c>
-      <c r="G92" s="33">
-        <f>IF($B92="","",风险登记册!Q75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G92" s="34">
+        <f>IF($L92="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H92" s="5">
-        <f>IF($B92="","",风险登记册!R75)</f>
-        <v/>
-      </c>
-      <c r="I92" s="33">
-        <f>IF($B92="","",风险登记册!T75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I92" s="34">
+        <f>IF($L92="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J92" s="5">
-        <f>IF($B92="","",风险登记册!U75)</f>
+        <f>IF($L92="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L92,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K92" s="5">
-        <f>IF($B92="","",IF($J92="极高","每年必审",IF($J92="高","每年审计",IF($J92="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L92="","",IF($J92="极高","每年必审",IF($J92="高","每年审计",IF($J92="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L92" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L92)),"")</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5">
-        <f>IF($B93="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I93)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I93,风险登记册!$A$4:$A$203,"&lt;"&amp;$B93)+1)</f>
+        <f>IF($L93="","",ROWS($A$21:A93))</f>
         <v/>
       </c>
       <c r="B93" s="5">
-        <f>IF($B93="","",风险登记册!A76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C93" s="6">
-        <f>IF($B93="","",风险登记册!B76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D93" s="6">
-        <f>IF($B93="","",风险登记册!C76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E93" s="6">
-        <f>IF($B93="","",风险登记册!E76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F93" s="5">
-        <f>IF($B93="","",风险登记册!G76)</f>
-        <v/>
-      </c>
-      <c r="G93" s="33">
-        <f>IF($B93="","",风险登记册!Q76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G93" s="34">
+        <f>IF($L93="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H93" s="5">
-        <f>IF($B93="","",风险登记册!R76)</f>
-        <v/>
-      </c>
-      <c r="I93" s="33">
-        <f>IF($B93="","",风险登记册!T76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I93" s="34">
+        <f>IF($L93="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J93" s="5">
-        <f>IF($B93="","",风险登记册!U76)</f>
+        <f>IF($L93="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L93,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K93" s="5">
-        <f>IF($B93="","",IF($J93="极高","每年必审",IF($J93="高","每年审计",IF($J93="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L93="","",IF($J93="极高","每年必审",IF($J93="高","每年审计",IF($J93="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L93" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L93)),"")</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5">
-        <f>IF($B94="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I94)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I94,风险登记册!$A$4:$A$203,"&lt;"&amp;$B94)+1)</f>
+        <f>IF($L94="","",ROWS($A$21:A94))</f>
         <v/>
       </c>
       <c r="B94" s="5">
-        <f>IF($B94="","",风险登记册!A77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C94" s="6">
-        <f>IF($B94="","",风险登记册!B77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D94" s="6">
-        <f>IF($B94="","",风险登记册!C77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E94" s="6">
-        <f>IF($B94="","",风险登记册!E77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F94" s="5">
-        <f>IF($B94="","",风险登记册!G77)</f>
-        <v/>
-      </c>
-      <c r="G94" s="33">
-        <f>IF($B94="","",风险登记册!Q77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G94" s="34">
+        <f>IF($L94="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H94" s="5">
-        <f>IF($B94="","",风险登记册!R77)</f>
-        <v/>
-      </c>
-      <c r="I94" s="33">
-        <f>IF($B94="","",风险登记册!T77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I94" s="34">
+        <f>IF($L94="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J94" s="5">
-        <f>IF($B94="","",风险登记册!U77)</f>
+        <f>IF($L94="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L94,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K94" s="5">
-        <f>IF($B94="","",IF($J94="极高","每年必审",IF($J94="高","每年审计",IF($J94="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L94="","",IF($J94="极高","每年必审",IF($J94="高","每年审计",IF($J94="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L94" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L94)),"")</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5">
-        <f>IF($B95="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I95)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I95,风险登记册!$A$4:$A$203,"&lt;"&amp;$B95)+1)</f>
+        <f>IF($L95="","",ROWS($A$21:A95))</f>
         <v/>
       </c>
       <c r="B95" s="5">
-        <f>IF($B95="","",风险登记册!A78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C95" s="6">
-        <f>IF($B95="","",风险登记册!B78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D95" s="6">
-        <f>IF($B95="","",风险登记册!C78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E95" s="6">
-        <f>IF($B95="","",风险登记册!E78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F95" s="5">
-        <f>IF($B95="","",风险登记册!G78)</f>
-        <v/>
-      </c>
-      <c r="G95" s="33">
-        <f>IF($B95="","",风险登记册!Q78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G95" s="34">
+        <f>IF($L95="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H95" s="5">
-        <f>IF($B95="","",风险登记册!R78)</f>
-        <v/>
-      </c>
-      <c r="I95" s="33">
-        <f>IF($B95="","",风险登记册!T78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I95" s="34">
+        <f>IF($L95="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J95" s="5">
-        <f>IF($B95="","",风险登记册!U78)</f>
+        <f>IF($L95="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L95,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K95" s="5">
-        <f>IF($B95="","",IF($J95="极高","每年必审",IF($J95="高","每年审计",IF($J95="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L95="","",IF($J95="极高","每年必审",IF($J95="高","每年审计",IF($J95="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L95" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L95)),"")</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5">
-        <f>IF($B96="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I96)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I96,风险登记册!$A$4:$A$203,"&lt;"&amp;$B96)+1)</f>
+        <f>IF($L96="","",ROWS($A$21:A96))</f>
         <v/>
       </c>
       <c r="B96" s="5">
-        <f>IF($B96="","",风险登记册!A79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C96" s="6">
-        <f>IF($B96="","",风险登记册!B79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D96" s="6">
-        <f>IF($B96="","",风险登记册!C79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E96" s="6">
-        <f>IF($B96="","",风险登记册!E79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F96" s="5">
-        <f>IF($B96="","",风险登记册!G79)</f>
-        <v/>
-      </c>
-      <c r="G96" s="33">
-        <f>IF($B96="","",风险登记册!Q79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G96" s="34">
+        <f>IF($L96="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H96" s="5">
-        <f>IF($B96="","",风险登记册!R79)</f>
-        <v/>
-      </c>
-      <c r="I96" s="33">
-        <f>IF($B96="","",风险登记册!T79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I96" s="34">
+        <f>IF($L96="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J96" s="5">
-        <f>IF($B96="","",风险登记册!U79)</f>
+        <f>IF($L96="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L96,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K96" s="5">
-        <f>IF($B96="","",IF($J96="极高","每年必审",IF($J96="高","每年审计",IF($J96="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L96="","",IF($J96="极高","每年必审",IF($J96="高","每年审计",IF($J96="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L96" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L96)),"")</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5">
-        <f>IF($B97="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I97)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I97,风险登记册!$A$4:$A$203,"&lt;"&amp;$B97)+1)</f>
+        <f>IF($L97="","",ROWS($A$21:A97))</f>
         <v/>
       </c>
       <c r="B97" s="5">
-        <f>IF($B97="","",风险登记册!A80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C97" s="6">
-        <f>IF($B97="","",风险登记册!B80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D97" s="6">
-        <f>IF($B97="","",风险登记册!C80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E97" s="6">
-        <f>IF($B97="","",风险登记册!E80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F97" s="5">
-        <f>IF($B97="","",风险登记册!G80)</f>
-        <v/>
-      </c>
-      <c r="G97" s="33">
-        <f>IF($B97="","",风险登记册!Q80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G97" s="34">
+        <f>IF($L97="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H97" s="5">
-        <f>IF($B97="","",风险登记册!R80)</f>
-        <v/>
-      </c>
-      <c r="I97" s="33">
-        <f>IF($B97="","",风险登记册!T80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I97" s="34">
+        <f>IF($L97="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J97" s="5">
-        <f>IF($B97="","",风险登记册!U80)</f>
+        <f>IF($L97="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L97,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K97" s="5">
-        <f>IF($B97="","",IF($J97="极高","每年必审",IF($J97="高","每年审计",IF($J97="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L97="","",IF($J97="极高","每年必审",IF($J97="高","每年审计",IF($J97="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L97" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L97)),"")</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5">
-        <f>IF($B98="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I98)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I98,风险登记册!$A$4:$A$203,"&lt;"&amp;$B98)+1)</f>
+        <f>IF($L98="","",ROWS($A$21:A98))</f>
         <v/>
       </c>
       <c r="B98" s="5">
-        <f>IF($B98="","",风险登记册!A81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C98" s="6">
-        <f>IF($B98="","",风险登记册!B81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D98" s="6">
-        <f>IF($B98="","",风险登记册!C81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E98" s="6">
-        <f>IF($B98="","",风险登记册!E81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F98" s="5">
-        <f>IF($B98="","",风险登记册!G81)</f>
-        <v/>
-      </c>
-      <c r="G98" s="33">
-        <f>IF($B98="","",风险登记册!Q81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G98" s="34">
+        <f>IF($L98="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H98" s="5">
-        <f>IF($B98="","",风险登记册!R81)</f>
-        <v/>
-      </c>
-      <c r="I98" s="33">
-        <f>IF($B98="","",风险登记册!T81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I98" s="34">
+        <f>IF($L98="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J98" s="5">
-        <f>IF($B98="","",风险登记册!U81)</f>
+        <f>IF($L98="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L98,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K98" s="5">
-        <f>IF($B98="","",IF($J98="极高","每年必审",IF($J98="高","每年审计",IF($J98="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L98="","",IF($J98="极高","每年必审",IF($J98="高","每年审计",IF($J98="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L98" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L98)),"")</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5">
-        <f>IF($B99="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I99)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I99,风险登记册!$A$4:$A$203,"&lt;"&amp;$B99)+1)</f>
+        <f>IF($L99="","",ROWS($A$21:A99))</f>
         <v/>
       </c>
       <c r="B99" s="5">
-        <f>IF($B99="","",风险登记册!A82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C99" s="6">
-        <f>IF($B99="","",风险登记册!B82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D99" s="6">
-        <f>IF($B99="","",风险登记册!C82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E99" s="6">
-        <f>IF($B99="","",风险登记册!E82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F99" s="5">
-        <f>IF($B99="","",风险登记册!G82)</f>
-        <v/>
-      </c>
-      <c r="G99" s="33">
-        <f>IF($B99="","",风险登记册!Q82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G99" s="34">
+        <f>IF($L99="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H99" s="5">
-        <f>IF($B99="","",风险登记册!R82)</f>
-        <v/>
-      </c>
-      <c r="I99" s="33">
-        <f>IF($B99="","",风险登记册!T82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I99" s="34">
+        <f>IF($L99="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J99" s="5">
-        <f>IF($B99="","",风险登记册!U82)</f>
+        <f>IF($L99="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L99,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K99" s="5">
-        <f>IF($B99="","",IF($J99="极高","每年必审",IF($J99="高","每年审计",IF($J99="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L99="","",IF($J99="极高","每年必审",IF($J99="高","每年审计",IF($J99="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L99" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L99)),"")</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5">
-        <f>IF($B100="","",COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,"&gt;"&amp;$I100)+COUNTIFS(风险登记册!$F$4:$F$203,IF($B$2="全部","&lt;&gt;",$B$2),风险登记册!$T$4:$T$203,$I100,风险登记册!$A$4:$A$203,"&lt;"&amp;$B100)+1)</f>
+        <f>IF($L100="","",ROWS($A$21:A100))</f>
         <v/>
       </c>
       <c r="B100" s="5">
-        <f>IF($B100="","",风险登记册!A83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$A$4:$A$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="C100" s="6">
-        <f>IF($B100="","",风险登记册!B83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$B$4:$B$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="D100" s="6">
-        <f>IF($B100="","",风险登记册!C83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$C$4:$C$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="E100" s="6">
-        <f>IF($B100="","",风险登记册!E83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$E$4:$E$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="F100" s="5">
-        <f>IF($B100="","",风险登记册!G83)</f>
-        <v/>
-      </c>
-      <c r="G100" s="33">
-        <f>IF($B100="","",风险登记册!Q83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$G$4:$G$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="G100" s="34">
+        <f>IF($L100="","",INDEX(风险登记册!$Q$4:$Q$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="H100" s="5">
-        <f>IF($B100="","",风险登记册!R83)</f>
-        <v/>
-      </c>
-      <c r="I100" s="33">
-        <f>IF($B100="","",风险登记册!T83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$R$4:$R$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
+        <v/>
+      </c>
+      <c r="I100" s="34">
+        <f>IF($L100="","",INDEX(风险登记册!$T$4:$T$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="J100" s="5">
-        <f>IF($B100="","",风险登记册!U83)</f>
+        <f>IF($L100="","",INDEX(风险登记册!$U$4:$U$203,MATCH($L100,风险登记册!$AA$4:$AA$203,0)))</f>
         <v/>
       </c>
       <c r="K100" s="5">
-        <f>IF($B100="","",IF($J100="极高","每年必审",IF($J100="高","每年审计",IF($J100="中","两年一轮","按需抽查"))))</f>
+        <f>IF($L100="","",IF($J100="极高","每年必审",IF($J100="高","每年审计",IF($J100="中","两年一轮","按需抽查"))))</f>
+        <v/>
+      </c>
+      <c r="L100" s="36">
+        <f>IFERROR(AGGREGATE(14,6,风险登记册!$AB$4:$AB$203,ROWS($L$21:L100)),"")</f>
         <v/>
       </c>
     </row>

--- a/audit_risk_register.xlsx
+++ b/audit_risk_register.xlsx
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>发生可能性（1-5）</t>
+          <t>发生可能性</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>COSO ERM 2017 风险偏好校准</t>
+          <t>COSO ERM 2017</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>内审发现/监管检查通报</t>
+          <t>内审发现/监管通报</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>ACFE：组织年均约 5% 收入流失于舞弊</t>
+          <t>ACFE：年均约 5% 营收流失于舞弊</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>已多次发生或正在发生，相关控制基本失效</t>
+          <t>已多次发生或正在发生，控制基本失效</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>经济损失 —— 国资委资产损失分级 + 国务院令第 493 号</t>
+          <t>经济损失（国资委资产损失分级 + 493 号令）</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>&lt;100 万元：未达“一般资产损失”标准，企业内部可消化</t>
+          <t>&lt;100 万元：未达“一般资产损失”</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>100~500 万元：构成“一般资产损失”</t>
+          <t>100~500 万元：一般资产损失</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>国资委办法：&lt;500 万为一般</t>
+          <t>国资委办法</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>500~5000 万元：构成“较大资产损失”；493 号令“较大事故”直接损失落于本档</t>
+          <t>500~5000 万元：较大资产损失；较大事故损失区间</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>国资委办法；国务院令第 493 号</t>
+          <t>国资委办法；493 号令</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>5000 万~1 亿元：构成“重大资产损失”；493 号令“重大事故”量级</t>
+          <t>5000 万~1 亿元：重大资产损失；重大事故量级</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>≥1 亿元：493 号令“特别重大事故”量级，危及企业生存</t>
+          <t>≥1 亿元：特别重大事故量级，危及企业生存</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>合规法律 —— 个保法/数安法/GDPR + 国资委不良后果三档</t>
+          <t>合规法律（个保法/数安法/GDPR + 不良后果三档）</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>内部制度瑕疵，责令整改即可，无外部后果</t>
+          <t>制度瑕疵，责令整改，无外部后果</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>监管关注/责令限期整改；罚款 &lt;100 万元</t>
+          <t>责令限期整改；罚款 &lt;100 万元</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>一般行政处罚，罚款 100~1000 万元；责任人被处分</t>
+          <t>一般行政处罚 100~1000 万元；责任人被处分</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>数安法第 45 条；网数条例第 56 条</t>
+          <t>数安法第 45 条</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>情节严重：罚款 1000~5000 万或上年营业额 5%（GDPR 顶格 2000 万欧/4% 同档）</t>
+          <t>情节严重 1000~5000 万或营业额 5%（GDPR 顶格同档）</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>个保法第 66 条第二款；GDPR Art.83</t>
+          <t>个保法第 66 条第二款；GDPR</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>刑事责任移送、责令停业/吊销执照；影响社会与国家层面</t>
+          <t>刑事移送、停业/吊照；影响社会与国家层面</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>运营中断 —— 493 号令事故等级 + ISO 22301 RTO 分级</t>
+          <t>运营中断（493 号令事故等级 + ISO 22301 RTO）</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>局部岗位受阻，当日恢复（RTO&lt;8h），无人员伤害</t>
+          <t>局部受阻，当日恢复（RTO&lt;8h）</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>ISO 22301 恢复目标分级</t>
+          <t>ISO 22301</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>单部门中断，RTO 1~3 天；轻微伤害事件</t>
+          <t>单部门中断，RTO 1~3 天</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>跨部门/跨区域中断，RTO 3~30 天；或 493 号令“一般事故”</t>
+          <t>跨部门中断，RTO 3~30 天；或“一般事故”</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>核心业务瘫痪 1~6 个月；或“较大/重大事故”量级</t>
+          <t>核心业务瘫痪 1~6 个月；或较大/重大事故量级</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>集团级瘫痪超 6 个月；或“特别重大事故”（≥30 人死亡或≥1 亿元）</t>
+          <t>集团级瘫痪超 6 个月；或特别重大事故</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>声誉舆情 —— 国资委不良后果三档 × 传播层级</t>
+          <t>声誉舆情（国资委不良后果三档 × 传播层级）</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>个别投诉、本地媒体负面报道，影响限于涉事企业</t>
+          <t>个别投诉、本地媒体报道，影响限于涉事企业</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>国资委：一般不良后果</t>
+          <t>一般不良后果</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>行业内流传、省级媒体或行业监管通报</t>
+          <t>行业内流传、省级媒体/监管通报</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>国资委：较大不良后果</t>
+          <t>较大不良后果</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>全国性媒体报道、上级通报批评，资本市场负面反应</t>
+          <t>全国性报道、上级通报批评、资本市场负面反应</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>国资委：较大~重大不良后果</t>
+          <t>较大~重大不良后果</t>
         </is>
       </c>
     </row>
@@ -1358,19 +1358,19 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>国家级媒体/监管部门点名、社会舆论事件、引发行业整顿</t>
+          <t>国家级点名、社会舆论事件、行业整顿</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>国资委：重大不良后果</t>
+          <t>重大不良后果</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>舞弊风险 —— ACFE 2024 基准 + 监察机关职务犯罪管辖</t>
+          <t>舞弊风险（ACFE 2024 基准 + 职务犯罪管辖）</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>无舞弊诱因，职责分离健全且经穿行测试，无历史案例</t>
+          <t>无诱因，职责分离健全经测试，无案例</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>COSO 控制环境；ISO 37001</t>
+          <t>COSO；ISO 37001</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>ACFE 2024：中位损失 $14.5 万</t>
+          <t>ACFE：中位 $14.5 万</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>诱因集中（权限集中/监督薄弱）；潜在损失 100~500 万元</t>
+          <t>诱因集中；潜在损失 100~500 万元</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>ACFE 2024：75 分位 $75 万</t>
+          <t>ACFE：75 分位 $75 万</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>诱因高危或有历史案例；潜在损失 500~5000 万元；涉嫌职务违法</t>
+          <t>诱因高危或有案例；潜在损失 500~5000 万元</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>国资委较大~重大资产损失档</t>
+          <t>国资委较大~重大档</t>
         </is>
       </c>
     </row>
@@ -1462,68 +1462,365 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>ACFE：年均 5% 收入流失于舞弊</t>
+          <t>ACFE：年均 5% 营收</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>战略影响（COSO ERM + 央企指引战略风险）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>分值</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>锚点</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>权威依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>对战略目标无偏离影响</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>COSO ERM 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>影响单项年度 KPI，可内部消化</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>COSO ERM 战略类</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>影响年度重点战略举措推进</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>央企指引战略风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>影响三年规划目标或主营业务布局</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>COSO：战略与绩效</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>颠覆战略目标/主营业务模式重构</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>央企指引：战略风险重大</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>数据安全（数安法分级 + ISO 27001 CIA）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>分值</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>锚点</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>权威依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>不涉及敏感数据</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>ISO 27001</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>少量内部非敏数据受损，可恢复</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>网数条例第 57 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>一般个人信息或商业数据泄露（&lt;10 万条）</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>个保法第 66 条第一款</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>大量个人信息/重要数据泄露或出境违规</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>个保法顶格；数安法第 45 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>重要数据泄露危害国家安全/公共安全</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>数安法：重大违规</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>健康安全（ISO 45001 + 安全生产法 + 493 号令）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>分值</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>锚点</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>权威依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>无人员伤害可能</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>ISO 45001</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>轻微伤风险，职业健康隐患</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>ISO 45001</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>重伤风险；一般事故苗头（&lt;3 人死亡）</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>493 号令一般事故</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>死亡 3~30 人或重伤 10~100 人量级</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>493 号令较大/重大事故</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>群死群伤（≥30 人死亡）或特别重大事故</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>493 号令特别重大</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>权威来源</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>1. 国务院国资委《中央企业违规经营投资责任追究实施办法》（2025 年修订，2026-01-01 施行，替代 37 号令）</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>2. 国务院令第 493 号《生产安全事故报告和调查处理条例》</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>3. 《个人信息保护法》第 66 条、《数据安全法》第 45 条、《网络数据安全管理条例》</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>4. GDPR 第 83 条（2000 万欧元或全球营业额 4%）</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>5. ACFE《Occupational Fraud 2024: A Report to the Nations》</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>6. 《监察法》《刑法》职务犯罪管辖标准</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>7. ISO 31000 / ISO 37301 / ISO 37001 / ISO 22301</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>8. COSO ERM 2017、IIA《全球内部审计准则》（2024）</t>
         </is>
